--- a/Input_data/EST_All Countries_trad_eco_cal_2025-02-14_to_2025-02-25.xlsx
+++ b/Input_data/EST_All Countries_trad_eco_cal_2025-02-14_to_2025-02-25.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G393"/>
+  <dimension ref="A1:G397"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3214,12 +3214,12 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>EU</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>European Commission Winter Forecasts</t>
+          <t>ImportsJAN</t>
         </is>
       </c>
       <c r="D93" t="inlineStr"/>
@@ -3333,12 +3333,12 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>EU</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>ImportsJAN</t>
+          <t>European Commission Winter Forecasts</t>
         </is>
       </c>
       <c r="D98" t="inlineStr"/>
@@ -3383,17 +3383,21 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>TR</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>RBA Press Conference</t>
+          <t>Auto Production YoYJAN</t>
         </is>
       </c>
       <c r="D100" t="inlineStr"/>
       <c r="E100" t="inlineStr"/>
-      <c r="F100" t="inlineStr"/>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>4.0%</t>
+        </is>
+      </c>
       <c r="G100" t="n">
         <v>2</v>
       </c>
@@ -3406,21 +3410,17 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>TR</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Budget BalanceJAN</t>
+          <t>RBA Press Conference</t>
         </is>
       </c>
       <c r="D101" t="inlineStr"/>
       <c r="E101" t="inlineStr"/>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>TRY-150.0B</t>
-        </is>
-      </c>
+      <c r="F101" t="inlineStr"/>
       <c r="G101" t="n">
         <v>2</v>
       </c>
@@ -3438,14 +3438,14 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Auto Production YoYJAN</t>
+          <t>Budget BalanceJAN</t>
         </is>
       </c>
       <c r="D102" t="inlineStr"/>
       <c r="E102" t="inlineStr"/>
       <c r="F102" t="inlineStr">
         <is>
-          <t>4.0%</t>
+          <t>TRY-150.0B</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -3542,14 +3542,14 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Average Earnings excl. Bonus (3Mo/Yr)DEC</t>
+          <t>HMRC Payrolls ChangeJAN</t>
         </is>
       </c>
       <c r="D106" t="inlineStr"/>
       <c r="E106" t="inlineStr"/>
       <c r="F106" t="inlineStr">
         <is>
-          <t>5.9%</t>
+          <t>-55.0K</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -3596,14 +3596,14 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>HMRC Payrolls ChangeJAN</t>
+          <t>Average Earnings excl. Bonus (3Mo/Yr)DEC</t>
         </is>
       </c>
       <c r="D108" t="inlineStr"/>
       <c r="E108" t="inlineStr"/>
       <c r="F108" t="inlineStr">
         <is>
-          <t>-55.0K</t>
+          <t>5.9%</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -3809,14 +3809,18 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>BoE Gov Bailey Speech</t>
+          <t>Labour Productivity QoQ PrelQ4</t>
         </is>
       </c>
       <c r="D115" t="inlineStr"/>
       <c r="E115" t="inlineStr"/>
-      <c r="F115" t="inlineStr"/>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>-0.1%</t>
+        </is>
+      </c>
       <c r="G115" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="116">
@@ -3827,23 +3831,23 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>ZA</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Labour Productivity QoQ PrelQ4</t>
+          <t>Unemployment RateQ4</t>
         </is>
       </c>
       <c r="D116" t="inlineStr"/>
       <c r="E116" t="inlineStr"/>
       <c r="F116" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>32.4%</t>
         </is>
       </c>
       <c r="G116" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="117">
@@ -3859,18 +3863,18 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Unemployment RateQ4</t>
+          <t>Unemployed PersonsQ4</t>
         </is>
       </c>
       <c r="D117" t="inlineStr"/>
       <c r="E117" t="inlineStr"/>
       <c r="F117" t="inlineStr">
         <is>
-          <t>32.4%</t>
+          <t>8.1M</t>
         </is>
       </c>
       <c r="G117" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="118">
@@ -3881,23 +3885,19 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>ZA</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Unemployed PersonsQ4</t>
+          <t>BoE Gov Bailey Speech</t>
         </is>
       </c>
       <c r="D118" t="inlineStr"/>
       <c r="E118" t="inlineStr"/>
-      <c r="F118" t="inlineStr">
-        <is>
-          <t>8.1M</t>
-        </is>
-      </c>
+      <c r="F118" t="inlineStr"/>
       <c r="G118" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="119">
@@ -4595,22 +4595,22 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Machinery Orders YoYDEC</t>
+          <t>Imports YoYJAN</t>
         </is>
       </c>
       <c r="D145" t="inlineStr"/>
       <c r="E145" t="inlineStr">
         <is>
-          <t>6.9%</t>
+          <t>9.7%</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>7.6%</t>
+          <t>2.0%</t>
         </is>
       </c>
       <c r="G145" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="146">
@@ -4626,22 +4626,22 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Imports YoYJAN</t>
+          <t>Machinery Orders MoMDEC</t>
         </is>
       </c>
       <c r="D146" t="inlineStr"/>
       <c r="E146" t="inlineStr">
         <is>
-          <t>9.7%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>2.0%</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="G146" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="147">
@@ -4657,18 +4657,18 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Machinery Orders MoMDEC</t>
+          <t>Machinery Orders YoYDEC</t>
         </is>
       </c>
       <c r="D147" t="inlineStr"/>
       <c r="E147" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>6.9%</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>7.6%</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -5306,18 +5306,18 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Lending Facility RateFEB</t>
+          <t>Deposit Facility RateFEB</t>
         </is>
       </c>
       <c r="D170" t="inlineStr"/>
       <c r="E170" t="inlineStr">
         <is>
-          <t>6.5%</t>
+          <t>5%</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>6.5%</t>
+          <t>5%</t>
         </is>
       </c>
       <c r="G170" t="n">
@@ -5337,18 +5337,18 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Deposit Facility RateFEB</t>
+          <t>Lending Facility RateFEB</t>
         </is>
       </c>
       <c r="D171" t="inlineStr"/>
       <c r="E171" t="inlineStr">
         <is>
-          <t>5%</t>
+          <t>6.5%</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>5%</t>
+          <t>6.5%</t>
         </is>
       </c>
       <c r="G171" t="n">
@@ -5583,17 +5583,21 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>4-Year Treasury Gilt Auction</t>
+          <t>Current AccountDEC</t>
         </is>
       </c>
       <c r="D180" t="inlineStr"/>
       <c r="E180" t="inlineStr"/>
-      <c r="F180" t="inlineStr"/>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>€ 3780M</t>
+        </is>
+      </c>
       <c r="G180" t="n">
         <v>3</v>
       </c>
@@ -5606,21 +5610,17 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Current AccountDEC</t>
+          <t>4-Year Treasury Gilt Auction</t>
         </is>
       </c>
       <c r="D181" t="inlineStr"/>
       <c r="E181" t="inlineStr"/>
-      <c r="F181" t="inlineStr">
-        <is>
-          <t>€ 3780M</t>
-        </is>
-      </c>
+      <c r="F181" t="inlineStr"/>
       <c r="G181" t="n">
         <v>3</v>
       </c>
@@ -5899,18 +5899,18 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Housing StartsJAN</t>
+          <t>Building Permits PrelJAN</t>
         </is>
       </c>
       <c r="D193" t="inlineStr"/>
       <c r="E193" t="inlineStr">
         <is>
-          <t>1.39M</t>
+          <t>1.45M</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>1.35M</t>
+          <t>1.47M</t>
         </is>
       </c>
       <c r="G193" t="n">
@@ -5930,18 +5930,22 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Housing Starts MoMJAN</t>
+          <t>Housing StartsJAN</t>
         </is>
       </c>
       <c r="D194" t="inlineStr"/>
-      <c r="E194" t="inlineStr"/>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>1.39M</t>
+        </is>
+      </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>-9.0%</t>
+          <t>1.35M</t>
         </is>
       </c>
       <c r="G194" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="195">
@@ -5984,22 +5988,18 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Building Permits PrelJAN</t>
+          <t>Housing Starts MoMJAN</t>
         </is>
       </c>
       <c r="D196" t="inlineStr"/>
-      <c r="E196" t="inlineStr">
-        <is>
-          <t>1.45M</t>
-        </is>
-      </c>
+      <c r="E196" t="inlineStr"/>
       <c r="F196" t="inlineStr">
         <is>
-          <t>1.47M</t>
+          <t>-9.0%</t>
         </is>
       </c>
       <c r="G196" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="197">
@@ -6342,7 +6342,7 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Foreign Bond InvestmentFEB/15</t>
+          <t>Stock Investment by ForeignersFEB/15</t>
         </is>
       </c>
       <c r="D210" t="inlineStr"/>
@@ -6365,7 +6365,7 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Stock Investment by ForeignersFEB/15</t>
+          <t>Foreign Bond InvestmentFEB/15</t>
         </is>
       </c>
       <c r="D211" t="inlineStr"/>
@@ -6616,12 +6616,16 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>M2 Money Supply YoYJAN</t>
+          <t>Current AccountQ4</t>
         </is>
       </c>
       <c r="D220" t="inlineStr"/>
       <c r="E220" t="inlineStr"/>
-      <c r="F220" t="inlineStr"/>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>$ -0.6B</t>
+        </is>
+      </c>
       <c r="G220" t="n">
         <v>3</v>
       </c>
@@ -6634,21 +6638,17 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>ID</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Consumer ConfidenceJAN</t>
+          <t>M2 Money Supply YoYJAN</t>
         </is>
       </c>
       <c r="D221" t="inlineStr"/>
       <c r="E221" t="inlineStr"/>
-      <c r="F221" t="inlineStr">
-        <is>
-          <t>85.5</t>
-        </is>
-      </c>
+      <c r="F221" t="inlineStr"/>
       <c r="G221" t="n">
         <v>3</v>
       </c>
@@ -6661,19 +6661,19 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>ID</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Current AccountQ4</t>
+          <t>Consumer ConfidenceJAN</t>
         </is>
       </c>
       <c r="D222" t="inlineStr"/>
       <c r="E222" t="inlineStr"/>
       <c r="F222" t="inlineStr">
         <is>
-          <t>$ -0.6B</t>
+          <t>85.5</t>
         </is>
       </c>
       <c r="G222" t="n">
@@ -6970,7 +6970,7 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>11-Year Index-Linked OAT Auction</t>
+          <t>6-Year Index-Linked OAT Auction</t>
         </is>
       </c>
       <c r="D234" t="inlineStr"/>
@@ -6988,19 +6988,27 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>18-Year Index-Linked OAT Auction</t>
+          <t>CBI Industrial Trends OrdersFEB</t>
         </is>
       </c>
       <c r="D235" t="inlineStr"/>
-      <c r="E235" t="inlineStr"/>
-      <c r="F235" t="inlineStr"/>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>-30</t>
+        </is>
+      </c>
+      <c r="F235" t="inlineStr">
+        <is>
+          <t>-25</t>
+        </is>
+      </c>
       <c r="G235" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="236">
@@ -7011,17 +7019,21 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>ZA</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>6-Year Index-Linked OAT Auction</t>
+          <t>Building Permits YoYDEC</t>
         </is>
       </c>
       <c r="D236" t="inlineStr"/>
       <c r="E236" t="inlineStr"/>
-      <c r="F236" t="inlineStr"/>
+      <c r="F236" t="inlineStr">
+        <is>
+          <t>18.0%</t>
+        </is>
+      </c>
       <c r="G236" t="n">
         <v>3</v>
       </c>
@@ -7057,21 +7069,17 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>ZA</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Building Permits YoYDEC</t>
+          <t>11-Year Index-Linked OAT Auction</t>
         </is>
       </c>
       <c r="D238" t="inlineStr"/>
       <c r="E238" t="inlineStr"/>
-      <c r="F238" t="inlineStr">
-        <is>
-          <t>18.0%</t>
-        </is>
-      </c>
+      <c r="F238" t="inlineStr"/>
       <c r="G238" t="n">
         <v>3</v>
       </c>
@@ -7084,27 +7092,19 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>CBI Industrial Trends OrdersFEB</t>
+          <t>18-Year Index-Linked OAT Auction</t>
         </is>
       </c>
       <c r="D239" t="inlineStr"/>
-      <c r="E239" t="inlineStr">
-        <is>
-          <t>-30</t>
-        </is>
-      </c>
-      <c r="F239" t="inlineStr">
-        <is>
-          <t>-25</t>
-        </is>
-      </c>
+      <c r="E239" t="inlineStr"/>
+      <c r="F239" t="inlineStr"/>
       <c r="G239" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="240">
@@ -7220,12 +7220,16 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Philly Fed CAPEX IndexFEB</t>
+          <t>Jobless Claims 4-week AverageFEB/15</t>
         </is>
       </c>
       <c r="D244" t="inlineStr"/>
       <c r="E244" t="inlineStr"/>
-      <c r="F244" t="inlineStr"/>
+      <c r="F244" t="inlineStr">
+        <is>
+          <t>219.0K</t>
+        </is>
+      </c>
       <c r="G244" t="n">
         <v>3</v>
       </c>
@@ -7238,21 +7242,17 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>US</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Raw Materials Prices MoMJAN</t>
+          <t>Philly Fed CAPEX IndexFEB</t>
         </is>
       </c>
       <c r="D245" t="inlineStr"/>
       <c r="E245" t="inlineStr"/>
-      <c r="F245" t="inlineStr">
-        <is>
-          <t>-0.2%</t>
-        </is>
-      </c>
+      <c r="F245" t="inlineStr"/>
       <c r="G245" t="n">
         <v>3</v>
       </c>
@@ -7270,12 +7270,16 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Philly Fed New OrdersFEB</t>
+          <t>Continuing Jobless ClaimsFEB/08</t>
         </is>
       </c>
       <c r="D246" t="inlineStr"/>
       <c r="E246" t="inlineStr"/>
-      <c r="F246" t="inlineStr"/>
+      <c r="F246" t="inlineStr">
+        <is>
+          <t>1879.0K</t>
+        </is>
+      </c>
       <c r="G246" t="n">
         <v>3</v>
       </c>
@@ -7293,16 +7297,12 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/15</t>
+          <t>Philly Fed New OrdersFEB</t>
         </is>
       </c>
       <c r="D247" t="inlineStr"/>
       <c r="E247" t="inlineStr"/>
-      <c r="F247" t="inlineStr">
-        <is>
-          <t>219.0K</t>
-        </is>
-      </c>
+      <c r="F247" t="inlineStr"/>
       <c r="G247" t="n">
         <v>3</v>
       </c>
@@ -7366,18 +7366,22 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/08</t>
+          <t>Philadelphia Fed Manufacturing IndexFEB</t>
         </is>
       </c>
       <c r="D250" t="inlineStr"/>
-      <c r="E250" t="inlineStr"/>
+      <c r="E250" t="inlineStr">
+        <is>
+          <t>25.5</t>
+        </is>
+      </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>1879.0K</t>
+          <t>18</t>
         </is>
       </c>
       <c r="G250" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="251">
@@ -7393,14 +7397,14 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>PPI MoMJAN</t>
+          <t>Raw Materials Prices YoYJAN</t>
         </is>
       </c>
       <c r="D251" t="inlineStr"/>
       <c r="E251" t="inlineStr"/>
       <c r="F251" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>10.0%</t>
         </is>
       </c>
       <c r="G251" t="n">
@@ -7415,27 +7419,23 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/15</t>
+          <t>Raw Materials Prices MoMJAN</t>
         </is>
       </c>
       <c r="D252" t="inlineStr"/>
-      <c r="E252" t="inlineStr">
-        <is>
-          <t>216K</t>
-        </is>
-      </c>
+      <c r="E252" t="inlineStr"/>
       <c r="F252" t="inlineStr">
         <is>
-          <t>220.0K</t>
+          <t>-0.2%</t>
         </is>
       </c>
       <c r="G252" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="253">
@@ -7451,18 +7451,18 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>New Housing Price Index MoMJAN</t>
+          <t>PPI YoYJAN</t>
         </is>
       </c>
       <c r="D253" t="inlineStr"/>
       <c r="E253" t="inlineStr"/>
       <c r="F253" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="G253" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="254">
@@ -7478,18 +7478,18 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>New Housing Price Index YoYJAN</t>
+          <t>PPI MoMJAN</t>
         </is>
       </c>
       <c r="D254" t="inlineStr"/>
       <c r="E254" t="inlineStr"/>
       <c r="F254" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="G254" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="255">
@@ -7500,23 +7500,19 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Philadelphia Fed Manufacturing IndexFEB</t>
+          <t>New Housing Price Index YoYJAN</t>
         </is>
       </c>
       <c r="D255" t="inlineStr"/>
-      <c r="E255" t="inlineStr">
-        <is>
-          <t>25.5</t>
-        </is>
-      </c>
+      <c r="E255" t="inlineStr"/>
       <c r="F255" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G255" t="n">
@@ -7536,18 +7532,18 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>PPI YoYJAN</t>
+          <t>New Housing Price Index MoMJAN</t>
         </is>
       </c>
       <c r="D256" t="inlineStr"/>
       <c r="E256" t="inlineStr"/>
       <c r="F256" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G256" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="257">
@@ -7558,23 +7554,27 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>US</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Raw Materials Prices YoYJAN</t>
+          <t>Initial Jobless ClaimsFEB/15</t>
         </is>
       </c>
       <c r="D257" t="inlineStr"/>
-      <c r="E257" t="inlineStr"/>
+      <c r="E257" t="inlineStr">
+        <is>
+          <t>216K</t>
+        </is>
+      </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>220.0K</t>
         </is>
       </c>
       <c r="G257" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="258">
@@ -7771,7 +7771,7 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>4-Week Bill Auction</t>
+          <t>8-Week Bill Auction</t>
         </is>
       </c>
       <c r="D265" t="inlineStr"/>
@@ -7794,7 +7794,7 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>8-Week Bill Auction</t>
+          <t>4-Week Bill Auction</t>
         </is>
       </c>
       <c r="D266" t="inlineStr"/>
@@ -7817,7 +7817,7 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/14</t>
+          <t>EIA Distillate Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="D267" t="inlineStr"/>
@@ -7840,7 +7840,7 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/14</t>
+          <t>EIA Gasoline Production ChangeFEB/14</t>
         </is>
       </c>
       <c r="D268" t="inlineStr"/>
@@ -7863,7 +7863,7 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/14</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/14</t>
         </is>
       </c>
       <c r="D269" t="inlineStr"/>
@@ -7886,7 +7886,7 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/14</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/14</t>
         </is>
       </c>
       <c r="D270" t="inlineStr"/>
@@ -7909,7 +7909,7 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/14</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="D271" t="inlineStr"/>
@@ -7932,7 +7932,7 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/14</t>
+          <t>EIA Crude Oil Imports ChangeFEB/14</t>
         </is>
       </c>
       <c r="D272" t="inlineStr"/>
@@ -7955,7 +7955,7 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/14</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="D273" t="inlineStr"/>
@@ -8207,21 +8207,17 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>US</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>S&amp;P Global Australia Manufacturing PMI FlashFEB</t>
+          <t>Fed Kugler Speech</t>
         </is>
       </c>
       <c r="D284" t="inlineStr"/>
       <c r="E284" t="inlineStr"/>
-      <c r="F284" t="inlineStr">
-        <is>
-          <t>49.9</t>
-        </is>
-      </c>
+      <c r="F284" t="inlineStr"/>
       <c r="G284" t="n">
         <v>2</v>
       </c>
@@ -8239,18 +8235,18 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>S&amp;P Global Australia Services PMI FlashFEB</t>
+          <t>S&amp;P Global Australia Composite PMI FlashFEB</t>
         </is>
       </c>
       <c r="D285" t="inlineStr"/>
       <c r="E285" t="inlineStr"/>
       <c r="F285" t="inlineStr">
         <is>
-          <t>51.3</t>
+          <t>50.6</t>
         </is>
       </c>
       <c r="G285" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="286">
@@ -8266,18 +8262,18 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>S&amp;P Global Australia Composite PMI FlashFEB</t>
+          <t>S&amp;P Global Australia Manufacturing PMI FlashFEB</t>
         </is>
       </c>
       <c r="D286" t="inlineStr"/>
       <c r="E286" t="inlineStr"/>
       <c r="F286" t="inlineStr">
         <is>
-          <t>50.6</t>
+          <t>49.9</t>
         </is>
       </c>
       <c r="G286" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="287">
@@ -8288,17 +8284,21 @@
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>Fed Kugler Speech</t>
+          <t>S&amp;P Global Australia Services PMI FlashFEB</t>
         </is>
       </c>
       <c r="D287" t="inlineStr"/>
       <c r="E287" t="inlineStr"/>
-      <c r="F287" t="inlineStr"/>
+      <c r="F287" t="inlineStr">
+        <is>
+          <t>51.3</t>
+        </is>
+      </c>
       <c r="G287" t="n">
         <v>2</v>
       </c>
@@ -8343,18 +8343,18 @@
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>Inflation Rate YoYJAN</t>
+          <t>Inflation Rate MoMJAN</t>
         </is>
       </c>
       <c r="D289" t="inlineStr"/>
       <c r="E289" t="inlineStr"/>
       <c r="F289" t="inlineStr">
         <is>
-          <t>3.7%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G289" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="290">
@@ -8370,22 +8370,18 @@
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>Core Inflation Rate YoYJAN</t>
+          <t>Inflation Rate YoYJAN</t>
         </is>
       </c>
       <c r="D290" t="inlineStr"/>
-      <c r="E290" t="inlineStr">
-        <is>
-          <t>3.1%</t>
-        </is>
-      </c>
+      <c r="E290" t="inlineStr"/>
       <c r="F290" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>3.7%</t>
         </is>
       </c>
       <c r="G290" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="291">
@@ -8401,18 +8397,22 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>Inflation Rate Ex-Food and Energy YoYJAN</t>
+          <t>Core Inflation Rate YoYJAN</t>
         </is>
       </c>
       <c r="D291" t="inlineStr"/>
-      <c r="E291" t="inlineStr"/>
+      <c r="E291" t="inlineStr">
+        <is>
+          <t>3.1%</t>
+        </is>
+      </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="G291" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="292">
@@ -8428,14 +8428,14 @@
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>Inflation Rate MoMJAN</t>
+          <t>Inflation Rate Ex-Food and Energy YoYJAN</t>
         </is>
       </c>
       <c r="D292" t="inlineStr"/>
       <c r="E292" t="inlineStr"/>
       <c r="F292" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>2.6%</t>
         </is>
       </c>
       <c r="G292" t="n">
@@ -8486,18 +8486,22 @@
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>Jibun Bank Composite PMI FlashFEB</t>
+          <t>Jibun Bank Manufacturing PMI FlashFEB</t>
         </is>
       </c>
       <c r="D294" t="inlineStr"/>
-      <c r="E294" t="inlineStr"/>
+      <c r="E294" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>51.5</t>
+          <t>49.6</t>
         </is>
       </c>
       <c r="G294" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="295">
@@ -8540,22 +8544,18 @@
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>Jibun Bank Manufacturing PMI FlashFEB</t>
+          <t>Jibun Bank Composite PMI FlashFEB</t>
         </is>
       </c>
       <c r="D296" t="inlineStr"/>
-      <c r="E296" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
+      <c r="E296" t="inlineStr"/>
       <c r="F296" t="inlineStr">
         <is>
-          <t>49.6</t>
+          <t>51.5</t>
         </is>
       </c>
       <c r="G296" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="297">
@@ -8612,17 +8612,21 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>TR</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>3-Month Bill Auction</t>
+          <t>Central Government DebtJAN</t>
         </is>
       </c>
       <c r="D299" t="inlineStr"/>
       <c r="E299" t="inlineStr"/>
-      <c r="F299" t="inlineStr"/>
+      <c r="F299" t="inlineStr">
+        <is>
+          <t>TRY 9.4T</t>
+        </is>
+      </c>
       <c r="G299" t="n">
         <v>3</v>
       </c>
@@ -8635,21 +8639,17 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>TR</t>
+          <t>BR</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>Central Government DebtJAN</t>
+          <t>10-Year NTN-F Auction</t>
         </is>
       </c>
       <c r="D300" t="inlineStr"/>
       <c r="E300" t="inlineStr"/>
-      <c r="F300" t="inlineStr">
-        <is>
-          <t>TRY 9.4T</t>
-        </is>
-      </c>
+      <c r="F300" t="inlineStr"/>
       <c r="G300" t="n">
         <v>3</v>
       </c>
@@ -8662,12 +8662,12 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>10-Year NTN-F Auction</t>
+          <t>3-Month Bill Auction</t>
         </is>
       </c>
       <c r="D301" t="inlineStr"/>
@@ -8771,18 +8771,22 @@
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>Retail Sales ex Fuel YoYJAN</t>
+          <t>Retail Sales MoMJAN</t>
         </is>
       </c>
       <c r="D305" t="inlineStr"/>
-      <c r="E305" t="inlineStr"/>
+      <c r="E305" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>3.0%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G305" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="306">
@@ -8798,22 +8802,18 @@
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>Retail Sales MoMJAN</t>
+          <t>Retail Sales YoYJAN</t>
         </is>
       </c>
       <c r="D306" t="inlineStr"/>
-      <c r="E306" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+      <c r="E306" t="inlineStr"/>
       <c r="F306" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>4.0%</t>
         </is>
       </c>
       <c r="G306" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="307">
@@ -8829,18 +8829,22 @@
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>Retail Sales YoYJAN</t>
+          <t>Public Sector Net Borrowing Ex BanksJAN</t>
         </is>
       </c>
       <c r="D307" t="inlineStr"/>
-      <c r="E307" t="inlineStr"/>
+      <c r="E307" t="inlineStr">
+        <is>
+          <t>£20.5B</t>
+        </is>
+      </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>4.0%</t>
+          <t>£19.0B</t>
         </is>
       </c>
       <c r="G307" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="308">
@@ -8856,18 +8860,14 @@
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>Public Sector Net Borrowing Ex BanksJAN</t>
+          <t>Retail Sales ex Fuel MoMJAN</t>
         </is>
       </c>
       <c r="D308" t="inlineStr"/>
-      <c r="E308" t="inlineStr">
-        <is>
-          <t>£20.5B</t>
-        </is>
-      </c>
+      <c r="E308" t="inlineStr"/>
       <c r="F308" t="inlineStr">
         <is>
-          <t>£19.0B</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G308" t="n">
@@ -8887,14 +8887,14 @@
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>Retail Sales ex Fuel MoMJAN</t>
+          <t>Retail Sales ex Fuel YoYJAN</t>
         </is>
       </c>
       <c r="D309" t="inlineStr"/>
       <c r="E309" t="inlineStr"/>
       <c r="F309" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.0%</t>
         </is>
       </c>
       <c r="G309" t="n">
@@ -8914,18 +8914,18 @@
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>Business ConfidenceFEB</t>
+          <t>Business Climate IndicatorFEB</t>
         </is>
       </c>
       <c r="D310" t="inlineStr"/>
       <c r="E310" t="inlineStr"/>
       <c r="F310" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>92</t>
         </is>
       </c>
       <c r="G310" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="311">
@@ -8941,18 +8941,18 @@
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>Business Climate IndicatorFEB</t>
+          <t>Business ConfidenceFEB</t>
         </is>
       </c>
       <c r="D311" t="inlineStr"/>
       <c r="E311" t="inlineStr"/>
       <c r="F311" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>94</t>
         </is>
       </c>
       <c r="G311" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="312">
@@ -9200,22 +9200,22 @@
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>Inflation Rate MoM FinalJAN</t>
+          <t>Harmonised Inflation Rate MoM FinalJAN</t>
         </is>
       </c>
       <c r="D320" t="inlineStr"/>
       <c r="E320" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>-0.7%</t>
         </is>
       </c>
       <c r="F320" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>-0.7%</t>
         </is>
       </c>
       <c r="G320" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="321">
@@ -9231,22 +9231,22 @@
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>Harmonised Inflation Rate MoM FinalJAN</t>
+          <t>Inflation Rate YoY FinalJAN</t>
         </is>
       </c>
       <c r="D321" t="inlineStr"/>
       <c r="E321" t="inlineStr">
         <is>
-          <t>-0.7%</t>
+          <t>1.5%</t>
         </is>
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t>-0.7%</t>
+          <t>1.5%</t>
         </is>
       </c>
       <c r="G321" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="322">
@@ -9262,18 +9262,18 @@
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>Inflation Rate YoY FinalJAN</t>
+          <t>Inflation Rate MoM FinalJAN</t>
         </is>
       </c>
       <c r="D322" t="inlineStr"/>
       <c r="E322" t="inlineStr">
         <is>
-          <t>1.5%</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t>1.5%</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="G322" t="n">
@@ -9517,14 +9517,14 @@
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>Economic Activity MoMDEC</t>
+          <t>Economic Activity YoYDEC</t>
         </is>
       </c>
       <c r="D331" t="inlineStr"/>
       <c r="E331" t="inlineStr"/>
       <c r="F331" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>2%</t>
         </is>
       </c>
       <c r="G331" t="n">
@@ -9544,18 +9544,22 @@
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>Economic Activity YoYDEC</t>
+          <t>GDP Growth Rate YoY FinalQ4</t>
         </is>
       </c>
       <c r="D332" t="inlineStr"/>
-      <c r="E332" t="inlineStr"/>
+      <c r="E332" t="inlineStr">
+        <is>
+          <t>0.6%</t>
+        </is>
+      </c>
       <c r="F332" t="inlineStr">
         <is>
-          <t>2%</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="G332" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="333">
@@ -9571,22 +9575,18 @@
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>GDP Growth Rate YoY FinalQ4</t>
+          <t>Economic Activity MoMDEC</t>
         </is>
       </c>
       <c r="D333" t="inlineStr"/>
-      <c r="E333" t="inlineStr">
-        <is>
-          <t>0.6%</t>
-        </is>
-      </c>
+      <c r="E333" t="inlineStr"/>
       <c r="F333" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="G333" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="334">
@@ -9772,7 +9772,7 @@
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>S&amp;P Global Services PMI FlashFEB</t>
+          <t>S&amp;P Global Composite PMI FlashFEB</t>
         </is>
       </c>
       <c r="D340" t="inlineStr"/>
@@ -9799,14 +9799,14 @@
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>S&amp;P Global Composite PMI FlashFEB</t>
+          <t>S&amp;P Global Manufacturing PMI FlashFEB</t>
         </is>
       </c>
       <c r="D341" t="inlineStr"/>
       <c r="E341" t="inlineStr"/>
       <c r="F341" t="inlineStr">
         <is>
-          <t>52.7</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="G341" t="n">
@@ -9826,14 +9826,14 @@
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>S&amp;P Global Manufacturing PMI FlashFEB</t>
+          <t>S&amp;P Global Services PMI FlashFEB</t>
         </is>
       </c>
       <c r="D342" t="inlineStr"/>
       <c r="E342" t="inlineStr"/>
       <c r="F342" t="inlineStr">
         <is>
-          <t>51.3</t>
+          <t>52.7</t>
         </is>
       </c>
       <c r="G342" t="n">
@@ -9853,18 +9853,18 @@
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>Michigan Consumer Expectations FinalFEB</t>
+          <t>Michigan Current Conditions FinalFEB</t>
         </is>
       </c>
       <c r="D343" t="inlineStr"/>
       <c r="E343" t="inlineStr">
         <is>
-          <t>67.3</t>
+          <t>68.7</t>
         </is>
       </c>
       <c r="F343" t="inlineStr">
         <is>
-          <t>67.3</t>
+          <t>68.7</t>
         </is>
       </c>
       <c r="G343" t="n">
@@ -9915,18 +9915,18 @@
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>Michigan Current Conditions FinalFEB</t>
+          <t>Michigan Consumer Expectations FinalFEB</t>
         </is>
       </c>
       <c r="D345" t="inlineStr"/>
       <c r="E345" t="inlineStr">
         <is>
-          <t>68.7</t>
+          <t>67.3</t>
         </is>
       </c>
       <c r="F345" t="inlineStr">
         <is>
-          <t>68.7</t>
+          <t>67.3</t>
         </is>
       </c>
       <c r="G345" t="n">
@@ -9977,14 +9977,18 @@
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>Existing Home Sales MoMJAN</t>
+          <t>Michigan Consumer Sentiment FinalFEB</t>
         </is>
       </c>
       <c r="D347" t="inlineStr"/>
-      <c r="E347" t="inlineStr"/>
+      <c r="E347" t="inlineStr">
+        <is>
+          <t>67.8</t>
+        </is>
+      </c>
       <c r="F347" t="inlineStr">
         <is>
-          <t>-1.7%</t>
+          <t>67.8</t>
         </is>
       </c>
       <c r="G347" t="n">
@@ -10004,18 +10008,14 @@
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>Michigan Consumer Sentiment FinalFEB</t>
+          <t>Existing Home Sales MoMJAN</t>
         </is>
       </c>
       <c r="D348" t="inlineStr"/>
-      <c r="E348" t="inlineStr">
-        <is>
-          <t>67.8</t>
-        </is>
-      </c>
+      <c r="E348" t="inlineStr"/>
       <c r="F348" t="inlineStr">
         <is>
-          <t>67.8</t>
+          <t>-1.7%</t>
         </is>
       </c>
       <c r="G348" t="n">
@@ -10379,18 +10379,18 @@
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>Ifo ExpectationsFEB</t>
+          <t>Ifo Business ClimateFEB</t>
         </is>
       </c>
       <c r="D363" t="inlineStr"/>
       <c r="E363" t="inlineStr"/>
       <c r="F363" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>84</t>
         </is>
       </c>
       <c r="G363" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="364">
@@ -10406,18 +10406,18 @@
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>Ifo Business ClimateFEB</t>
+          <t>Ifo Current ConditionsFEB</t>
         </is>
       </c>
       <c r="D364" t="inlineStr"/>
       <c r="E364" t="inlineStr"/>
       <c r="F364" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>85.1</t>
         </is>
       </c>
       <c r="G364" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="365">
@@ -10433,14 +10433,14 @@
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>Ifo Current ConditionsFEB</t>
+          <t>Ifo ExpectationsFEB</t>
         </is>
       </c>
       <c r="D365" t="inlineStr"/>
       <c r="E365" t="inlineStr"/>
       <c r="F365" t="inlineStr">
         <is>
-          <t>85.1</t>
+          <t>83</t>
         </is>
       </c>
       <c r="G365" t="n">
@@ -10460,18 +10460,18 @@
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>Inflation Rate MoM FinalJAN</t>
+          <t>CPI FinalJAN</t>
         </is>
       </c>
       <c r="D366" t="inlineStr"/>
       <c r="E366" t="inlineStr">
         <is>
-          <t>-0.3%</t>
+          <t>126.71</t>
         </is>
       </c>
       <c r="F366" t="inlineStr">
         <is>
-          <t>-0.3%</t>
+          <t>126.71</t>
         </is>
       </c>
       <c r="G366" t="n">
@@ -10491,18 +10491,18 @@
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>CPI FinalJAN</t>
+          <t>Inflation Rate MoM FinalJAN</t>
         </is>
       </c>
       <c r="D367" t="inlineStr"/>
       <c r="E367" t="inlineStr">
         <is>
-          <t>126.71</t>
+          <t>-0.3%</t>
         </is>
       </c>
       <c r="F367" t="inlineStr">
         <is>
-          <t>126.71</t>
+          <t>-0.3%</t>
         </is>
       </c>
       <c r="G367" t="n">
@@ -10676,7 +10676,7 @@
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>Mid-month Inflation Rate MoMFEB</t>
+          <t>Mid-month Inflation Rate YoYFEB</t>
         </is>
       </c>
       <c r="D374" t="inlineStr"/>
@@ -10745,7 +10745,7 @@
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>Mid-month Inflation Rate YoYFEB</t>
+          <t>Mid-month Inflation Rate MoMFEB</t>
         </is>
       </c>
       <c r="D377" t="inlineStr"/>
@@ -11139,6 +11139,118 @@
         <v>3</v>
       </c>
     </row>
+    <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>2025-02-25 02:00:00-05:00</t>
+        </is>
+      </c>
+      <c r="B394" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="C394" t="inlineStr">
+        <is>
+          <t>GDP Growth Rate QoQ FinalQ4</t>
+        </is>
+      </c>
+      <c r="D394" t="inlineStr"/>
+      <c r="E394" t="inlineStr">
+        <is>
+          <t>-0.2%</t>
+        </is>
+      </c>
+      <c r="F394" t="inlineStr">
+        <is>
+          <t>-0.2%</t>
+        </is>
+      </c>
+      <c r="G394" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>2025-02-25 02:00:00-05:00</t>
+        </is>
+      </c>
+      <c r="B395" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="C395" t="inlineStr">
+        <is>
+          <t>GDP Growth Rate YoY FinalQ4</t>
+        </is>
+      </c>
+      <c r="D395" t="inlineStr"/>
+      <c r="E395" t="inlineStr">
+        <is>
+          <t>-0.2%</t>
+        </is>
+      </c>
+      <c r="F395" t="inlineStr">
+        <is>
+          <t>-0.2%</t>
+        </is>
+      </c>
+      <c r="G395" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>2025-02-25 02:00:00-05:00</t>
+        </is>
+      </c>
+      <c r="B396" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="C396" t="inlineStr">
+        <is>
+          <t>New Car Registrations YoYJAN</t>
+        </is>
+      </c>
+      <c r="D396" t="inlineStr"/>
+      <c r="E396" t="inlineStr"/>
+      <c r="F396" t="inlineStr"/>
+      <c r="G396" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>2025-02-25 02:00:00-05:00</t>
+        </is>
+      </c>
+      <c r="B397" t="inlineStr">
+        <is>
+          <t>ZA</t>
+        </is>
+      </c>
+      <c r="C397" t="inlineStr">
+        <is>
+          <t>Leading Business Cycle Indicator MoMDEC</t>
+        </is>
+      </c>
+      <c r="D397" t="inlineStr"/>
+      <c r="E397" t="inlineStr"/>
+      <c r="F397" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="G397" t="n">
+        <v>3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Input_data/EST_All Countries_trad_eco_cal_2025-02-14_to_2025-02-25.xlsx
+++ b/Input_data/EST_All Countries_trad_eco_cal_2025-02-14_to_2025-02-25.xlsx
@@ -699,22 +699,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Core Inflation Rate YoY FinalJAN</t>
+          <t>Inflation Rate MoM FinalJAN</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2.4%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2.4%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2.4%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -734,22 +734,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Inflation Rate YoY FinalJAN</t>
+          <t>Harmonised Inflation Rate MoM FinalJAN</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>3%</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>3.0%</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -769,22 +769,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Harmonised Inflation Rate MoM FinalJAN</t>
+          <t>Harmonised Inflation Rate YoY FinalJAN</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -804,22 +804,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Inflation Rate MoM FinalJAN</t>
+          <t>Core Inflation Rate YoY FinalJAN</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>2.4%</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>2.4%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>2.4%</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -839,7 +839,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Harmonised Inflation Rate YoY FinalJAN</t>
+          <t>Inflation Rate YoY FinalJAN</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -849,12 +849,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>3%</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>3.0%</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1220,12 +1220,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Bank Loan Growth YoYJAN/31</t>
+          <t>Foreign Exchange ReservesFEB/07</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>11.4%</t>
+          <t>$638.26B</t>
         </is>
       </c>
       <c r="E24" t="inlineStr"/>
@@ -1247,12 +1247,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Deposit Growth YoYJAN/31</t>
+          <t>Bank Loan Growth YoYJAN/31</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>10.3%</t>
+          <t>11.4%</t>
         </is>
       </c>
       <c r="E25" t="inlineStr"/>
@@ -1274,12 +1274,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Foreign Exchange ReservesFEB/07</t>
+          <t>Deposit Growth YoYJAN/31</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>$638.26B</t>
+          <t>10.3%</t>
         </is>
       </c>
       <c r="E26" t="inlineStr"/>
@@ -1319,27 +1319,23 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>US</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Wholesale Sales MoM FinalDEC</t>
+          <t>Import Prices YoYJAN</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>-0.2%</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
+          <t>1.9%</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -1359,26 +1355,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Import Prices MoMJAN</t>
+          <t>Export Prices YoYJAN</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
+          <t>2.7%</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="30">
@@ -1389,27 +1381,23 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>US</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Manufacturing Sales MoM FinalDEC</t>
+          <t>Retail Sales Ex Gas/Autos MoMJAN</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>0.7%</t>
-        </is>
-      </c>
+          <t>-0.5%</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -1424,23 +1412,23 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>US</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>New Motor Vehicle SalesDEC</t>
+          <t>Retail Sales YoYJAN</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>135.5K</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr">
         <is>
-          <t>153K</t>
+          <t>3.7%</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -1460,12 +1448,12 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Export Prices MoMJAN</t>
+          <t>Retail Sales Control Group MoMJAN</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1.3%</t>
+          <t>-0.8%</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1475,7 +1463,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -1495,26 +1483,26 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Retail Sales MoMJAN</t>
+          <t>Retail Sales Ex Autos MoMJAN</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>-0.9%</t>
+          <t>-0.4%</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G33" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="34">
@@ -1530,12 +1518,12 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Retail Sales Control Group MoMJAN</t>
+          <t>Export Prices MoMJAN</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>-0.8%</t>
+          <t>1.3%</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1545,7 +1533,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -1560,31 +1548,27 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Autos MoMJAN</t>
+          <t>New Motor Vehicle SalesDEC</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>-0.4%</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>135.5K</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>153K</t>
         </is>
       </c>
       <c r="G35" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="36">
@@ -1595,23 +1579,27 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Import Prices YoYJAN</t>
+          <t>Manufacturing Sales MoM FinalDEC</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1.9%</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr"/>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>0.7%</t>
+        </is>
+      </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -1631,22 +1619,26 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Retail Sales YoYJAN</t>
+          <t>Import Prices MoMJAN</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>4.2%</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr"/>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>3.7%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G37" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="38">
@@ -1657,20 +1649,24 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Gas/Autos MoMJAN</t>
+          <t>Wholesale Sales MoM FinalDEC</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>-0.5%</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr"/>
+          <t>-0.2%</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
       <c r="F38" t="inlineStr">
         <is>
           <t>0.2%</t>
@@ -1693,22 +1689,26 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Export Prices YoYJAN</t>
+          <t>Retail Sales MoMJAN</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2.7%</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr"/>
+          <t>-0.9%</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>-0.1%</t>
+        </is>
+      </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G39" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="40">
@@ -1724,22 +1724,18 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Manufacturing Production MoMJAN</t>
+          <t>Industrial Production YoYJAN</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>-0.1%</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>0.1%</t>
-        </is>
-      </c>
+          <t>2%</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -1759,26 +1755,26 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Industrial Production MoMJAN</t>
+          <t>Manufacturing Production MoMJAN</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G41" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="42">
@@ -1794,26 +1790,26 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Capacity UtilizationJAN</t>
+          <t>Industrial Production MoMJAN</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>77.8%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>77.7%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>77.4%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G42" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="43">
@@ -1829,18 +1825,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Industrial Production YoYJAN</t>
+          <t>Capacity UtilizationJAN</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2%</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr"/>
+          <t>77.8%</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>77.7%</t>
+        </is>
+      </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>77.4%</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -1891,26 +1891,26 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Business Inventories MoMDEC</t>
+          <t>Retail Inventories Ex Autos MoMDEC</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>-0.2%</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G45" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="46">
@@ -1926,26 +1926,26 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Retail Inventories Ex Autos MoMDEC</t>
+          <t>Business Inventories MoMDEC</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
+          <t>-0.2%</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
           <t>-0.1%</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
       <c r="G46" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="47">
@@ -1984,22 +1984,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Inflation Rate MoMJAN</t>
+          <t>Inflation Rate YoYJAN</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>1.2%</t>
+          <t>9.9%</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>1.3%</t>
+          <t>10%</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>1.2%</t>
+          <t>9.9%</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -2019,22 +2019,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Inflation Rate YoYJAN</t>
+          <t>Inflation Rate MoMJAN</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>9.9%</t>
+          <t>1.2%</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>1.3%</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>9.9%</t>
+          <t>1.2%</t>
         </is>
       </c>
       <c r="G49" t="n">

--- a/Input_data/EST_All Countries_trad_eco_cal_2025-02-14_to_2025-02-25.xlsx
+++ b/Input_data/EST_All Countries_trad_eco_cal_2025-02-14_to_2025-02-25.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G403"/>
+  <dimension ref="A1:G406"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -699,22 +699,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Inflation Rate MoM FinalJAN</t>
+          <t>Core Inflation Rate YoY FinalJAN</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>2.4%</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>2.4%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>2.4%</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -734,22 +734,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Inflation Rate YoY FinalJAN</t>
+          <t>Harmonised Inflation Rate MoM FinalJAN</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>3%</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>3.0%</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -769,22 +769,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Harmonised Inflation Rate MoM FinalJAN</t>
+          <t>Harmonised Inflation Rate YoY FinalJAN</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -804,22 +804,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Core Inflation Rate YoY FinalJAN</t>
+          <t>Inflation Rate MoM FinalJAN</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2.4%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2.4%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2.4%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -839,7 +839,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Harmonised Inflation Rate YoY FinalJAN</t>
+          <t>Inflation Rate YoY FinalJAN</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -849,12 +849,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>3%</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>3.0%</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1220,12 +1220,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Bank Loan Growth YoYJAN/31</t>
+          <t>Deposit Growth YoYJAN/31</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>11.4%</t>
+          <t>10.3%</t>
         </is>
       </c>
       <c r="E24" t="inlineStr"/>
@@ -1247,12 +1247,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Deposit Growth YoYJAN/31</t>
+          <t>Foreign Exchange ReservesFEB/07</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>10.3%</t>
+          <t>$638.26B</t>
         </is>
       </c>
       <c r="E25" t="inlineStr"/>
@@ -1274,12 +1274,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Foreign Exchange ReservesFEB/07</t>
+          <t>Bank Loan Growth YoYJAN/31</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>$638.26B</t>
+          <t>11.4%</t>
         </is>
       </c>
       <c r="E26" t="inlineStr"/>
@@ -1319,23 +1319,27 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Gas/Autos MoMJAN</t>
+          <t>Manufacturing Sales MoM FinalDEC</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>-0.5%</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr"/>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>0.7%</t>
+        </is>
+      </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -1350,31 +1354,27 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Autos MoMJAN</t>
+          <t>New Motor Vehicle SalesDEC</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>-0.4%</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>135.5K</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>153K</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="30">
@@ -1390,22 +1390,26 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Import Prices YoYJAN</t>
+          <t>Retail Sales MoMJAN</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1.9%</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr"/>
+          <t>-0.9%</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>-0.1%</t>
+        </is>
+      </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -1421,22 +1425,26 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Export Prices YoYJAN</t>
+          <t>Import Prices MoMJAN</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2.7%</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr"/>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="32">
@@ -1452,12 +1460,12 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Retail Sales Control Group MoMJAN</t>
+          <t>Export Prices MoMJAN</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>-0.8%</t>
+          <t>1.3%</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1467,7 +1475,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -1482,23 +1490,27 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Retail Sales YoYJAN</t>
+          <t>Wholesale Sales MoM FinalDEC</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>4.2%</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr"/>
+          <t>-0.2%</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>3.7%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -1518,12 +1530,12 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Export Prices MoMJAN</t>
+          <t>Retail Sales Control Group MoMJAN</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>1.3%</t>
+          <t>-0.8%</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1533,7 +1545,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -1553,26 +1565,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Import Prices MoMJAN</t>
+          <t>Export Prices YoYJAN</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
+          <t>2.7%</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="G35" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="36">
@@ -1583,27 +1591,23 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>US</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Wholesale Sales MoM FinalDEC</t>
+          <t>Import Prices YoYJAN</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>-0.2%</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
+          <t>1.9%</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -1623,26 +1627,26 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Retail Sales MoMJAN</t>
+          <t>Retail Sales Ex Autos MoMJAN</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>-0.9%</t>
+          <t>-0.4%</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G37" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="38">
@@ -1653,27 +1657,23 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>US</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Manufacturing Sales MoM FinalDEC</t>
+          <t>Retail Sales Ex Gas/Autos MoMJAN</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>0.7%</t>
-        </is>
-      </c>
+          <t>-0.5%</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -1688,23 +1688,23 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>US</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>New Motor Vehicle SalesDEC</t>
+          <t>Retail Sales YoYJAN</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>135.5K</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr">
         <is>
-          <t>153K</t>
+          <t>3.7%</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -1891,26 +1891,26 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Retail Inventories Ex Autos MoMDEC</t>
+          <t>Business Inventories MoMDEC</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
+          <t>-0.2%</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
           <t>-0.1%</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
       <c r="G45" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="46">
@@ -1926,26 +1926,26 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Business Inventories MoMDEC</t>
+          <t>Retail Inventories Ex Autos MoMDEC</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>-0.2%</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G46" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="47">
@@ -1984,22 +1984,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Inflation Rate YoYJAN</t>
+          <t>Inflation Rate MoMJAN</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>9.9%</t>
+          <t>1.2%</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>1.3%</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>9.9%</t>
+          <t>1.2%</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -2019,22 +2019,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Inflation Rate MoMJAN</t>
+          <t>Inflation Rate YoYJAN</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>1.2%</t>
+          <t>9.9%</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>1.3%</t>
+          <t>10%</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>1.2%</t>
+          <t>9.9%</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -2054,12 +2054,12 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Baker Hughes Total Rigs CountFEB/14</t>
+          <t>Baker Hughes Oil Rig CountFEB/14</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>588</t>
+          <t>481</t>
         </is>
       </c>
       <c r="E50" t="inlineStr"/>
@@ -2081,12 +2081,12 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Baker Hughes Oil Rig CountFEB/14</t>
+          <t>Baker Hughes Total Rigs CountFEB/14</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>481</t>
+          <t>588</t>
         </is>
       </c>
       <c r="E51" t="inlineStr"/>
@@ -2158,22 +2158,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>GDP Growth Rate QoQ PrelQ4</t>
+          <t>GDP External Demand QoQ PrelQ4</t>
         </is>
       </c>
       <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr">
         <is>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
           <t>0.3%</t>
         </is>
       </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>0.5%</t>
-        </is>
-      </c>
       <c r="G54" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="55">
@@ -2189,7 +2189,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>GDP Growth Annualized PrelQ4</t>
+          <t>GDP Capital Expenditure QoQ PrelQ4</t>
         </is>
       </c>
       <c r="D55" t="inlineStr"/>
@@ -2200,11 +2200,11 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2.1%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="G55" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="56">
@@ -2220,18 +2220,18 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>GDP Capital Expenditure QoQ PrelQ4</t>
+          <t>GDP Private Consumption QoQ PrelQ4</t>
         </is>
       </c>
       <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr">
         <is>
-          <t>1%</t>
+          <t>-0.3%</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -2251,22 +2251,22 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>GDP External Demand QoQ PrelQ4</t>
+          <t>GDP Growth Rate QoQ PrelQ4</t>
         </is>
       </c>
       <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="G57" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="58">
@@ -2282,22 +2282,22 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>GDP Private Consumption QoQ PrelQ4</t>
+          <t>GDP Growth Annualized PrelQ4</t>
         </is>
       </c>
       <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr">
         <is>
-          <t>-0.3%</t>
+          <t>1%</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>2.1%</t>
         </is>
       </c>
       <c r="G58" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="59">
@@ -2402,18 +2402,22 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Imports YoYJAN</t>
+          <t>Balance of TradeJAN</t>
         </is>
       </c>
       <c r="D62" t="inlineStr"/>
       <c r="E62" t="inlineStr">
         <is>
-          <t>9.95%</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr"/>
+          <t>$1.91B</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>$2.2B</t>
+        </is>
+      </c>
       <c r="G62" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="63">
@@ -2429,22 +2433,18 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Balance of TradeJAN</t>
+          <t>Exports YoYJAN</t>
         </is>
       </c>
       <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr">
         <is>
-          <t>$1.91B</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>$2.2B</t>
-        </is>
-      </c>
+          <t>6.99%</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr"/>
       <c r="G63" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="64">
@@ -2460,13 +2460,13 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Exports YoYJAN</t>
+          <t>Imports YoYJAN</t>
         </is>
       </c>
       <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr">
         <is>
-          <t>6.99%</t>
+          <t>9.95%</t>
         </is>
       </c>
       <c r="F64" t="inlineStr"/>
@@ -2487,14 +2487,18 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Wholesale Prices YoYJAN</t>
+          <t>Inflation Rate YoYJAN</t>
         </is>
       </c>
       <c r="D65" t="inlineStr"/>
-      <c r="E65" t="inlineStr"/>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>1.9%</t>
+        </is>
+      </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>1.3%</t>
+          <t>2.0%</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -2509,17 +2513,21 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>EA</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Eurogroup Meeting</t>
+          <t>Wholesale Prices YoYJAN</t>
         </is>
       </c>
       <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr"/>
-      <c r="F66" t="inlineStr"/>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>1.3%</t>
+        </is>
+      </c>
       <c r="G66" t="n">
         <v>3</v>
       </c>
@@ -2532,23 +2540,19 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>SA</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Inflation Rate YoYJAN</t>
+          <t>Vehicle Sales YoYJAN</t>
         </is>
       </c>
       <c r="D67" t="inlineStr"/>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>1.9%</t>
-        </is>
-      </c>
+      <c r="E67" t="inlineStr"/>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2.0%</t>
+          <t>12.0%</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -2563,19 +2567,23 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Vehicle Sales YoYJAN</t>
+          <t>Inflation Rate MoMJAN</t>
         </is>
       </c>
       <c r="D68" t="inlineStr"/>
-      <c r="E68" t="inlineStr"/>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>12.0%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -2590,12 +2598,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>SA</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Inflation Rate MoMJAN</t>
+          <t>Tertiary Industry Index MoMDEC</t>
         </is>
       </c>
       <c r="D69" t="inlineStr"/>
@@ -2606,7 +2614,7 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -2621,21 +2629,17 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>EA</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Industrial Production YoY FinalDEC</t>
+          <t>Eurogroup Meeting</t>
         </is>
       </c>
       <c r="D70" t="inlineStr"/>
       <c r="E70" t="inlineStr"/>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>-1.6%</t>
-        </is>
-      </c>
+      <c r="F70" t="inlineStr"/>
       <c r="G70" t="n">
         <v>3</v>
       </c>
@@ -2653,18 +2657,18 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Tertiary Industry Index MoMDEC</t>
+          <t>Industrial Production MoM FinalDEC</t>
         </is>
       </c>
       <c r="D71" t="inlineStr"/>
       <c r="E71" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -2684,18 +2688,14 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Industrial Production MoM FinalDEC</t>
+          <t>Capacity Utilization MoMDEC</t>
         </is>
       </c>
       <c r="D72" t="inlineStr"/>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+      <c r="E72" t="inlineStr"/>
       <c r="F72" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -2715,14 +2715,14 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Capacity Utilization MoMDEC</t>
+          <t>Industrial Production YoY FinalDEC</t>
         </is>
       </c>
       <c r="D73" t="inlineStr"/>
       <c r="E73" t="inlineStr"/>
       <c r="F73" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>-1.6%</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -3219,7 +3219,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>ImportsJAN</t>
+          <t>ExportsJAN</t>
         </is>
       </c>
       <c r="D93" t="inlineStr"/>
@@ -3242,12 +3242,16 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>ExportsJAN</t>
+          <t>Balance of TradeJAN</t>
         </is>
       </c>
       <c r="D94" t="inlineStr"/>
       <c r="E94" t="inlineStr"/>
-      <c r="F94" t="inlineStr"/>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>$-24.0B</t>
+        </is>
+      </c>
       <c r="G94" t="n">
         <v>2</v>
       </c>
@@ -3260,12 +3264,12 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>EA</t>
+          <t>BR</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>ECOFIN Meeting</t>
+          <t>BCB Focus Market Readout</t>
         </is>
       </c>
       <c r="D95" t="inlineStr"/>
@@ -3283,12 +3287,12 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>EA</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>BCB Focus Market Readout</t>
+          <t>ECOFIN Meeting</t>
         </is>
       </c>
       <c r="D96" t="inlineStr"/>
@@ -3311,16 +3315,12 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Balance of TradeJAN</t>
+          <t>ImportsJAN</t>
         </is>
       </c>
       <c r="D97" t="inlineStr"/>
       <c r="E97" t="inlineStr"/>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>$-24.0B</t>
-        </is>
-      </c>
+      <c r="F97" t="inlineStr"/>
       <c r="G97" t="n">
         <v>2</v>
       </c>
@@ -3333,17 +3333,21 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>EU</t>
+          <t>TR</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>European Commission Winter Forecasts</t>
+          <t>Budget BalanceJAN</t>
         </is>
       </c>
       <c r="D98" t="inlineStr"/>
       <c r="E98" t="inlineStr"/>
-      <c r="F98" t="inlineStr"/>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>TRY-150.0B</t>
+        </is>
+      </c>
       <c r="G98" t="n">
         <v>2</v>
       </c>
@@ -3356,21 +3360,17 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>TR</t>
+          <t>EU</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Auto Sales YoYJAN</t>
+          <t>European Commission Winter Forecasts</t>
         </is>
       </c>
       <c r="D99" t="inlineStr"/>
       <c r="E99" t="inlineStr"/>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>6.0%</t>
-        </is>
-      </c>
+      <c r="F99" t="inlineStr"/>
       <c r="G99" t="n">
         <v>2</v>
       </c>
@@ -3438,14 +3438,14 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Budget BalanceJAN</t>
+          <t>Auto Sales YoYJAN</t>
         </is>
       </c>
       <c r="D102" t="inlineStr"/>
       <c r="E102" t="inlineStr"/>
       <c r="F102" t="inlineStr">
         <is>
-          <t>TRY-150.0B</t>
+          <t>6.0%</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -3569,18 +3569,18 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Employment ChangeDEC</t>
+          <t>Average Earnings excl. Bonus (3Mo/Yr)DEC</t>
         </is>
       </c>
       <c r="D107" t="inlineStr"/>
       <c r="E107" t="inlineStr"/>
       <c r="F107" t="inlineStr">
         <is>
-          <t>-130K</t>
+          <t>5.9%</t>
         </is>
       </c>
       <c r="G107" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="108">
@@ -3596,18 +3596,22 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Average Earnings excl. Bonus (3Mo/Yr)DEC</t>
+          <t>Average Earnings incl. Bonus (3Mo/Yr)DEC</t>
         </is>
       </c>
       <c r="D108" t="inlineStr"/>
-      <c r="E108" t="inlineStr"/>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>5.9%</t>
+        </is>
+      </c>
       <c r="F108" t="inlineStr">
         <is>
           <t>5.9%</t>
         </is>
       </c>
       <c r="G108" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="109">
@@ -3623,22 +3627,18 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Unemployment RateDEC</t>
+          <t>Employment ChangeDEC</t>
         </is>
       </c>
       <c r="D109" t="inlineStr"/>
-      <c r="E109" t="inlineStr">
-        <is>
-          <t>4.5%</t>
-        </is>
-      </c>
+      <c r="E109" t="inlineStr"/>
       <c r="F109" t="inlineStr">
         <is>
-          <t>4.4%</t>
+          <t>-130K</t>
         </is>
       </c>
       <c r="G109" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="110">
@@ -3654,22 +3654,22 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Average Earnings incl. Bonus (3Mo/Yr)DEC</t>
+          <t>Unemployment RateDEC</t>
         </is>
       </c>
       <c r="D110" t="inlineStr"/>
       <c r="E110" t="inlineStr">
         <is>
-          <t>5.9%</t>
+          <t>4.5%</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>5.9%</t>
+          <t>4.4%</t>
         </is>
       </c>
       <c r="G110" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="111">
@@ -3809,14 +3809,18 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Labour Productivity QoQ PrelQ4</t>
+          <t>Labour Productivity QoQ FinalQ3</t>
         </is>
       </c>
       <c r="D115" t="inlineStr"/>
-      <c r="E115" t="inlineStr"/>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>-0.8%</t>
+        </is>
+      </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>-0.8%</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -3913,18 +3917,14 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Labour Productivity QoQ FinalQ3</t>
+          <t>Labour Productivity QoQ PrelQ4</t>
         </is>
       </c>
       <c r="D119" t="inlineStr"/>
-      <c r="E119" t="inlineStr">
-        <is>
-          <t>-0.8%</t>
-        </is>
-      </c>
+      <c r="E119" t="inlineStr"/>
       <c r="F119" t="inlineStr">
         <is>
-          <t>-0.8%</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -3944,22 +3944,22 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>ZEW Current ConditionsFEB</t>
+          <t>ZEW Economic Sentiment IndexFEB</t>
         </is>
       </c>
       <c r="D120" t="inlineStr"/>
       <c r="E120" t="inlineStr">
         <is>
-          <t>-89</t>
+          <t>15</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>-89</t>
+          <t>12</t>
         </is>
       </c>
       <c r="G120" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="121">
@@ -3970,17 +3970,25 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>40-Year Treasury Gilt Auction</t>
+          <t>ZEW Current ConditionsFEB</t>
         </is>
       </c>
       <c r="D121" t="inlineStr"/>
-      <c r="E121" t="inlineStr"/>
-      <c r="F121" t="inlineStr"/>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>-89</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>-89</t>
+        </is>
+      </c>
       <c r="G121" t="n">
         <v>3</v>
       </c>
@@ -3993,27 +4001,19 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>ZEW Economic Sentiment IndexFEB</t>
+          <t>40-Year Treasury Gilt Auction</t>
         </is>
       </c>
       <c r="D122" t="inlineStr"/>
-      <c r="E122" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="F122" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
+      <c r="E122" t="inlineStr"/>
+      <c r="F122" t="inlineStr"/>
       <c r="G122" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="123">
@@ -4074,27 +4074,27 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>NY Empire State Manufacturing IndexFEB</t>
+          <t>CPI Trimmed-Mean YoYJAN</t>
         </is>
       </c>
       <c r="D125" t="inlineStr"/>
       <c r="E125" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>2.6%</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="G125" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="126">
@@ -4105,23 +4105,27 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>US</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Inflation Rate YoYJAN</t>
+          <t>NY Empire State Manufacturing IndexFEB</t>
         </is>
       </c>
       <c r="D126" t="inlineStr"/>
-      <c r="E126" t="inlineStr"/>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>-1</t>
+        </is>
+      </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>1.8%</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G126" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="127">
@@ -4137,18 +4141,22 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Core Inflation Rate YoYJAN</t>
+          <t>CPI Median YoYJAN</t>
         </is>
       </c>
       <c r="D127" t="inlineStr"/>
-      <c r="E127" t="inlineStr"/>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>2.4%</t>
+        </is>
+      </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>1.7%</t>
+          <t>2.4%</t>
         </is>
       </c>
       <c r="G127" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="128">
@@ -4164,22 +4172,18 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Inflation Rate MoMJAN</t>
+          <t>Inflation Rate YoYJAN</t>
         </is>
       </c>
       <c r="D128" t="inlineStr"/>
-      <c r="E128" t="inlineStr">
-        <is>
-          <t>0.1%</t>
-        </is>
-      </c>
+      <c r="E128" t="inlineStr"/>
       <c r="F128" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>1.8%</t>
         </is>
       </c>
       <c r="G128" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="129">
@@ -4195,18 +4199,18 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Core Inflation Rate MoMJAN</t>
+          <t>Core Inflation Rate YoYJAN</t>
         </is>
       </c>
       <c r="D129" t="inlineStr"/>
       <c r="E129" t="inlineStr"/>
       <c r="F129" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>1.7%</t>
         </is>
       </c>
       <c r="G129" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="130">
@@ -4222,22 +4226,22 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>CPI Median YoYJAN</t>
+          <t>Inflation Rate MoMJAN</t>
         </is>
       </c>
       <c r="D130" t="inlineStr"/>
       <c r="E130" t="inlineStr">
         <is>
-          <t>2.4%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>2.4%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G130" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="131">
@@ -4253,18 +4257,14 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>CPI Trimmed-Mean YoYJAN</t>
+          <t>Core Inflation Rate MoMJAN</t>
         </is>
       </c>
       <c r="D131" t="inlineStr"/>
-      <c r="E131" t="inlineStr">
-        <is>
-          <t>2.6%</t>
-        </is>
-      </c>
+      <c r="E131" t="inlineStr"/>
       <c r="F131" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -4453,14 +4453,14 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Fed Barr Speech</t>
+          <t>52-Week Bill Auction</t>
         </is>
       </c>
       <c r="D139" t="inlineStr"/>
       <c r="E139" t="inlineStr"/>
       <c r="F139" t="inlineStr"/>
       <c r="G139" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="140">
@@ -4476,14 +4476,14 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>52-Week Bill Auction</t>
+          <t>Fed Barr Speech</t>
         </is>
       </c>
       <c r="D140" t="inlineStr"/>
       <c r="E140" t="inlineStr"/>
       <c r="F140" t="inlineStr"/>
       <c r="G140" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="141">
@@ -4526,14 +4526,14 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Overall Net Capital FlowsDEC</t>
+          <t>Net Long-term TIC FlowsDEC</t>
         </is>
       </c>
       <c r="D142" t="inlineStr"/>
       <c r="E142" t="inlineStr"/>
       <c r="F142" t="inlineStr"/>
       <c r="G142" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="143">
@@ -4549,7 +4549,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Foreign Bond InvestmentDEC</t>
+          <t>Overall Net Capital FlowsDEC</t>
         </is>
       </c>
       <c r="D143" t="inlineStr"/>
@@ -4572,14 +4572,14 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Net Long-term TIC FlowsDEC</t>
+          <t>Foreign Bond InvestmentDEC</t>
         </is>
       </c>
       <c r="D144" t="inlineStr"/>
       <c r="E144" t="inlineStr"/>
       <c r="F144" t="inlineStr"/>
       <c r="G144" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="145">
@@ -4595,22 +4595,22 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Machinery Orders MoMDEC</t>
+          <t>Imports YoYJAN</t>
         </is>
       </c>
       <c r="D145" t="inlineStr"/>
       <c r="E145" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>9.7%</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>2.0%</t>
         </is>
       </c>
       <c r="G145" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="146">
@@ -4626,22 +4626,22 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Imports YoYJAN</t>
+          <t>Machinery Orders MoMDEC</t>
         </is>
       </c>
       <c r="D146" t="inlineStr"/>
       <c r="E146" t="inlineStr">
         <is>
-          <t>9.7%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>2.0%</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="G146" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="147">
@@ -4935,14 +4935,14 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Retail Price Index MoMJAN</t>
+          <t>PPI Output YoYJAN</t>
         </is>
       </c>
       <c r="D157" t="inlineStr"/>
       <c r="E157" t="inlineStr"/>
       <c r="F157" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -4962,14 +4962,18 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>PPI Output YoYJAN</t>
+          <t>PPI Output MoMJAN</t>
         </is>
       </c>
       <c r="D158" t="inlineStr"/>
-      <c r="E158" t="inlineStr"/>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -4989,18 +4993,14 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>PPI Output MoMJAN</t>
+          <t>PPI Input YoYJAN</t>
         </is>
       </c>
       <c r="D159" t="inlineStr"/>
-      <c r="E159" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
+      <c r="E159" t="inlineStr"/>
       <c r="F159" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>-0.8%</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -5020,14 +5020,18 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>PPI Input YoYJAN</t>
+          <t>PPI Input MoMJAN</t>
         </is>
       </c>
       <c r="D160" t="inlineStr"/>
-      <c r="E160" t="inlineStr"/>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>0.7%</t>
+        </is>
+      </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>-0.8%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="G160" t="n">
@@ -5047,18 +5051,14 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>PPI Input MoMJAN</t>
+          <t>PPI Core Output YoYJAN</t>
         </is>
       </c>
       <c r="D161" t="inlineStr"/>
-      <c r="E161" t="inlineStr">
-        <is>
-          <t>0.7%</t>
-        </is>
-      </c>
+      <c r="E161" t="inlineStr"/>
       <c r="F161" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>1.3%</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -5078,14 +5078,14 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>PPI Core Output YoYJAN</t>
+          <t>PPI Core Output MoMJAN</t>
         </is>
       </c>
       <c r="D162" t="inlineStr"/>
       <c r="E162" t="inlineStr"/>
       <c r="F162" t="inlineStr">
         <is>
-          <t>1.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -5105,22 +5105,22 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Inflation Rate YoYJAN</t>
+          <t>Retail Price Index YoYJAN</t>
         </is>
       </c>
       <c r="D163" t="inlineStr"/>
       <c r="E163" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>3.7%</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>2.7%</t>
+          <t>3.6%</t>
         </is>
       </c>
       <c r="G163" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="164">
@@ -5136,18 +5136,18 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Core Inflation Rate MoMJAN</t>
+          <t>Inflation Rate MoMJAN</t>
         </is>
       </c>
       <c r="D164" t="inlineStr"/>
       <c r="E164" t="inlineStr"/>
       <c r="F164" t="inlineStr">
         <is>
-          <t>-0.7%</t>
+          <t>-0.3%</t>
         </is>
       </c>
       <c r="G164" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="165">
@@ -5163,14 +5163,18 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Inflation Rate MoMJAN</t>
+          <t>Core Inflation Rate YoYJAN</t>
         </is>
       </c>
       <c r="D165" t="inlineStr"/>
-      <c r="E165" t="inlineStr"/>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>3.7%</t>
+        </is>
+      </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>-0.3%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="G165" t="n">
@@ -5190,22 +5194,22 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Core Inflation Rate YoYJAN</t>
+          <t>Inflation Rate YoYJAN</t>
         </is>
       </c>
       <c r="D166" t="inlineStr"/>
       <c r="E166" t="inlineStr">
         <is>
-          <t>3.7%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>2.7%</t>
         </is>
       </c>
       <c r="G166" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="167">
@@ -5221,18 +5225,14 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Retail Price Index YoYJAN</t>
+          <t>Retail Price Index MoMJAN</t>
         </is>
       </c>
       <c r="D167" t="inlineStr"/>
-      <c r="E167" t="inlineStr">
-        <is>
-          <t>3.7%</t>
-        </is>
-      </c>
+      <c r="E167" t="inlineStr"/>
       <c r="F167" t="inlineStr">
         <is>
-          <t>3.6%</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="G167" t="n">
@@ -5252,14 +5252,14 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>PPI Core Output MoMJAN</t>
+          <t>Core Inflation Rate MoMJAN</t>
         </is>
       </c>
       <c r="D168" t="inlineStr"/>
       <c r="E168" t="inlineStr"/>
       <c r="F168" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>-0.7%</t>
         </is>
       </c>
       <c r="G168" t="n">
@@ -5583,21 +5583,17 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Current AccountDEC</t>
+          <t>4-Year Treasury Gilt Auction</t>
         </is>
       </c>
       <c r="D180" t="inlineStr"/>
       <c r="E180" t="inlineStr"/>
-      <c r="F180" t="inlineStr">
-        <is>
-          <t>€ 3780M</t>
-        </is>
-      </c>
+      <c r="F180" t="inlineStr"/>
       <c r="G180" t="n">
         <v>3</v>
       </c>
@@ -5610,17 +5606,21 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>4-Year Treasury Gilt Auction</t>
+          <t>Current AccountDEC</t>
         </is>
       </c>
       <c r="D181" t="inlineStr"/>
       <c r="E181" t="inlineStr"/>
-      <c r="F181" t="inlineStr"/>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>€ 3780M</t>
+        </is>
+      </c>
       <c r="G181" t="n">
         <v>3</v>
       </c>
@@ -5715,7 +5715,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>6-Month Bill Auction</t>
+          <t>3-Month Bill Auction</t>
         </is>
       </c>
       <c r="D185" t="inlineStr"/>
@@ -5738,7 +5738,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>3-Month Bill Auction</t>
+          <t>6-Month Bill Auction</t>
         </is>
       </c>
       <c r="D186" t="inlineStr"/>
@@ -5899,18 +5899,22 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Housing Starts MoMJAN</t>
+          <t>Building Permits PrelJAN</t>
         </is>
       </c>
       <c r="D193" t="inlineStr"/>
-      <c r="E193" t="inlineStr"/>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>1.45M</t>
+        </is>
+      </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>-9.0%</t>
+          <t>1.47M</t>
         </is>
       </c>
       <c r="G193" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="194">
@@ -5926,22 +5930,18 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Building Permits PrelJAN</t>
+          <t>Building Permits MoM PrelJAN</t>
         </is>
       </c>
       <c r="D194" t="inlineStr"/>
-      <c r="E194" t="inlineStr">
-        <is>
-          <t>1.45M</t>
-        </is>
-      </c>
+      <c r="E194" t="inlineStr"/>
       <c r="F194" t="inlineStr">
         <is>
-          <t>1.47M</t>
+          <t>-0.8%</t>
         </is>
       </c>
       <c r="G194" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="195">
@@ -5957,22 +5957,18 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Housing StartsJAN</t>
+          <t>Housing Starts MoMJAN</t>
         </is>
       </c>
       <c r="D195" t="inlineStr"/>
-      <c r="E195" t="inlineStr">
-        <is>
-          <t>1.39M</t>
-        </is>
-      </c>
+      <c r="E195" t="inlineStr"/>
       <c r="F195" t="inlineStr">
         <is>
-          <t>1.35M</t>
+          <t>-9.0%</t>
         </is>
       </c>
       <c r="G195" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="196">
@@ -5988,18 +5984,22 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Building Permits MoM PrelJAN</t>
+          <t>Housing StartsJAN</t>
         </is>
       </c>
       <c r="D196" t="inlineStr"/>
-      <c r="E196" t="inlineStr"/>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>1.39M</t>
+        </is>
+      </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>-0.8%</t>
+          <t>1.35M</t>
         </is>
       </c>
       <c r="G196" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="197">
@@ -6419,18 +6419,22 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Part Time Employment ChgJAN</t>
+          <t>Unemployment RateJAN</t>
         </is>
       </c>
       <c r="D213" t="inlineStr"/>
-      <c r="E213" t="inlineStr"/>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>4.1%</t>
+        </is>
+      </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>-10.0K</t>
+          <t>4.0%</t>
         </is>
       </c>
       <c r="G213" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="214">
@@ -6446,14 +6450,18 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Full Time Employment ChgJAN</t>
+          <t>Employment ChangeJAN</t>
         </is>
       </c>
       <c r="D214" t="inlineStr"/>
-      <c r="E214" t="inlineStr"/>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>20K</t>
+        </is>
+      </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>33.0K</t>
+          <t>23.0K</t>
         </is>
       </c>
       <c r="G214" t="n">
@@ -6473,22 +6481,18 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Unemployment RateJAN</t>
+          <t>Full Time Employment ChgJAN</t>
         </is>
       </c>
       <c r="D215" t="inlineStr"/>
-      <c r="E215" t="inlineStr">
-        <is>
-          <t>4.1%</t>
-        </is>
-      </c>
+      <c r="E215" t="inlineStr"/>
       <c r="F215" t="inlineStr">
         <is>
-          <t>4.0%</t>
+          <t>33.0K</t>
         </is>
       </c>
       <c r="G215" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="216">
@@ -6504,22 +6508,18 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Employment ChangeJAN</t>
+          <t>Part Time Employment ChgJAN</t>
         </is>
       </c>
       <c r="D216" t="inlineStr"/>
-      <c r="E216" t="inlineStr">
-        <is>
-          <t>20K</t>
-        </is>
-      </c>
+      <c r="E216" t="inlineStr"/>
       <c r="F216" t="inlineStr">
         <is>
-          <t>23.0K</t>
+          <t>-10.0K</t>
         </is>
       </c>
       <c r="G216" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="217">
@@ -6535,14 +6535,14 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Loan Prime Rate 1Y</t>
+          <t>Loan Prime Rate 5YFEB</t>
         </is>
       </c>
       <c r="D217" t="inlineStr"/>
       <c r="E217" t="inlineStr"/>
       <c r="F217" t="inlineStr">
         <is>
-          <t>3.1%</t>
+          <t>3.6%</t>
         </is>
       </c>
       <c r="G217" t="n">
@@ -6562,14 +6562,14 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Loan Prime Rate 5YFEB</t>
+          <t>Loan Prime Rate 1Y</t>
         </is>
       </c>
       <c r="D218" t="inlineStr"/>
       <c r="E218" t="inlineStr"/>
       <c r="F218" t="inlineStr">
         <is>
-          <t>3.6%</t>
+          <t>3.1%</t>
         </is>
       </c>
       <c r="G218" t="n">
@@ -6584,21 +6584,17 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>ID</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Leading Indicator MoMJAN</t>
+          <t>M2 Money Supply YoYJAN</t>
         </is>
       </c>
       <c r="D219" t="inlineStr"/>
       <c r="E219" t="inlineStr"/>
-      <c r="F219" t="inlineStr">
-        <is>
-          <t>1.5%</t>
-        </is>
-      </c>
+      <c r="F219" t="inlineStr"/>
       <c r="G219" t="n">
         <v>3</v>
       </c>
@@ -6638,19 +6634,19 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Consumer ConfidenceJAN</t>
+          <t>Leading Indicator MoMJAN</t>
         </is>
       </c>
       <c r="D221" t="inlineStr"/>
       <c r="E221" t="inlineStr"/>
       <c r="F221" t="inlineStr">
         <is>
-          <t>85.5</t>
+          <t>1.5%</t>
         </is>
       </c>
       <c r="G221" t="n">
@@ -6665,17 +6661,21 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>ID</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>M2 Money Supply YoYJAN</t>
+          <t>Consumer ConfidenceJAN</t>
         </is>
       </c>
       <c r="D222" t="inlineStr"/>
       <c r="E222" t="inlineStr"/>
-      <c r="F222" t="inlineStr"/>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>85.5</t>
+        </is>
+      </c>
       <c r="G222" t="n">
         <v>3</v>
       </c>
@@ -6874,7 +6874,7 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>5-Year OAT Auction</t>
+          <t>4-Year OAT Auction</t>
         </is>
       </c>
       <c r="D230" t="inlineStr"/>
@@ -6947,7 +6947,7 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>4-Year OAT Auction</t>
+          <t>5-Year OAT Auction</t>
         </is>
       </c>
       <c r="D233" t="inlineStr"/>
@@ -7028,7 +7028,7 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>7-Year OATi Auction</t>
+          <t>11-Year Index-Linked OAT Auction</t>
         </is>
       </c>
       <c r="D236" t="inlineStr"/>
@@ -7051,7 +7051,7 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>6-Year Index-Linked OAT Auction</t>
+          <t>18-Year Index-Linked OAT Auction</t>
         </is>
       </c>
       <c r="D237" t="inlineStr"/>
@@ -7074,7 +7074,7 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>11-Year Index-Linked OAT Auction</t>
+          <t>6-Year Index-Linked OAT Auction</t>
         </is>
       </c>
       <c r="D238" t="inlineStr"/>
@@ -7097,7 +7097,7 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>18-Year Index-Linked OAT Auction</t>
+          <t>7-Year OATi Auction</t>
         </is>
       </c>
       <c r="D239" t="inlineStr"/>
@@ -7143,14 +7143,14 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Retail Sales YoYDEC</t>
+          <t>Retail Sales MoMDEC</t>
         </is>
       </c>
       <c r="D241" t="inlineStr"/>
       <c r="E241" t="inlineStr"/>
       <c r="F241" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>-0.4%</t>
         </is>
       </c>
       <c r="G241" t="n">
@@ -7170,14 +7170,14 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Retail Sales MoMDEC</t>
+          <t>Retail Sales YoYDEC</t>
         </is>
       </c>
       <c r="D242" t="inlineStr"/>
       <c r="E242" t="inlineStr"/>
       <c r="F242" t="inlineStr">
         <is>
-          <t>-0.4%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="G242" t="n">
@@ -7197,12 +7197,16 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Philly Fed Business ConditionsFEB</t>
+          <t>Jobless Claims 4-week AverageFEB/15</t>
         </is>
       </c>
       <c r="D243" t="inlineStr"/>
       <c r="E243" t="inlineStr"/>
-      <c r="F243" t="inlineStr"/>
+      <c r="F243" t="inlineStr">
+        <is>
+          <t>219.0K</t>
+        </is>
+      </c>
       <c r="G243" t="n">
         <v>3</v>
       </c>
@@ -7220,16 +7224,12 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/15</t>
+          <t>Philly Fed CAPEX IndexFEB</t>
         </is>
       </c>
       <c r="D244" t="inlineStr"/>
       <c r="E244" t="inlineStr"/>
-      <c r="F244" t="inlineStr">
-        <is>
-          <t>219.0K</t>
-        </is>
-      </c>
+      <c r="F244" t="inlineStr"/>
       <c r="G244" t="n">
         <v>3</v>
       </c>
@@ -7247,7 +7247,7 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Philly Fed CAPEX IndexFEB</t>
+          <t>Philly Fed Business ConditionsFEB</t>
         </is>
       </c>
       <c r="D245" t="inlineStr"/>
@@ -7301,12 +7301,16 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Philly Fed New OrdersFEB</t>
+          <t>Continuing Jobless ClaimsFEB/08</t>
         </is>
       </c>
       <c r="D247" t="inlineStr"/>
       <c r="E247" t="inlineStr"/>
-      <c r="F247" t="inlineStr"/>
+      <c r="F247" t="inlineStr">
+        <is>
+          <t>1879.0K</t>
+        </is>
+      </c>
       <c r="G247" t="n">
         <v>3</v>
       </c>
@@ -7324,7 +7328,7 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Philly Fed Prices PaidFEB</t>
+          <t>Philly Fed New OrdersFEB</t>
         </is>
       </c>
       <c r="D248" t="inlineStr"/>
@@ -7347,7 +7351,7 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Philly Fed EmploymentFEB</t>
+          <t>Philly Fed Prices PaidFEB</t>
         </is>
       </c>
       <c r="D249" t="inlineStr"/>
@@ -7370,22 +7374,14 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/15</t>
+          <t>Philly Fed EmploymentFEB</t>
         </is>
       </c>
       <c r="D250" t="inlineStr"/>
-      <c r="E250" t="inlineStr">
-        <is>
-          <t>216K</t>
-        </is>
-      </c>
-      <c r="F250" t="inlineStr">
-        <is>
-          <t>220.0K</t>
-        </is>
-      </c>
+      <c r="E250" t="inlineStr"/>
+      <c r="F250" t="inlineStr"/>
       <c r="G250" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="251">
@@ -7401,18 +7397,22 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/08</t>
+          <t>Initial Jobless ClaimsFEB/15</t>
         </is>
       </c>
       <c r="D251" t="inlineStr"/>
-      <c r="E251" t="inlineStr"/>
+      <c r="E251" t="inlineStr">
+        <is>
+          <t>216K</t>
+        </is>
+      </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>1879.0K</t>
+          <t>220.0K</t>
         </is>
       </c>
       <c r="G251" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="252">
@@ -7428,14 +7428,14 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Raw Materials Prices MoMJAN</t>
+          <t>Raw Materials Prices YoYJAN</t>
         </is>
       </c>
       <c r="D252" t="inlineStr"/>
       <c r="E252" t="inlineStr"/>
       <c r="F252" t="inlineStr">
         <is>
-          <t>-0.2%</t>
+          <t>10.0%</t>
         </is>
       </c>
       <c r="G252" t="n">
@@ -7455,14 +7455,14 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>PPI YoYJAN</t>
+          <t>Raw Materials Prices MoMJAN</t>
         </is>
       </c>
       <c r="D253" t="inlineStr"/>
       <c r="E253" t="inlineStr"/>
       <c r="F253" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>-0.2%</t>
         </is>
       </c>
       <c r="G253" t="n">
@@ -7482,14 +7482,14 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>PPI MoMJAN</t>
+          <t>PPI YoYJAN</t>
         </is>
       </c>
       <c r="D254" t="inlineStr"/>
       <c r="E254" t="inlineStr"/>
       <c r="F254" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="G254" t="n">
@@ -7509,18 +7509,18 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>New Housing Price Index YoYJAN</t>
+          <t>PPI MoMJAN</t>
         </is>
       </c>
       <c r="D255" t="inlineStr"/>
       <c r="E255" t="inlineStr"/>
       <c r="F255" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="G255" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="256">
@@ -7536,14 +7536,14 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>New Housing Price Index MoMJAN</t>
+          <t>New Housing Price Index YoYJAN</t>
         </is>
       </c>
       <c r="D256" t="inlineStr"/>
       <c r="E256" t="inlineStr"/>
       <c r="F256" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G256" t="n">
@@ -7563,18 +7563,18 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Raw Materials Prices YoYJAN</t>
+          <t>New Housing Price Index MoMJAN</t>
         </is>
       </c>
       <c r="D257" t="inlineStr"/>
       <c r="E257" t="inlineStr"/>
       <c r="F257" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G257" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="258">
@@ -7635,27 +7635,27 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>EA</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>CB Leading Index MoMJAN</t>
+          <t>Consumer Confidence FlashFEB</t>
         </is>
       </c>
       <c r="D260" t="inlineStr"/>
       <c r="E260" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-14</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-14.4</t>
         </is>
       </c>
       <c r="G260" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="261">
@@ -7689,27 +7689,27 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>EA</t>
+          <t>US</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Consumer Confidence FlashFEB</t>
+          <t>CB Leading Index MoMJAN</t>
         </is>
       </c>
       <c r="D262" t="inlineStr"/>
       <c r="E262" t="inlineStr">
         <is>
-          <t>-14</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>-14.4</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G262" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="263">
@@ -7771,7 +7771,7 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>4-Week Bill Auction</t>
+          <t>8-Week Bill Auction</t>
         </is>
       </c>
       <c r="D265" t="inlineStr"/>
@@ -7794,7 +7794,7 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>8-Week Bill Auction</t>
+          <t>4-Week Bill Auction</t>
         </is>
       </c>
       <c r="D266" t="inlineStr"/>
@@ -7817,7 +7817,7 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/14</t>
+          <t>EIA Distillate Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="D267" t="inlineStr"/>
@@ -7840,7 +7840,7 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/14</t>
+          <t>EIA Gasoline Production ChangeFEB/14</t>
         </is>
       </c>
       <c r="D268" t="inlineStr"/>
@@ -7863,7 +7863,7 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/14</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="D269" t="inlineStr"/>
@@ -7886,7 +7886,7 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/14</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="D270" t="inlineStr"/>
@@ -7909,7 +7909,7 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/14</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/14</t>
         </is>
       </c>
       <c r="D271" t="inlineStr"/>
@@ -7932,7 +7932,7 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/14</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/14</t>
         </is>
       </c>
       <c r="D272" t="inlineStr"/>
@@ -7955,7 +7955,7 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/14</t>
+          <t>EIA Crude Oil Imports ChangeFEB/14</t>
         </is>
       </c>
       <c r="D273" t="inlineStr"/>
@@ -8207,23 +8207,19 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>US</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>S&amp;P Global Australia Composite PMI FlashFEB</t>
+          <t>Fed Kugler Speech</t>
         </is>
       </c>
       <c r="D284" t="inlineStr"/>
       <c r="E284" t="inlineStr"/>
-      <c r="F284" t="inlineStr">
-        <is>
-          <t>50.6</t>
-        </is>
-      </c>
+      <c r="F284" t="inlineStr"/>
       <c r="G284" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="285">
@@ -8239,14 +8235,14 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>S&amp;P Global Australia Services PMI FlashFEB</t>
+          <t>S&amp;P Global Australia Manufacturing PMI FlashFEB</t>
         </is>
       </c>
       <c r="D285" t="inlineStr"/>
       <c r="E285" t="inlineStr"/>
       <c r="F285" t="inlineStr">
         <is>
-          <t>51.3</t>
+          <t>49.9</t>
         </is>
       </c>
       <c r="G285" t="n">
@@ -8261,17 +8257,21 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>Fed Kugler Speech</t>
+          <t>S&amp;P Global Australia Services PMI FlashFEB</t>
         </is>
       </c>
       <c r="D286" t="inlineStr"/>
       <c r="E286" t="inlineStr"/>
-      <c r="F286" t="inlineStr"/>
+      <c r="F286" t="inlineStr">
+        <is>
+          <t>51.3</t>
+        </is>
+      </c>
       <c r="G286" t="n">
         <v>2</v>
       </c>
@@ -8289,18 +8289,18 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>S&amp;P Global Australia Manufacturing PMI FlashFEB</t>
+          <t>S&amp;P Global Australia Composite PMI FlashFEB</t>
         </is>
       </c>
       <c r="D287" t="inlineStr"/>
       <c r="E287" t="inlineStr"/>
       <c r="F287" t="inlineStr">
         <is>
-          <t>49.9</t>
+          <t>50.6</t>
         </is>
       </c>
       <c r="G287" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="288">
@@ -8401,14 +8401,14 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>Inflation Rate Ex-Food and Energy YoYJAN</t>
+          <t>Inflation Rate MoMJAN</t>
         </is>
       </c>
       <c r="D291" t="inlineStr"/>
       <c r="E291" t="inlineStr"/>
       <c r="F291" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G291" t="n">
@@ -8428,14 +8428,14 @@
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>Inflation Rate MoMJAN</t>
+          <t>Inflation Rate Ex-Food and Energy YoYJAN</t>
         </is>
       </c>
       <c r="D292" t="inlineStr"/>
       <c r="E292" t="inlineStr"/>
       <c r="F292" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>2.6%</t>
         </is>
       </c>
       <c r="G292" t="n">
@@ -8517,18 +8517,18 @@
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>Jibun Bank Services PMI FlashFEB</t>
+          <t>Jibun Bank Composite PMI FlashFEB</t>
         </is>
       </c>
       <c r="D295" t="inlineStr"/>
       <c r="E295" t="inlineStr"/>
       <c r="F295" t="inlineStr">
         <is>
-          <t>52.2</t>
+          <t>51.5</t>
         </is>
       </c>
       <c r="G295" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="296">
@@ -8544,18 +8544,18 @@
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>Jibun Bank Composite PMI FlashFEB</t>
+          <t>Jibun Bank Services PMI FlashFEB</t>
         </is>
       </c>
       <c r="D296" t="inlineStr"/>
       <c r="E296" t="inlineStr"/>
       <c r="F296" t="inlineStr">
         <is>
-          <t>51.5</t>
+          <t>52.2</t>
         </is>
       </c>
       <c r="G296" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="297">
@@ -8639,12 +8639,12 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>BR</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>3-Month Bill Auction</t>
+          <t>2-Year LTN Auction</t>
         </is>
       </c>
       <c r="D300" t="inlineStr"/>
@@ -8662,12 +8662,12 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>2-Year LTN Auction</t>
+          <t>3-Month Bill Auction</t>
         </is>
       </c>
       <c r="D301" t="inlineStr"/>
@@ -8717,14 +8717,14 @@
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>HSBC Manufacturing PMI FlashFEB</t>
+          <t>HSBC Composite PMI FlashFEB</t>
         </is>
       </c>
       <c r="D303" t="inlineStr"/>
       <c r="E303" t="inlineStr"/>
       <c r="F303" t="inlineStr">
         <is>
-          <t>57.9</t>
+          <t>58.2</t>
         </is>
       </c>
       <c r="G303" t="n">
@@ -8744,14 +8744,14 @@
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>HSBC Composite PMI FlashFEB</t>
+          <t>HSBC Manufacturing PMI FlashFEB</t>
         </is>
       </c>
       <c r="D304" t="inlineStr"/>
       <c r="E304" t="inlineStr"/>
       <c r="F304" t="inlineStr">
         <is>
-          <t>58.2</t>
+          <t>57.9</t>
         </is>
       </c>
       <c r="G304" t="n">
@@ -8914,18 +8914,18 @@
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>Business Climate IndicatorFEB</t>
+          <t>Business ConfidenceFEB</t>
         </is>
       </c>
       <c r="D310" t="inlineStr"/>
       <c r="E310" t="inlineStr"/>
       <c r="F310" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>94</t>
         </is>
       </c>
       <c r="G310" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="311">
@@ -8941,18 +8941,18 @@
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>Business ConfidenceFEB</t>
+          <t>Business Climate IndicatorFEB</t>
         </is>
       </c>
       <c r="D311" t="inlineStr"/>
       <c r="E311" t="inlineStr"/>
       <c r="F311" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>92</t>
         </is>
       </c>
       <c r="G311" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="312">
@@ -8991,14 +8991,18 @@
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>HCOB Composite PMI FlashFEB</t>
+          <t>HCOB Services PMI FlashFEB</t>
         </is>
       </c>
       <c r="D313" t="inlineStr"/>
-      <c r="E313" t="inlineStr"/>
+      <c r="E313" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t>47.2</t>
+          <t>48</t>
         </is>
       </c>
       <c r="G313" t="n">
@@ -9049,18 +9053,14 @@
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>HCOB Services PMI FlashFEB</t>
+          <t>HCOB Composite PMI FlashFEB</t>
         </is>
       </c>
       <c r="D315" t="inlineStr"/>
-      <c r="E315" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
+      <c r="E315" t="inlineStr"/>
       <c r="F315" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>47.2</t>
         </is>
       </c>
       <c r="G315" t="n">
@@ -9080,22 +9080,22 @@
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>HCOB Services PMI FlashFEB</t>
+          <t>HCOB Manufacturing PMI FlashFEB</t>
         </is>
       </c>
       <c r="D316" t="inlineStr"/>
       <c r="E316" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>45.5</t>
         </is>
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t>51.9</t>
+          <t>45.1</t>
         </is>
       </c>
       <c r="G316" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="317">
@@ -9138,22 +9138,22 @@
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>HCOB Manufacturing PMI FlashFEB</t>
+          <t>HCOB Services PMI FlashFEB</t>
         </is>
       </c>
       <c r="D318" t="inlineStr"/>
       <c r="E318" t="inlineStr">
         <is>
-          <t>45.5</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="F318" t="inlineStr">
         <is>
-          <t>45.1</t>
+          <t>51.9</t>
         </is>
       </c>
       <c r="G318" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="319">
@@ -9164,27 +9164,27 @@
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>EA</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>Harmonised Inflation Rate YoY FinalJAN</t>
+          <t>HCOB Manufacturing PMI FlashFEB</t>
         </is>
       </c>
       <c r="D319" t="inlineStr"/>
       <c r="E319" t="inlineStr">
         <is>
-          <t>1.7%</t>
+          <t>47</t>
         </is>
       </c>
       <c r="F319" t="inlineStr">
         <is>
-          <t>1.7%</t>
+          <t>46.8</t>
         </is>
       </c>
       <c r="G319" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="320">
@@ -9195,27 +9195,27 @@
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>EA</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>Harmonised Inflation Rate MoM FinalJAN</t>
+          <t>HCOB Services PMI FlashFEB</t>
         </is>
       </c>
       <c r="D320" t="inlineStr"/>
       <c r="E320" t="inlineStr">
         <is>
-          <t>-0.7%</t>
+          <t>51.5</t>
         </is>
       </c>
       <c r="F320" t="inlineStr">
         <is>
-          <t>-0.7%</t>
+          <t>51.2</t>
         </is>
       </c>
       <c r="G320" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="321">
@@ -9231,22 +9231,22 @@
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>Inflation Rate MoM FinalJAN</t>
+          <t>Harmonised Inflation Rate YoY FinalJAN</t>
         </is>
       </c>
       <c r="D321" t="inlineStr"/>
       <c r="E321" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>1.7%</t>
         </is>
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>1.7%</t>
         </is>
       </c>
       <c r="G321" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="322">
@@ -9257,23 +9257,23 @@
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>EA</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>HCOB Services PMI FlashFEB</t>
+          <t>Inflation Rate MoM FinalJAN</t>
         </is>
       </c>
       <c r="D322" t="inlineStr"/>
       <c r="E322" t="inlineStr">
         <is>
-          <t>51.5</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t>51.2</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="G322" t="n">
@@ -9346,27 +9346,27 @@
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>EA</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>HCOB Manufacturing PMI FlashFEB</t>
+          <t>Harmonised Inflation Rate MoM FinalJAN</t>
         </is>
       </c>
       <c r="D325" t="inlineStr"/>
       <c r="E325" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>-0.7%</t>
         </is>
       </c>
       <c r="F325" t="inlineStr">
         <is>
-          <t>46.8</t>
+          <t>-0.7%</t>
         </is>
       </c>
       <c r="G325" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="326">
@@ -9382,18 +9382,18 @@
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>S&amp;P Global Manufacturing PMI FlashFEB</t>
+          <t>S&amp;P Global Services PMI FlashFEB</t>
         </is>
       </c>
       <c r="D326" t="inlineStr"/>
       <c r="E326" t="inlineStr">
         <is>
-          <t>48.5</t>
+          <t>51</t>
         </is>
       </c>
       <c r="F326" t="inlineStr">
         <is>
-          <t>48.5</t>
+          <t>51</t>
         </is>
       </c>
       <c r="G326" t="n">
@@ -9413,22 +9413,18 @@
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>S&amp;P Global Services PMI FlashFEB</t>
+          <t>S&amp;P Global Composite PMI FlashFEB</t>
         </is>
       </c>
       <c r="D327" t="inlineStr"/>
-      <c r="E327" t="inlineStr">
+      <c r="E327" t="inlineStr"/>
+      <c r="F327" t="inlineStr">
         <is>
           <t>51</t>
         </is>
       </c>
-      <c r="F327" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
       <c r="G327" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="328">
@@ -9444,18 +9440,22 @@
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>S&amp;P Global Composite PMI FlashFEB</t>
+          <t>S&amp;P Global Manufacturing PMI FlashFEB</t>
         </is>
       </c>
       <c r="D328" t="inlineStr"/>
-      <c r="E328" t="inlineStr"/>
+      <c r="E328" t="inlineStr">
+        <is>
+          <t>48.5</t>
+        </is>
+      </c>
       <c r="F328" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>48.5</t>
         </is>
       </c>
       <c r="G328" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="329">
@@ -9544,18 +9544,22 @@
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>Economic Activity MoMDEC</t>
+          <t>GDP Growth Rate QoQ FinalQ4</t>
         </is>
       </c>
       <c r="D332" t="inlineStr"/>
-      <c r="E332" t="inlineStr"/>
+      <c r="E332" t="inlineStr">
+        <is>
+          <t>-0.6%</t>
+        </is>
+      </c>
       <c r="F332" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>-0.6%</t>
         </is>
       </c>
       <c r="G332" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="333">
@@ -9602,22 +9606,18 @@
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>GDP Growth Rate QoQ FinalQ4</t>
+          <t>Economic Activity MoMDEC</t>
         </is>
       </c>
       <c r="D334" t="inlineStr"/>
-      <c r="E334" t="inlineStr">
-        <is>
-          <t>-0.6%</t>
-        </is>
-      </c>
+      <c r="E334" t="inlineStr"/>
       <c r="F334" t="inlineStr">
         <is>
-          <t>-0.6%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="G334" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="335">
@@ -9772,14 +9772,14 @@
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>S&amp;P Global Services PMI FlashFEB</t>
+          <t>S&amp;P Global Manufacturing PMI FlashFEB</t>
         </is>
       </c>
       <c r="D340" t="inlineStr"/>
       <c r="E340" t="inlineStr"/>
       <c r="F340" t="inlineStr">
         <is>
-          <t>52.7</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="G340" t="n">
@@ -9826,14 +9826,14 @@
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>S&amp;P Global Manufacturing PMI FlashFEB</t>
+          <t>S&amp;P Global Services PMI FlashFEB</t>
         </is>
       </c>
       <c r="D342" t="inlineStr"/>
       <c r="E342" t="inlineStr"/>
       <c r="F342" t="inlineStr">
         <is>
-          <t>51.3</t>
+          <t>52.7</t>
         </is>
       </c>
       <c r="G342" t="n">
@@ -9853,22 +9853,22 @@
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>Michigan Consumer Sentiment FinalFEB</t>
+          <t>Michigan 5 Year Inflation Expectations FinalFEB</t>
         </is>
       </c>
       <c r="D343" t="inlineStr"/>
       <c r="E343" t="inlineStr">
         <is>
-          <t>67.8</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F343" t="inlineStr">
         <is>
-          <t>67.8</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="G343" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="344">
@@ -9884,18 +9884,18 @@
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>Michigan 5 Year Inflation Expectations FinalFEB</t>
+          <t>Michigan Consumer Expectations FinalFEB</t>
         </is>
       </c>
       <c r="D344" t="inlineStr"/>
       <c r="E344" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>67.3</t>
         </is>
       </c>
       <c r="F344" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>67.3</t>
         </is>
       </c>
       <c r="G344" t="n">
@@ -9915,18 +9915,22 @@
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>Existing Home Sales MoMJAN</t>
+          <t>Michigan Current Conditions FinalFEB</t>
         </is>
       </c>
       <c r="D345" t="inlineStr"/>
-      <c r="E345" t="inlineStr"/>
+      <c r="E345" t="inlineStr">
+        <is>
+          <t>68.7</t>
+        </is>
+      </c>
       <c r="F345" t="inlineStr">
         <is>
-          <t>-1.7%</t>
+          <t>68.7</t>
         </is>
       </c>
       <c r="G345" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="346">
@@ -9942,22 +9946,22 @@
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>Michigan Inflation Expectations FinalFEB</t>
+          <t>Michigan Consumer Sentiment FinalFEB</t>
         </is>
       </c>
       <c r="D346" t="inlineStr"/>
       <c r="E346" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>67.8</t>
         </is>
       </c>
       <c r="F346" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>67.8</t>
         </is>
       </c>
       <c r="G346" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="347">
@@ -9973,18 +9977,18 @@
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>Michigan Consumer Expectations FinalFEB</t>
+          <t>Michigan Inflation Expectations FinalFEB</t>
         </is>
       </c>
       <c r="D347" t="inlineStr"/>
       <c r="E347" t="inlineStr">
         <is>
-          <t>67.3</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="F347" t="inlineStr">
         <is>
-          <t>67.3</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="G347" t="n">
@@ -10035,22 +10039,18 @@
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>Michigan Current Conditions FinalFEB</t>
+          <t>Existing Home Sales MoMJAN</t>
         </is>
       </c>
       <c r="D349" t="inlineStr"/>
-      <c r="E349" t="inlineStr">
-        <is>
-          <t>68.7</t>
-        </is>
-      </c>
+      <c r="E349" t="inlineStr"/>
       <c r="F349" t="inlineStr">
         <is>
-          <t>68.7</t>
+          <t>-1.7%</t>
         </is>
       </c>
       <c r="G349" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="350">
@@ -10107,17 +10107,21 @@
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>Baker Hughes Oil Rig CountFEB/21</t>
+          <t>FDI (YTD) YoYJAN</t>
         </is>
       </c>
       <c r="D352" t="inlineStr"/>
       <c r="E352" t="inlineStr"/>
-      <c r="F352" t="inlineStr"/>
+      <c r="F352" t="inlineStr">
+        <is>
+          <t>-18.0%</t>
+        </is>
+      </c>
       <c r="G352" t="n">
         <v>3</v>
       </c>
@@ -10130,12 +10134,12 @@
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>BR</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>Baker Hughes Total Rigs CountFEB/21</t>
+          <t>Federal Tax RevenuesJAN</t>
         </is>
       </c>
       <c r="D353" t="inlineStr"/>
@@ -10153,21 +10157,17 @@
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>US</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>FDI (YTD) YoYJAN</t>
+          <t>Baker Hughes Total Rigs CountFEB/21</t>
         </is>
       </c>
       <c r="D354" t="inlineStr"/>
       <c r="E354" t="inlineStr"/>
-      <c r="F354" t="inlineStr">
-        <is>
-          <t>-18.0%</t>
-        </is>
-      </c>
+      <c r="F354" t="inlineStr"/>
       <c r="G354" t="n">
         <v>3</v>
       </c>
@@ -10180,12 +10180,12 @@
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>US</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>Federal Tax RevenuesJAN</t>
+          <t>Baker Hughes Oil Rig CountFEB/21</t>
         </is>
       </c>
       <c r="D355" t="inlineStr"/>
@@ -10224,21 +10224,17 @@
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>Inflation Rate MoMJAN</t>
+          <t>5-Year KTB Auction</t>
         </is>
       </c>
       <c r="D357" t="inlineStr"/>
       <c r="E357" t="inlineStr"/>
-      <c r="F357" t="inlineStr">
-        <is>
-          <t>-0.1%</t>
-        </is>
-      </c>
+      <c r="F357" t="inlineStr"/>
       <c r="G357" t="n">
         <v>3</v>
       </c>
@@ -10283,14 +10279,14 @@
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>Inflation Rate YoYJAN</t>
+          <t>Inflation Rate MoMJAN</t>
         </is>
       </c>
       <c r="D359" t="inlineStr"/>
       <c r="E359" t="inlineStr"/>
       <c r="F359" t="inlineStr">
         <is>
-          <t>2.1%</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="G359" t="n">
@@ -10305,17 +10301,21 @@
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>5-Year KTB Auction</t>
+          <t>Inflation Rate YoYJAN</t>
         </is>
       </c>
       <c r="D360" t="inlineStr"/>
       <c r="E360" t="inlineStr"/>
-      <c r="F360" t="inlineStr"/>
+      <c r="F360" t="inlineStr">
+        <is>
+          <t>2.1%</t>
+        </is>
+      </c>
       <c r="G360" t="n">
         <v>3</v>
       </c>
@@ -10333,14 +10333,14 @@
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>Capacity UtilizationFEB</t>
+          <t>Business ConfidenceFEB</t>
         </is>
       </c>
       <c r="D361" t="inlineStr"/>
       <c r="E361" t="inlineStr"/>
       <c r="F361" t="inlineStr"/>
       <c r="G361" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="362">
@@ -10356,14 +10356,14 @@
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>Business ConfidenceFEB</t>
+          <t>Capacity UtilizationFEB</t>
         </is>
       </c>
       <c r="D362" t="inlineStr"/>
       <c r="E362" t="inlineStr"/>
       <c r="F362" t="inlineStr"/>
       <c r="G362" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="363">
@@ -10379,14 +10379,14 @@
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>Ifo Current ConditionsFEB</t>
+          <t>Ifo ExpectationsFEB</t>
         </is>
       </c>
       <c r="D363" t="inlineStr"/>
       <c r="E363" t="inlineStr"/>
       <c r="F363" t="inlineStr">
         <is>
-          <t>85.1</t>
+          <t>83</t>
         </is>
       </c>
       <c r="G363" t="n">
@@ -10433,14 +10433,14 @@
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>Ifo ExpectationsFEB</t>
+          <t>Ifo Current ConditionsFEB</t>
         </is>
       </c>
       <c r="D365" t="inlineStr"/>
       <c r="E365" t="inlineStr"/>
       <c r="F365" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>85.1</t>
         </is>
       </c>
       <c r="G365" t="n">
@@ -10460,22 +10460,22 @@
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>Inflation Rate YoY FinalJAN</t>
+          <t>Core Inflation Rate YoY FinalJAN</t>
         </is>
       </c>
       <c r="D366" t="inlineStr"/>
       <c r="E366" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>2.7%</t>
         </is>
       </c>
       <c r="F366" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>2.7%</t>
         </is>
       </c>
       <c r="G366" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="367">
@@ -10491,22 +10491,22 @@
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>Inflation Rate MoM FinalJAN</t>
+          <t>Inflation Rate YoY FinalJAN</t>
         </is>
       </c>
       <c r="D367" t="inlineStr"/>
       <c r="E367" t="inlineStr">
         <is>
-          <t>-0.3%</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="F367" t="inlineStr">
         <is>
-          <t>-0.3%</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="G367" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="368">
@@ -10522,18 +10522,18 @@
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>Core Inflation Rate YoY FinalJAN</t>
+          <t>Inflation Rate MoM FinalJAN</t>
         </is>
       </c>
       <c r="D368" t="inlineStr"/>
       <c r="E368" t="inlineStr">
         <is>
-          <t>2.7%</t>
+          <t>-0.3%</t>
         </is>
       </c>
       <c r="F368" t="inlineStr">
         <is>
-          <t>2.7%</t>
+          <t>-0.3%</t>
         </is>
       </c>
       <c r="G368" t="n">
@@ -10584,7 +10584,7 @@
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>3-Month Bubill Auction</t>
+          <t>9-Month Bubill Auction</t>
         </is>
       </c>
       <c r="D370" t="inlineStr"/>
@@ -10607,7 +10607,7 @@
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>9-Month Bubill Auction</t>
+          <t>3-Month Bubill Auction</t>
         </is>
       </c>
       <c r="D371" t="inlineStr"/>
@@ -11071,14 +11071,14 @@
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>Balance of TradeDEC</t>
+          <t>ExportsDEC</t>
         </is>
       </c>
       <c r="D391" t="inlineStr"/>
       <c r="E391" t="inlineStr"/>
       <c r="F391" t="inlineStr">
         <is>
-          <t>SAR 34B</t>
+          <t>SAR 94.5B</t>
         </is>
       </c>
       <c r="G391" t="n">
@@ -11098,14 +11098,14 @@
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>ImportsDEC</t>
+          <t>Balance of TradeDEC</t>
         </is>
       </c>
       <c r="D392" t="inlineStr"/>
       <c r="E392" t="inlineStr"/>
       <c r="F392" t="inlineStr">
         <is>
-          <t>SAR 60.5B</t>
+          <t>SAR 34B</t>
         </is>
       </c>
       <c r="G392" t="n">
@@ -11125,14 +11125,14 @@
       </c>
       <c r="C393" t="inlineStr">
         <is>
-          <t>ExportsDEC</t>
+          <t>ImportsDEC</t>
         </is>
       </c>
       <c r="D393" t="inlineStr"/>
       <c r="E393" t="inlineStr"/>
       <c r="F393" t="inlineStr">
         <is>
-          <t>SAR 94.5B</t>
+          <t>SAR 60.5B</t>
         </is>
       </c>
       <c r="G393" t="n">
@@ -11147,19 +11147,23 @@
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>EU</t>
+          <t>ZA</t>
         </is>
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>New Car Registrations YoYJAN</t>
+          <t>Leading Business Cycle Indicator MoMDEC</t>
         </is>
       </c>
       <c r="D394" t="inlineStr"/>
       <c r="E394" t="inlineStr"/>
-      <c r="F394" t="inlineStr"/>
+      <c r="F394" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="G394" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="395">
@@ -11175,7 +11179,7 @@
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>GDP Growth Rate QoQ FinalQ4</t>
+          <t>GDP Growth Rate YoY FinalQ4</t>
         </is>
       </c>
       <c r="D395" t="inlineStr"/>
@@ -11206,7 +11210,7 @@
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>GDP Growth Rate YoY FinalQ4</t>
+          <t>GDP Growth Rate QoQ FinalQ4</t>
         </is>
       </c>
       <c r="D396" t="inlineStr"/>
@@ -11232,23 +11236,19 @@
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>ZA</t>
+          <t>EU</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>Leading Business Cycle Indicator MoMDEC</t>
+          <t>New Car Registrations YoYJAN</t>
         </is>
       </c>
       <c r="D397" t="inlineStr"/>
       <c r="E397" t="inlineStr"/>
-      <c r="F397" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+      <c r="F397" t="inlineStr"/>
       <c r="G397" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="398">
@@ -11264,7 +11264,7 @@
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>BTP€i Auction</t>
+          <t>2-Year BTP Short Term Auction</t>
         </is>
       </c>
       <c r="D398" t="inlineStr"/>
@@ -11282,17 +11282,21 @@
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>EA</t>
         </is>
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>2-Year BTP Short Term Auction</t>
+          <t>Negotiated Wage GrowthQ4</t>
         </is>
       </c>
       <c r="D399" t="inlineStr"/>
       <c r="E399" t="inlineStr"/>
-      <c r="F399" t="inlineStr"/>
+      <c r="F399" t="inlineStr">
+        <is>
+          <t>5.1%</t>
+        </is>
+      </c>
       <c r="G399" t="n">
         <v>3</v>
       </c>
@@ -11305,21 +11309,17 @@
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>EA</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>Negotiated Wage GrowthQ4</t>
+          <t>BTP€i Auction</t>
         </is>
       </c>
       <c r="D400" t="inlineStr"/>
       <c r="E400" t="inlineStr"/>
-      <c r="F400" t="inlineStr">
-        <is>
-          <t>5.1%</t>
-        </is>
-      </c>
+      <c r="F400" t="inlineStr"/>
       <c r="G400" t="n">
         <v>3</v>
       </c>
@@ -11401,6 +11401,79 @@
         <v>2</v>
       </c>
     </row>
+    <row r="404">
+      <c r="A404" t="inlineStr">
+        <is>
+          <t>2025-02-25 07:00:00-05:00</t>
+        </is>
+      </c>
+      <c r="B404" t="inlineStr">
+        <is>
+          <t>BR</t>
+        </is>
+      </c>
+      <c r="C404" t="inlineStr">
+        <is>
+          <t>IPCA mid-month CPI YoYFEB</t>
+        </is>
+      </c>
+      <c r="D404" t="inlineStr"/>
+      <c r="E404" t="inlineStr"/>
+      <c r="F404" t="inlineStr"/>
+      <c r="G404" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="inlineStr">
+        <is>
+          <t>2025-02-25 07:00:00-05:00</t>
+        </is>
+      </c>
+      <c r="B405" t="inlineStr">
+        <is>
+          <t>BR</t>
+        </is>
+      </c>
+      <c r="C405" t="inlineStr">
+        <is>
+          <t>IPCA mid-month CPI MoMFEB</t>
+        </is>
+      </c>
+      <c r="D405" t="inlineStr"/>
+      <c r="E405" t="inlineStr"/>
+      <c r="F405" t="inlineStr"/>
+      <c r="G405" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="inlineStr">
+        <is>
+          <t>2025-02-25 07:00:00-05:00</t>
+        </is>
+      </c>
+      <c r="B406" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="C406" t="inlineStr">
+        <is>
+          <t>Negotiated Wage GrowthQ4</t>
+        </is>
+      </c>
+      <c r="D406" t="inlineStr"/>
+      <c r="E406" t="inlineStr"/>
+      <c r="F406" t="inlineStr">
+        <is>
+          <t>5.1%</t>
+        </is>
+      </c>
+      <c r="G406" t="n">
+        <v>3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Input_data/EST_All Countries_trad_eco_cal_2025-02-14_to_2025-02-25.xlsx
+++ b/Input_data/EST_All Countries_trad_eco_cal_2025-02-14_to_2025-02-25.xlsx
@@ -699,22 +699,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Inflation Rate MoM FinalJAN</t>
+          <t>Core Inflation Rate YoY FinalJAN</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>2.4%</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>2.4%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>2.4%</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -734,22 +734,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Harmonised Inflation Rate MoM FinalJAN</t>
+          <t>Harmonised Inflation Rate YoY FinalJAN</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -769,7 +769,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Harmonised Inflation Rate YoY FinalJAN</t>
+          <t>Inflation Rate YoY FinalJAN</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -779,12 +779,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>3%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>3.0%</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -804,22 +804,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Core Inflation Rate YoY FinalJAN</t>
+          <t>Inflation Rate MoM FinalJAN</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2.4%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2.4%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2.4%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -839,22 +839,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Inflation Rate YoY FinalJAN</t>
+          <t>Harmonised Inflation Rate MoM FinalJAN</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>3%</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>3.0%</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1220,12 +1220,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Deposit Growth YoYJAN/31</t>
+          <t>Foreign Exchange ReservesFEB/07</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>10.3%</t>
+          <t>$638.26B</t>
         </is>
       </c>
       <c r="E24" t="inlineStr"/>
@@ -1247,12 +1247,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Foreign Exchange ReservesFEB/07</t>
+          <t>Bank Loan Growth YoYJAN/31</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>$638.26B</t>
+          <t>11.4%</t>
         </is>
       </c>
       <c r="E25" t="inlineStr"/>
@@ -1274,12 +1274,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Bank Loan Growth YoYJAN/31</t>
+          <t>Deposit Growth YoYJAN/31</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>11.4%</t>
+          <t>10.3%</t>
         </is>
       </c>
       <c r="E26" t="inlineStr"/>
@@ -1319,23 +1319,27 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Gas/Autos MoMJAN</t>
+          <t>Manufacturing Sales MoM FinalDEC</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>-0.5%</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr"/>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>0.7%</t>
+        </is>
+      </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -1355,22 +1359,26 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Import Prices YoYJAN</t>
+          <t>Retail Sales MoMJAN</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1.9%</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr"/>
+          <t>-0.9%</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>-0.1%</t>
+        </is>
+      </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -1381,23 +1389,27 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Retail Sales YoYJAN</t>
+          <t>Wholesale Sales MoM FinalDEC</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>4.2%</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr"/>
+          <t>-0.2%</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>3.7%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -1417,22 +1429,26 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Export Prices YoYJAN</t>
+          <t>Import Prices MoMJAN</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2.7%</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr"/>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="32">
@@ -1448,12 +1464,12 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Retail Sales Control Group MoMJAN</t>
+          <t>Export Prices MoMJAN</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>-0.8%</t>
+          <t>1.3%</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1463,7 +1479,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -1478,31 +1494,27 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Autos MoMJAN</t>
+          <t>New Motor Vehicle SalesDEC</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>-0.4%</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>135.5K</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>153K</t>
         </is>
       </c>
       <c r="G33" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="34">
@@ -1518,12 +1530,12 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Export Prices MoMJAN</t>
+          <t>Retail Sales Control Group MoMJAN</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>1.3%</t>
+          <t>-0.8%</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1533,7 +1545,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -1553,26 +1565,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Import Prices MoMJAN</t>
+          <t>Export Prices YoYJAN</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
+          <t>2.7%</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="G35" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="36">
@@ -1583,23 +1591,23 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>US</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>New Motor Vehicle SalesDEC</t>
+          <t>Retail Sales YoYJAN</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>135.5K</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr">
         <is>
-          <t>153K</t>
+          <t>3.7%</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -1614,27 +1622,23 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>US</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Wholesale Sales MoM FinalDEC</t>
+          <t>Import Prices YoYJAN</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>-0.2%</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
+          <t>1.9%</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -1649,27 +1653,23 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>US</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Manufacturing Sales MoM FinalDEC</t>
+          <t>Retail Sales Ex Gas/Autos MoMJAN</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>0.7%</t>
-        </is>
-      </c>
+          <t>-0.5%</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -1689,26 +1689,26 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Retail Sales MoMJAN</t>
+          <t>Retail Sales Ex Autos MoMJAN</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>-0.9%</t>
+          <t>-0.4%</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G39" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="40">
@@ -1891,26 +1891,26 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Retail Inventories Ex Autos MoMDEC</t>
+          <t>Business Inventories MoMDEC</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
+          <t>-0.2%</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
           <t>-0.1%</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
       <c r="G45" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="46">
@@ -1926,26 +1926,26 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Business Inventories MoMDEC</t>
+          <t>Retail Inventories Ex Autos MoMDEC</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>-0.2%</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G46" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="47">
@@ -1984,22 +1984,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Inflation Rate YoYJAN</t>
+          <t>Inflation Rate MoMJAN</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>9.9%</t>
+          <t>1.2%</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>1.3%</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>9.9%</t>
+          <t>1.2%</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -2019,22 +2019,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Inflation Rate MoMJAN</t>
+          <t>Inflation Rate YoYJAN</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>1.2%</t>
+          <t>9.9%</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>1.3%</t>
+          <t>10%</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>1.2%</t>
+          <t>9.9%</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -2054,12 +2054,12 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Baker Hughes Total Rigs CountFEB/14</t>
+          <t>Baker Hughes Oil Rig CountFEB/14</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>588</t>
+          <t>481</t>
         </is>
       </c>
       <c r="E50" t="inlineStr"/>
@@ -2081,12 +2081,12 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Baker Hughes Oil Rig CountFEB/14</t>
+          <t>Baker Hughes Total Rigs CountFEB/14</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>481</t>
+          <t>588</t>
         </is>
       </c>
       <c r="E51" t="inlineStr"/>

--- a/Input_data/EST_All Countries_trad_eco_cal_2025-02-14_to_2025-02-25.xlsx
+++ b/Input_data/EST_All Countries_trad_eco_cal_2025-02-14_to_2025-02-25.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G426"/>
+  <dimension ref="A1:G428"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -699,22 +699,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Inflation Rate MoM FinalJAN</t>
+          <t>Core Inflation Rate YoY FinalJAN</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>2.4%</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>2.4%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>2.4%</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -734,22 +734,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Inflation Rate YoY FinalJAN</t>
+          <t>Harmonised Inflation Rate MoM FinalJAN</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>3%</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>3.0%</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -769,22 +769,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Harmonised Inflation Rate MoM FinalJAN</t>
+          <t>Harmonised Inflation Rate YoY FinalJAN</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -804,22 +804,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Core Inflation Rate YoY FinalJAN</t>
+          <t>Inflation Rate MoM FinalJAN</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2.4%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2.4%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2.4%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -839,7 +839,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Harmonised Inflation Rate YoY FinalJAN</t>
+          <t>Inflation Rate YoY FinalJAN</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -849,12 +849,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>3%</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>3.0%</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1220,12 +1220,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Deposit Growth YoYJAN/31</t>
+          <t>Foreign Exchange ReservesFEB/07</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>10.3%</t>
+          <t>$638.26B</t>
         </is>
       </c>
       <c r="E24" t="inlineStr"/>
@@ -1274,12 +1274,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Foreign Exchange ReservesFEB/07</t>
+          <t>Deposit Growth YoYJAN/31</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>$638.26B</t>
+          <t>10.3%</t>
         </is>
       </c>
       <c r="E26" t="inlineStr"/>
@@ -1319,31 +1319,27 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Autos MoMJAN</t>
+          <t>New Motor Vehicle SalesDEC</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>-0.4%</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>135.5K</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>153K</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="29">
@@ -1354,23 +1350,27 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Gas/Autos MoMJAN</t>
+          <t>Manufacturing Sales MoM FinalDEC</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>-0.5%</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr"/>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>0.7%</t>
+        </is>
+      </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -1385,23 +1385,27 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Retail Sales YoYJAN</t>
+          <t>Wholesale Sales MoM FinalDEC</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>4.2%</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr"/>
+          <t>-0.2%</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>3.7%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -1421,22 +1425,26 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Export Prices YoYJAN</t>
+          <t>Import Prices MoMJAN</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2.7%</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr"/>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="32">
@@ -1452,12 +1460,12 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Retail Sales Control Group MoMJAN</t>
+          <t>Export Prices MoMJAN</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>-0.8%</t>
+          <t>1.3%</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1467,7 +1475,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -1487,22 +1495,26 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Import Prices YoYJAN</t>
+          <t>Retail Sales MoMJAN</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1.9%</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr"/>
+          <t>-0.9%</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>-0.1%</t>
+        </is>
+      </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G33" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="34">
@@ -1518,12 +1530,12 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Export Prices MoMJAN</t>
+          <t>Retail Sales Control Group MoMJAN</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>1.3%</t>
+          <t>-0.8%</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1533,7 +1545,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -1553,26 +1565,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Import Prices MoMJAN</t>
+          <t>Export Prices YoYJAN</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
+          <t>2.7%</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="G35" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="36">
@@ -1583,27 +1591,23 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>US</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Wholesale Sales MoM FinalDEC</t>
+          <t>Retail Sales YoYJAN</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>-0.2%</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
+          <t>4.2%</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>3.7%</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -1623,26 +1627,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Retail Sales MoMJAN</t>
+          <t>Retail Sales Ex Gas/Autos MoMJAN</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>-0.9%</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>-0.1%</t>
-        </is>
-      </c>
+          <t>-0.5%</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G37" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="38">
@@ -1653,31 +1653,31 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>US</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Manufacturing Sales MoM FinalDEC</t>
+          <t>Retail Sales Ex Autos MoMJAN</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
+          <t>-0.4%</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
           <t>0.3%</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>0.7%</t>
-        </is>
-      </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G38" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="39">
@@ -1688,23 +1688,23 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>US</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>New Motor Vehicle SalesDEC</t>
+          <t>Import Prices YoYJAN</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>135.5K</t>
+          <t>1.9%</t>
         </is>
       </c>
       <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr">
         <is>
-          <t>153K</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -2054,12 +2054,12 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Baker Hughes Total Rigs CountFEB/14</t>
+          <t>Baker Hughes Oil Rig CountFEB/14</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>588</t>
+          <t>481</t>
         </is>
       </c>
       <c r="E50" t="inlineStr"/>
@@ -2081,12 +2081,12 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Baker Hughes Oil Rig CountFEB/14</t>
+          <t>Baker Hughes Total Rigs CountFEB/14</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>481</t>
+          <t>588</t>
         </is>
       </c>
       <c r="E51" t="inlineStr"/>
@@ -2131,7 +2131,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>GDP Capital Expenditure QoQ PrelQ4</t>
+          <t>GDP Growth Annualized PrelQ4</t>
         </is>
       </c>
       <c r="D53" t="inlineStr"/>
@@ -2142,11 +2142,11 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>2.1%</t>
         </is>
       </c>
       <c r="G53" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="54">
@@ -2162,22 +2162,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>GDP Growth Rate QoQ PrelQ4</t>
+          <t>GDP Private Consumption QoQ PrelQ4</t>
         </is>
       </c>
       <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr">
         <is>
+          <t>-0.3%</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
           <t>0.3%</t>
         </is>
       </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>0.5%</t>
-        </is>
-      </c>
       <c r="G54" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="55">
@@ -2193,22 +2193,22 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>GDP Growth Annualized PrelQ4</t>
+          <t>GDP Price Index YoY PrelQ4</t>
         </is>
       </c>
       <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr">
         <is>
-          <t>1%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2.1%</t>
+          <t>2.6%</t>
         </is>
       </c>
       <c r="G55" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="56">
@@ -2224,22 +2224,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>GDP External Demand QoQ PrelQ4</t>
+          <t>GDP Growth Rate QoQ PrelQ4</t>
         </is>
       </c>
       <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="G56" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="57">
@@ -2255,14 +2255,18 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>GDP Price Index YoY PrelQ4</t>
+          <t>GDP External Demand QoQ PrelQ4</t>
         </is>
       </c>
       <c r="D57" t="inlineStr"/>
-      <c r="E57" t="inlineStr"/>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -2282,18 +2286,18 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>GDP Private Consumption QoQ PrelQ4</t>
+          <t>GDP Capital Expenditure QoQ PrelQ4</t>
         </is>
       </c>
       <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr">
         <is>
-          <t>-0.3%</t>
+          <t>1%</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -2402,18 +2406,22 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Exports YoYJAN</t>
+          <t>Balance of TradeJAN</t>
         </is>
       </c>
       <c r="D62" t="inlineStr"/>
       <c r="E62" t="inlineStr">
         <is>
-          <t>6.99%</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr"/>
+          <t>$1.91B</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>$2.2B</t>
+        </is>
+      </c>
       <c r="G62" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="63">
@@ -2429,22 +2437,18 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Balance of TradeJAN</t>
+          <t>Exports YoYJAN</t>
         </is>
       </c>
       <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr">
         <is>
-          <t>$1.91B</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>$2.2B</t>
-        </is>
-      </c>
+          <t>6.99%</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr"/>
       <c r="G63" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="64">
@@ -2482,19 +2486,19 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Vehicle Sales YoYJAN</t>
+          <t>Industrial Production YoY FinalDEC</t>
         </is>
       </c>
       <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr"/>
       <c r="F65" t="inlineStr">
         <is>
-          <t>12.0%</t>
+          <t>-1.6%</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -2509,23 +2513,19 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>SA</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Inflation Rate MoMJAN</t>
+          <t>Vehicle Sales YoYJAN</t>
         </is>
       </c>
       <c r="D66" t="inlineStr"/>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
+      <c r="E66" t="inlineStr"/>
       <c r="F66" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>12.0%</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -2545,18 +2545,18 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Inflation Rate YoYJAN</t>
+          <t>Inflation Rate MoMJAN</t>
         </is>
       </c>
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr">
         <is>
-          <t>1.9%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2.0%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -2576,14 +2576,18 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Wholesale Prices YoYJAN</t>
+          <t>Inflation Rate YoYJAN</t>
         </is>
       </c>
       <c r="D68" t="inlineStr"/>
-      <c r="E68" t="inlineStr"/>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>1.9%</t>
+        </is>
+      </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>1.3%</t>
+          <t>2.0%</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -2598,17 +2602,21 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>EA</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Eurogroup Meeting</t>
+          <t>Wholesale Prices YoYJAN</t>
         </is>
       </c>
       <c r="D69" t="inlineStr"/>
       <c r="E69" t="inlineStr"/>
-      <c r="F69" t="inlineStr"/>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>1.3%</t>
+        </is>
+      </c>
       <c r="G69" t="n">
         <v>3</v>
       </c>
@@ -2621,25 +2629,17 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>EA</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Tertiary Industry Index MoMDEC</t>
+          <t>Eurogroup Meeting</t>
         </is>
       </c>
       <c r="D70" t="inlineStr"/>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>0.1%</t>
-        </is>
-      </c>
+      <c r="E70" t="inlineStr"/>
+      <c r="F70" t="inlineStr"/>
       <c r="G70" t="n">
         <v>3</v>
       </c>
@@ -2657,14 +2657,18 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Industrial Production YoY FinalDEC</t>
+          <t>Industrial Production MoM FinalDEC</t>
         </is>
       </c>
       <c r="D71" t="inlineStr"/>
-      <c r="E71" t="inlineStr"/>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>-1.6%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -2684,14 +2688,18 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Capacity Utilization MoMDEC</t>
+          <t>Tertiary Industry Index MoMDEC</t>
         </is>
       </c>
       <c r="D72" t="inlineStr"/>
-      <c r="E72" t="inlineStr"/>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -2711,18 +2719,14 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Industrial Production MoM FinalDEC</t>
+          <t>Capacity Utilization MoMDEC</t>
         </is>
       </c>
       <c r="D73" t="inlineStr"/>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+      <c r="E73" t="inlineStr"/>
       <c r="F73" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -2760,7 +2764,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -2769,14 +2773,10 @@
         </is>
       </c>
       <c r="D75" t="inlineStr"/>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>€4.35B</t>
-        </is>
-      </c>
+      <c r="E75" t="inlineStr"/>
       <c r="F75" t="inlineStr">
         <is>
-          <t>€4.5B</t>
+          <t>€ -4.9B</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -2791,7 +2791,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -2800,10 +2800,14 @@
         </is>
       </c>
       <c r="D76" t="inlineStr"/>
-      <c r="E76" t="inlineStr"/>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>€4.35B</t>
+        </is>
+      </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>€ -4.9B</t>
+          <t>€4.5B</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -2827,7 +2831,11 @@
         </is>
       </c>
       <c r="D77" t="inlineStr"/>
-      <c r="E77" t="inlineStr"/>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>€14.4B</t>
+        </is>
+      </c>
       <c r="F77" t="inlineStr">
         <is>
           <t>€ 33B</t>
@@ -2954,15 +2962,11 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Foreign Securities PurchasesDEC</t>
+          <t>Foreign Securities Purchases by CanadiansDEC</t>
         </is>
       </c>
       <c r="D82" t="inlineStr"/>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>C$14.23B</t>
-        </is>
-      </c>
+      <c r="E82" t="inlineStr"/>
       <c r="F82" t="inlineStr"/>
       <c r="G82" t="n">
         <v>3</v>
@@ -2981,11 +2985,15 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Foreign Securities Purchases by CanadiansDEC</t>
+          <t>Foreign Securities PurchasesDEC</t>
         </is>
       </c>
       <c r="D83" t="inlineStr"/>
-      <c r="E83" t="inlineStr"/>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>C$14.23B</t>
+        </is>
+      </c>
       <c r="F83" t="inlineStr"/>
       <c r="G83" t="n">
         <v>3</v>
@@ -3219,14 +3227,14 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Budget BalanceJAN</t>
+          <t>Auto Sales YoYJAN</t>
         </is>
       </c>
       <c r="D93" t="inlineStr"/>
       <c r="E93" t="inlineStr"/>
       <c r="F93" t="inlineStr">
         <is>
-          <t>TRY-150.0B</t>
+          <t>6.0%</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -3241,19 +3249,19 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>TR</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Balance of TradeJAN</t>
+          <t>Budget BalanceJAN</t>
         </is>
       </c>
       <c r="D94" t="inlineStr"/>
       <c r="E94" t="inlineStr"/>
       <c r="F94" t="inlineStr">
         <is>
-          <t>$-24.0B</t>
+          <t>TRY-150.0B</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -3273,12 +3281,16 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>ExportsJAN</t>
+          <t>Balance of TradeJAN</t>
         </is>
       </c>
       <c r="D95" t="inlineStr"/>
       <c r="E95" t="inlineStr"/>
-      <c r="F95" t="inlineStr"/>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>$-24.0B</t>
+        </is>
+      </c>
       <c r="G95" t="n">
         <v>2</v>
       </c>
@@ -3291,12 +3303,12 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>EU</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>European Commission Winter Forecasts</t>
+          <t>ImportsJAN</t>
         </is>
       </c>
       <c r="D96" t="inlineStr"/>
@@ -3314,12 +3326,12 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>EU</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>BCB Focus Market Readout</t>
+          <t>European Commission Winter Forecasts</t>
         </is>
       </c>
       <c r="D97" t="inlineStr"/>
@@ -3337,12 +3349,12 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>EA</t>
+          <t>BR</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>ECOFIN Meeting</t>
+          <t>BCB Focus Market Readout</t>
         </is>
       </c>
       <c r="D98" t="inlineStr"/>
@@ -3360,21 +3372,17 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>TR</t>
+          <t>EA</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Auto Sales YoYJAN</t>
+          <t>ECOFIN Meeting</t>
         </is>
       </c>
       <c r="D99" t="inlineStr"/>
       <c r="E99" t="inlineStr"/>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>6.0%</t>
-        </is>
-      </c>
+      <c r="F99" t="inlineStr"/>
       <c r="G99" t="n">
         <v>2</v>
       </c>
@@ -3419,7 +3427,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>ImportsJAN</t>
+          <t>ExportsJAN</t>
         </is>
       </c>
       <c r="D101" t="inlineStr"/>
@@ -3511,14 +3519,18 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>HMRC Payrolls ChangeJAN</t>
+          <t>Average Earnings excl. Bonus (3Mo/Yr)DEC</t>
         </is>
       </c>
       <c r="D105" t="inlineStr"/>
-      <c r="E105" t="inlineStr"/>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>5.9%</t>
+        </is>
+      </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>-55.0K</t>
+          <t>5.9%</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -3538,18 +3550,18 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Average Earnings excl. Bonus (3Mo/Yr)DEC</t>
+          <t>Employment ChangeDEC</t>
         </is>
       </c>
       <c r="D106" t="inlineStr"/>
       <c r="E106" t="inlineStr"/>
       <c r="F106" t="inlineStr">
         <is>
-          <t>5.9%</t>
+          <t>-130K</t>
         </is>
       </c>
       <c r="G106" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="107">
@@ -3565,14 +3577,18 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Employment ChangeDEC</t>
+          <t>Average Earnings incl. Bonus (3Mo/Yr)DEC</t>
         </is>
       </c>
       <c r="D107" t="inlineStr"/>
-      <c r="E107" t="inlineStr"/>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>5.9%</t>
+        </is>
+      </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>-130K</t>
+          <t>5.9%</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -3592,22 +3608,22 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Average Earnings incl. Bonus (3Mo/Yr)DEC</t>
+          <t>Unemployment RateDEC</t>
         </is>
       </c>
       <c r="D108" t="inlineStr"/>
       <c r="E108" t="inlineStr">
         <is>
-          <t>5.9%</t>
+          <t>4.5%</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>5.9%</t>
+          <t>4.4%</t>
         </is>
       </c>
       <c r="G108" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="109">
@@ -3623,22 +3639,22 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Unemployment RateDEC</t>
+          <t>Claimant Count ChangeJAN</t>
         </is>
       </c>
       <c r="D109" t="inlineStr"/>
       <c r="E109" t="inlineStr">
         <is>
-          <t>4.5%</t>
+          <t>10K</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>4.4%</t>
+          <t>7.0K</t>
         </is>
       </c>
       <c r="G109" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="110">
@@ -3654,18 +3670,14 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Claimant Count ChangeJAN</t>
+          <t>HMRC Payrolls ChangeJAN</t>
         </is>
       </c>
       <c r="D110" t="inlineStr"/>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>10K</t>
-        </is>
-      </c>
+      <c r="E110" t="inlineStr"/>
       <c r="F110" t="inlineStr">
         <is>
-          <t>7.0K</t>
+          <t>-55.0K</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -3685,18 +3697,18 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Inflation Rate YoY FinalJAN</t>
+          <t>Inflation Rate MoM FinalJAN</t>
         </is>
       </c>
       <c r="D111" t="inlineStr"/>
       <c r="E111" t="inlineStr">
         <is>
-          <t>1.4%</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>1.4%</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -3716,18 +3728,18 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Harmonised Inflation Rate YoY FinalJAN</t>
+          <t>Harmonised Inflation Rate MoM FinalJAN</t>
         </is>
       </c>
       <c r="D112" t="inlineStr"/>
       <c r="E112" t="inlineStr">
         <is>
-          <t>1.8%</t>
+          <t>-0.2%</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>1.8%</t>
+          <t>-0.2%</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -3747,18 +3759,18 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Harmonised Inflation Rate MoM FinalJAN</t>
+          <t>Harmonised Inflation Rate YoY FinalJAN</t>
         </is>
       </c>
       <c r="D113" t="inlineStr"/>
       <c r="E113" t="inlineStr">
         <is>
-          <t>-0.2%</t>
+          <t>1.8%</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>-0.2%</t>
+          <t>1.8%</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -3778,18 +3790,18 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Inflation Rate MoM FinalJAN</t>
+          <t>Inflation Rate YoY FinalJAN</t>
         </is>
       </c>
       <c r="D114" t="inlineStr"/>
       <c r="E114" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>1.4%</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>1.4%</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -3831,23 +3843,19 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>ZA</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Unemployed PersonsQ4</t>
+          <t>BoE Gov Bailey Speech</t>
         </is>
       </c>
       <c r="D116" t="inlineStr"/>
       <c r="E116" t="inlineStr"/>
-      <c r="F116" t="inlineStr">
-        <is>
-          <t>8.1M</t>
-        </is>
-      </c>
+      <c r="F116" t="inlineStr"/>
       <c r="G116" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="117">
@@ -3916,19 +3924,23 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>ZA</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>BoE Gov Bailey Speech</t>
+          <t>Unemployed PersonsQ4</t>
         </is>
       </c>
       <c r="D119" t="inlineStr"/>
       <c r="E119" t="inlineStr"/>
-      <c r="F119" t="inlineStr"/>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>8.1M</t>
+        </is>
+      </c>
       <c r="G119" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="120">
@@ -3939,19 +3951,27 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>40-Year Treasury Gilt Auction</t>
+          <t>ZEW Economic Sentiment IndexFEB</t>
         </is>
       </c>
       <c r="D120" t="inlineStr"/>
-      <c r="E120" t="inlineStr"/>
-      <c r="F120" t="inlineStr"/>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
       <c r="G120" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="121">
@@ -3962,23 +3982,19 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>EA</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>ZEW Economic Sentiment IndexFEB</t>
+          <t>40-Year Treasury Gilt Auction</t>
         </is>
       </c>
       <c r="D121" t="inlineStr"/>
       <c r="E121" t="inlineStr"/>
-      <c r="F121" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
+      <c r="F121" t="inlineStr"/>
       <c r="G121" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="122">
@@ -3994,22 +4010,22 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>ZEW Economic Sentiment IndexFEB</t>
+          <t>ZEW Current ConditionsFEB</t>
         </is>
       </c>
       <c r="D122" t="inlineStr"/>
       <c r="E122" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>-89</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>-89</t>
         </is>
       </c>
       <c r="G122" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="123">
@@ -4020,27 +4036,27 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>EA</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>ZEW Current ConditionsFEB</t>
+          <t>ZEW Economic Sentiment IndexFEB</t>
         </is>
       </c>
       <c r="D123" t="inlineStr"/>
       <c r="E123" t="inlineStr">
         <is>
-          <t>-89</t>
+          <t>24.3</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>-89</t>
+          <t>15</t>
         </is>
       </c>
       <c r="G123" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="124">
@@ -4074,27 +4090,23 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>NY Empire State Manufacturing IndexFEB</t>
+          <t>Core Inflation Rate MoMJAN</t>
         </is>
       </c>
       <c r="D125" t="inlineStr"/>
-      <c r="E125" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
+      <c r="E125" t="inlineStr"/>
       <c r="F125" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="G125" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="126">
@@ -4110,22 +4122,22 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>CPI Trimmed-Mean YoYJAN</t>
+          <t>Inflation Rate MoMJAN</t>
         </is>
       </c>
       <c r="D126" t="inlineStr"/>
       <c r="E126" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G126" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="127">
@@ -4136,27 +4148,27 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>US</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>CPI Median YoYJAN</t>
+          <t>NY Empire State Manufacturing IndexFEB</t>
         </is>
       </c>
       <c r="D127" t="inlineStr"/>
       <c r="E127" t="inlineStr">
         <is>
-          <t>2.4%</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>2.4%</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G127" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="128">
@@ -4172,18 +4184,18 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Core Inflation Rate MoMJAN</t>
+          <t>Inflation Rate YoYJAN</t>
         </is>
       </c>
       <c r="D128" t="inlineStr"/>
       <c r="E128" t="inlineStr"/>
       <c r="F128" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>1.8%</t>
         </is>
       </c>
       <c r="G128" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="129">
@@ -4226,18 +4238,22 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Inflation Rate YoYJAN</t>
+          <t>CPI Median YoYJAN</t>
         </is>
       </c>
       <c r="D130" t="inlineStr"/>
-      <c r="E130" t="inlineStr"/>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>2.4%</t>
+        </is>
+      </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>1.8%</t>
+          <t>2.4%</t>
         </is>
       </c>
       <c r="G130" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="131">
@@ -4253,22 +4269,22 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Inflation Rate MoMJAN</t>
+          <t>CPI Trimmed-Mean YoYJAN</t>
         </is>
       </c>
       <c r="D131" t="inlineStr"/>
       <c r="E131" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>2.6%</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="G131" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="132">
@@ -4333,19 +4349,19 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Fed Daly Speech</t>
+          <t>Bundesbank Balz Speech</t>
         </is>
       </c>
       <c r="D134" t="inlineStr"/>
       <c r="E134" t="inlineStr"/>
       <c r="F134" t="inlineStr"/>
       <c r="G134" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="135">
@@ -4356,19 +4372,19 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>US</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Bundesbank Balz Speech</t>
+          <t>Fed Daly Speech</t>
         </is>
       </c>
       <c r="D135" t="inlineStr"/>
       <c r="E135" t="inlineStr"/>
       <c r="F135" t="inlineStr"/>
       <c r="G135" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="136">
@@ -4549,14 +4565,14 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Net Long-term TIC FlowsDEC</t>
+          <t>Foreign Bond InvestmentDEC</t>
         </is>
       </c>
       <c r="D143" t="inlineStr"/>
       <c r="E143" t="inlineStr"/>
       <c r="F143" t="inlineStr"/>
       <c r="G143" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="144">
@@ -4572,14 +4588,18 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Foreign Bond InvestmentDEC</t>
+          <t>Net Long-term TIC FlowsDEC</t>
         </is>
       </c>
       <c r="D144" t="inlineStr"/>
-      <c r="E144" t="inlineStr"/>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>$149.1B</t>
+        </is>
+      </c>
       <c r="F144" t="inlineStr"/>
       <c r="G144" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="145">
@@ -4626,18 +4646,18 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Machinery Orders MoMDEC</t>
+          <t>Machinery Orders YoYDEC</t>
         </is>
       </c>
       <c r="D146" t="inlineStr"/>
       <c r="E146" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>6.9%</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>7.6%</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -4719,18 +4739,18 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Machinery Orders YoYDEC</t>
+          <t>Machinery Orders MoMDEC</t>
         </is>
       </c>
       <c r="D149" t="inlineStr"/>
       <c r="E149" t="inlineStr">
         <is>
-          <t>6.9%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>7.6%</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -4777,12 +4797,20 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>RBA Chart Pack</t>
+          <t>Wage Price Index YoYQ4</t>
         </is>
       </c>
       <c r="D151" t="inlineStr"/>
-      <c r="E151" t="inlineStr"/>
-      <c r="F151" t="inlineStr"/>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>3.2%</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>3.3%</t>
+        </is>
+      </c>
       <c r="G151" t="n">
         <v>3</v>
       </c>
@@ -4800,20 +4828,12 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Wage Price Index QoQQ4</t>
+          <t>RBA Chart Pack</t>
         </is>
       </c>
       <c r="D152" t="inlineStr"/>
-      <c r="E152" t="inlineStr">
-        <is>
-          <t>0.8%</t>
-        </is>
-      </c>
-      <c r="F152" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
+      <c r="E152" t="inlineStr"/>
+      <c r="F152" t="inlineStr"/>
       <c r="G152" t="n">
         <v>3</v>
       </c>
@@ -4831,18 +4851,18 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Wage Price Index YoYQ4</t>
+          <t>Wage Price Index QoQQ4</t>
         </is>
       </c>
       <c r="D153" t="inlineStr"/>
       <c r="E153" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>0.8%</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -4884,12 +4904,12 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>ZA</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>52-Week Bill Auction</t>
+          <t>Annual Budget Speech</t>
         </is>
       </c>
       <c r="D155" t="inlineStr"/>
@@ -4907,12 +4927,12 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>ZA</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Annual Budget Speech</t>
+          <t>52-Week Bill Auction</t>
         </is>
       </c>
       <c r="D156" t="inlineStr"/>
@@ -4935,14 +4955,14 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>PPI Core Output YoYJAN</t>
+          <t>PPI Core Output MoMJAN</t>
         </is>
       </c>
       <c r="D157" t="inlineStr"/>
       <c r="E157" t="inlineStr"/>
       <c r="F157" t="inlineStr">
         <is>
-          <t>1.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -4962,14 +4982,14 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>PPI Core Output MoMJAN</t>
+          <t>Core Inflation Rate MoMJAN</t>
         </is>
       </c>
       <c r="D158" t="inlineStr"/>
       <c r="E158" t="inlineStr"/>
       <c r="F158" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>-0.7%</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -4989,18 +5009,18 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Core Inflation Rate MoMJAN</t>
+          <t>Inflation Rate MoMJAN</t>
         </is>
       </c>
       <c r="D159" t="inlineStr"/>
       <c r="E159" t="inlineStr"/>
       <c r="F159" t="inlineStr">
         <is>
-          <t>-0.7%</t>
+          <t>-0.3%</t>
         </is>
       </c>
       <c r="G159" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="160">
@@ -5016,14 +5036,18 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Inflation Rate MoMJAN</t>
+          <t>Core Inflation Rate YoYJAN</t>
         </is>
       </c>
       <c r="D160" t="inlineStr"/>
-      <c r="E160" t="inlineStr"/>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>3.7%</t>
+        </is>
+      </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>-0.3%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="G160" t="n">
@@ -5043,22 +5067,22 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Core Inflation Rate YoYJAN</t>
+          <t>Inflation Rate YoYJAN</t>
         </is>
       </c>
       <c r="D161" t="inlineStr"/>
       <c r="E161" t="inlineStr">
         <is>
-          <t>3.7%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>2.7%</t>
         </is>
       </c>
       <c r="G161" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="162">
@@ -5074,22 +5098,18 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Inflation Rate YoYJAN</t>
+          <t>PPI Input YoYJAN</t>
         </is>
       </c>
       <c r="D162" t="inlineStr"/>
-      <c r="E162" t="inlineStr">
-        <is>
-          <t>2.8%</t>
-        </is>
-      </c>
+      <c r="E162" t="inlineStr"/>
       <c r="F162" t="inlineStr">
         <is>
-          <t>2.7%</t>
+          <t>-0.8%</t>
         </is>
       </c>
       <c r="G162" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="163">
@@ -5105,14 +5125,18 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Retail Price Index MoMJAN</t>
+          <t>PPI Output MoMJAN</t>
         </is>
       </c>
       <c r="D163" t="inlineStr"/>
-      <c r="E163" t="inlineStr"/>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G163" t="n">
@@ -5132,18 +5156,14 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>PPI Input MoMJAN</t>
+          <t>PPI Output YoYJAN</t>
         </is>
       </c>
       <c r="D164" t="inlineStr"/>
-      <c r="E164" t="inlineStr">
-        <is>
-          <t>0.7%</t>
-        </is>
-      </c>
+      <c r="E164" t="inlineStr"/>
       <c r="F164" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G164" t="n">
@@ -5163,14 +5183,14 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>PPI Output YoYJAN</t>
+          <t>Retail Price Index MoMJAN</t>
         </is>
       </c>
       <c r="D165" t="inlineStr"/>
       <c r="E165" t="inlineStr"/>
       <c r="F165" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="G165" t="n">
@@ -5221,18 +5241,14 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>PPI Output MoMJAN</t>
+          <t>PPI Core Output YoYJAN</t>
         </is>
       </c>
       <c r="D167" t="inlineStr"/>
-      <c r="E167" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
+      <c r="E167" t="inlineStr"/>
       <c r="F167" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>1.3%</t>
         </is>
       </c>
       <c r="G167" t="n">
@@ -5252,14 +5268,18 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>PPI Input YoYJAN</t>
+          <t>PPI Input MoMJAN</t>
         </is>
       </c>
       <c r="D168" t="inlineStr"/>
-      <c r="E168" t="inlineStr"/>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>0.7%</t>
+        </is>
+      </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>-0.8%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="G168" t="n">
@@ -5306,22 +5326,22 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Interest Rate Decision</t>
+          <t>Deposit Facility RateFEB</t>
         </is>
       </c>
       <c r="D170" t="inlineStr"/>
       <c r="E170" t="inlineStr">
         <is>
-          <t>5.75%</t>
+          <t>5%</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>5.75%</t>
+          <t>5%</t>
         </is>
       </c>
       <c r="G170" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="171">
@@ -5368,22 +5388,22 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Deposit Facility RateFEB</t>
+          <t>Interest Rate Decision</t>
         </is>
       </c>
       <c r="D172" t="inlineStr"/>
       <c r="E172" t="inlineStr">
         <is>
-          <t>5%</t>
+          <t>5.75%</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>5%</t>
+          <t>5.75%</t>
         </is>
       </c>
       <c r="G172" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="173">
@@ -5399,18 +5419,18 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Inflation Rate YoYJAN</t>
+          <t>Core Inflation Rate YoYJAN</t>
         </is>
       </c>
       <c r="D173" t="inlineStr"/>
       <c r="E173" t="inlineStr"/>
       <c r="F173" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>3.6%</t>
         </is>
       </c>
       <c r="G173" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="174">
@@ -5421,21 +5441,17 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>ZA</t>
+          <t>EA</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Core Inflation Rate YoYJAN</t>
+          <t>ECB Non-Monetary Policy Meeting</t>
         </is>
       </c>
       <c r="D174" t="inlineStr"/>
       <c r="E174" t="inlineStr"/>
-      <c r="F174" t="inlineStr">
-        <is>
-          <t>3.6%</t>
-        </is>
-      </c>
+      <c r="F174" t="inlineStr"/>
       <c r="G174" t="n">
         <v>3</v>
       </c>
@@ -5453,7 +5469,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Core Inflation Rate MoMJAN</t>
+          <t>Inflation Rate MoMJAN</t>
         </is>
       </c>
       <c r="D175" t="inlineStr"/>
@@ -5464,7 +5480,7 @@
         </is>
       </c>
       <c r="G175" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="176">
@@ -5480,14 +5496,14 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Inflation Rate MoMJAN</t>
+          <t>Inflation Rate YoYJAN</t>
         </is>
       </c>
       <c r="D176" t="inlineStr"/>
       <c r="E176" t="inlineStr"/>
       <c r="F176" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="G176" t="n">
@@ -5502,17 +5518,21 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>EA</t>
+          <t>ZA</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>ECB Non-Monetary Policy Meeting</t>
+          <t>Core Inflation Rate MoMJAN</t>
         </is>
       </c>
       <c r="D177" t="inlineStr"/>
       <c r="E177" t="inlineStr"/>
-      <c r="F177" t="inlineStr"/>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>0.1%</t>
+        </is>
+      </c>
       <c r="G177" t="n">
         <v>3</v>
       </c>
@@ -5583,21 +5603,17 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Current AccountDEC</t>
+          <t>4-Year Treasury Gilt Auction</t>
         </is>
       </c>
       <c r="D180" t="inlineStr"/>
       <c r="E180" t="inlineStr"/>
-      <c r="F180" t="inlineStr">
-        <is>
-          <t>€ 3780M</t>
-        </is>
-      </c>
+      <c r="F180" t="inlineStr"/>
       <c r="G180" t="n">
         <v>3</v>
       </c>
@@ -5610,17 +5626,21 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>4-Year Treasury Gilt Auction</t>
+          <t>Current AccountDEC</t>
         </is>
       </c>
       <c r="D181" t="inlineStr"/>
       <c r="E181" t="inlineStr"/>
-      <c r="F181" t="inlineStr"/>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>€ 3780M</t>
+        </is>
+      </c>
       <c r="G181" t="n">
         <v>3</v>
       </c>
@@ -5830,7 +5850,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexFEB/14</t>
+          <t>MBA Purchase IndexFEB/14</t>
         </is>
       </c>
       <c r="D190" t="inlineStr"/>
@@ -5876,7 +5896,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexFEB/14</t>
+          <t>MBA Mortgage Market IndexFEB/14</t>
         </is>
       </c>
       <c r="D192" t="inlineStr"/>
@@ -5899,14 +5919,14 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Building Permits MoM PrelJAN</t>
+          <t>Housing Starts MoMJAN</t>
         </is>
       </c>
       <c r="D193" t="inlineStr"/>
       <c r="E193" t="inlineStr"/>
       <c r="F193" t="inlineStr">
         <is>
-          <t>-0.8%</t>
+          <t>-9.0%</t>
         </is>
       </c>
       <c r="G193" t="n">
@@ -5926,14 +5946,14 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Housing Starts MoMJAN</t>
+          <t>Building Permits MoM PrelJAN</t>
         </is>
       </c>
       <c r="D194" t="inlineStr"/>
       <c r="E194" t="inlineStr"/>
       <c r="F194" t="inlineStr">
         <is>
-          <t>-9.0%</t>
+          <t>-0.8%</t>
         </is>
       </c>
       <c r="G194" t="n">
@@ -6065,14 +6085,14 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>PPI MoMJAN</t>
+          <t>PPI YoYJAN</t>
         </is>
       </c>
       <c r="D199" t="inlineStr"/>
       <c r="E199" t="inlineStr"/>
       <c r="F199" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>8.2%</t>
         </is>
       </c>
       <c r="G199" t="n">
@@ -6092,14 +6112,14 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>PPI YoYJAN</t>
+          <t>PPI MoMJAN</t>
         </is>
       </c>
       <c r="D200" t="inlineStr"/>
       <c r="E200" t="inlineStr"/>
       <c r="F200" t="inlineStr">
         <is>
-          <t>8.2%</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="G200" t="n">
@@ -6535,14 +6555,18 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Loan Prime Rate 1Y</t>
+          <t>Loan Prime Rate 5YFEB</t>
         </is>
       </c>
       <c r="D217" t="inlineStr"/>
-      <c r="E217" t="inlineStr"/>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>3.6%</t>
+        </is>
+      </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>3.1%</t>
+          <t>3.6%</t>
         </is>
       </c>
       <c r="G217" t="n">
@@ -6562,14 +6586,18 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Loan Prime Rate 5YFEB</t>
+          <t>Loan Prime Rate 1Y</t>
         </is>
       </c>
       <c r="D218" t="inlineStr"/>
-      <c r="E218" t="inlineStr"/>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>3.1%</t>
+        </is>
+      </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>3.6%</t>
+          <t>3.1%</t>
         </is>
       </c>
       <c r="G218" t="n">
@@ -6589,12 +6617,16 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>M2 Money Supply YoYJAN</t>
+          <t>Current AccountQ4</t>
         </is>
       </c>
       <c r="D219" t="inlineStr"/>
       <c r="E219" t="inlineStr"/>
-      <c r="F219" t="inlineStr"/>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>$ -0.6B</t>
+        </is>
+      </c>
       <c r="G219" t="n">
         <v>3</v>
       </c>
@@ -6666,16 +6698,12 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Current AccountQ4</t>
+          <t>M2 Money Supply YoYJAN</t>
         </is>
       </c>
       <c r="D222" t="inlineStr"/>
       <c r="E222" t="inlineStr"/>
-      <c r="F222" t="inlineStr">
-        <is>
-          <t>$ -0.6B</t>
-        </is>
-      </c>
+      <c r="F222" t="inlineStr"/>
       <c r="G222" t="n">
         <v>3</v>
       </c>
@@ -6805,7 +6833,7 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>3-Year Bonos Auction</t>
+          <t>8-Year Obligacion Auction</t>
         </is>
       </c>
       <c r="D227" t="inlineStr"/>
@@ -6828,7 +6856,7 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>8-Year Obligacion Auction</t>
+          <t>5-Year Bonos Auction</t>
         </is>
       </c>
       <c r="D228" t="inlineStr"/>
@@ -6851,7 +6879,7 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>5-Year Bonos Auction</t>
+          <t>3-Year Bonos Auction</t>
         </is>
       </c>
       <c r="D229" t="inlineStr"/>
@@ -6993,7 +7021,7 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>18-Year Index-Linked OAT Auction</t>
+          <t>6-Year Index-Linked OAT Auction</t>
         </is>
       </c>
       <c r="D235" t="inlineStr"/>
@@ -7034,23 +7062,27 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>ZA</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Building Permits YoYDEC</t>
+          <t>CBI Industrial Trends OrdersFEB</t>
         </is>
       </c>
       <c r="D237" t="inlineStr"/>
-      <c r="E237" t="inlineStr"/>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>-30</t>
+        </is>
+      </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>18.0%</t>
+          <t>-25</t>
         </is>
       </c>
       <c r="G237" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="238">
@@ -7061,27 +7093,23 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>ZA</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>CBI Industrial Trends OrdersFEB</t>
+          <t>Building Permits YoYDEC</t>
         </is>
       </c>
       <c r="D238" t="inlineStr"/>
-      <c r="E238" t="inlineStr">
-        <is>
-          <t>-30</t>
-        </is>
-      </c>
+      <c r="E238" t="inlineStr"/>
       <c r="F238" t="inlineStr">
         <is>
-          <t>-25</t>
+          <t>18.0%</t>
         </is>
       </c>
       <c r="G238" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="239">
@@ -7097,7 +7125,7 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>6-Year Index-Linked OAT Auction</t>
+          <t>18-Year Index-Linked OAT Auction</t>
         </is>
       </c>
       <c r="D239" t="inlineStr"/>
@@ -7197,18 +7225,18 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Philadelphia Fed Manufacturing IndexFEB</t>
+          <t>Initial Jobless ClaimsFEB/15</t>
         </is>
       </c>
       <c r="D243" t="inlineStr"/>
       <c r="E243" t="inlineStr">
         <is>
-          <t>25.5</t>
+          <t>216K</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>220.0K</t>
         </is>
       </c>
       <c r="G243" t="n">
@@ -7228,12 +7256,16 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Philly Fed Business ConditionsFEB</t>
+          <t>Jobless Claims 4-week AverageFEB/15</t>
         </is>
       </c>
       <c r="D244" t="inlineStr"/>
       <c r="E244" t="inlineStr"/>
-      <c r="F244" t="inlineStr"/>
+      <c r="F244" t="inlineStr">
+        <is>
+          <t>219.0K</t>
+        </is>
+      </c>
       <c r="G244" t="n">
         <v>3</v>
       </c>
@@ -7251,18 +7283,22 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/08</t>
+          <t>Philadelphia Fed Manufacturing IndexFEB</t>
         </is>
       </c>
       <c r="D245" t="inlineStr"/>
-      <c r="E245" t="inlineStr"/>
+      <c r="E245" t="inlineStr">
+        <is>
+          <t>25.5</t>
+        </is>
+      </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>1879.0K</t>
+          <t>18</t>
         </is>
       </c>
       <c r="G245" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="246">
@@ -7278,14 +7314,14 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/15</t>
+          <t>Continuing Jobless ClaimsFEB/08</t>
         </is>
       </c>
       <c r="D246" t="inlineStr"/>
       <c r="E246" t="inlineStr"/>
       <c r="F246" t="inlineStr">
         <is>
-          <t>219.0K</t>
+          <t>1879.0K</t>
         </is>
       </c>
       <c r="G246" t="n">
@@ -7305,7 +7341,7 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Philly Fed CAPEX IndexFEB</t>
+          <t>Philly Fed Business ConditionsFEB</t>
         </is>
       </c>
       <c r="D247" t="inlineStr"/>
@@ -7328,7 +7364,7 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Philly Fed EmploymentFEB</t>
+          <t>Philly Fed CAPEX IndexFEB</t>
         </is>
       </c>
       <c r="D248" t="inlineStr"/>
@@ -7351,7 +7387,7 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Philly Fed New OrdersFEB</t>
+          <t>Philly Fed EmploymentFEB</t>
         </is>
       </c>
       <c r="D249" t="inlineStr"/>
@@ -7374,7 +7410,7 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Philly Fed Prices PaidFEB</t>
+          <t>Philly Fed New OrdersFEB</t>
         </is>
       </c>
       <c r="D250" t="inlineStr"/>
@@ -7392,21 +7428,17 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>US</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Raw Materials Prices YoYJAN</t>
+          <t>Philly Fed Prices PaidFEB</t>
         </is>
       </c>
       <c r="D251" t="inlineStr"/>
       <c r="E251" t="inlineStr"/>
-      <c r="F251" t="inlineStr">
-        <is>
-          <t>10.0%</t>
-        </is>
-      </c>
+      <c r="F251" t="inlineStr"/>
       <c r="G251" t="n">
         <v>3</v>
       </c>
@@ -7446,27 +7478,23 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/15</t>
+          <t>PPI YoYJAN</t>
         </is>
       </c>
       <c r="D253" t="inlineStr"/>
-      <c r="E253" t="inlineStr">
-        <is>
-          <t>216K</t>
-        </is>
-      </c>
+      <c r="E253" t="inlineStr"/>
       <c r="F253" t="inlineStr">
         <is>
-          <t>220.0K</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="G253" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="254">
@@ -7482,14 +7510,14 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>PPI MoMJAN</t>
+          <t>Raw Materials Prices YoYJAN</t>
         </is>
       </c>
       <c r="D254" t="inlineStr"/>
       <c r="E254" t="inlineStr"/>
       <c r="F254" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>10.0%</t>
         </is>
       </c>
       <c r="G254" t="n">
@@ -7509,14 +7537,14 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>New Housing Price Index MoMJAN</t>
+          <t>New Housing Price Index YoYJAN</t>
         </is>
       </c>
       <c r="D255" t="inlineStr"/>
       <c r="E255" t="inlineStr"/>
       <c r="F255" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G255" t="n">
@@ -7536,18 +7564,22 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>PPI YoYJAN</t>
+          <t>New Housing Price Index MoMJAN</t>
         </is>
       </c>
       <c r="D256" t="inlineStr"/>
-      <c r="E256" t="inlineStr"/>
+      <c r="E256" t="inlineStr">
+        <is>
+          <t>0.1%</t>
+        </is>
+      </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G256" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="257">
@@ -7563,18 +7595,18 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>New Housing Price Index YoYJAN</t>
+          <t>PPI MoMJAN</t>
         </is>
       </c>
       <c r="D257" t="inlineStr"/>
       <c r="E257" t="inlineStr"/>
       <c r="F257" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="G257" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="258">
@@ -7635,27 +7667,27 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>EA</t>
+          <t>US</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Consumer Confidence FlashFEB</t>
+          <t>CB Leading Index MoMJAN</t>
         </is>
       </c>
       <c r="D260" t="inlineStr"/>
       <c r="E260" t="inlineStr">
         <is>
-          <t>-14</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>-14.4</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G260" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="261">
@@ -7689,27 +7721,27 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>EA</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>CB Leading Index MoMJAN</t>
+          <t>Consumer Confidence FlashFEB</t>
         </is>
       </c>
       <c r="D262" t="inlineStr"/>
       <c r="E262" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-14</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-14.4</t>
         </is>
       </c>
       <c r="G262" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="263">
@@ -7817,7 +7849,7 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/14</t>
+          <t>15-Year Mortgage RateFEB/20</t>
         </is>
       </c>
       <c r="D267" t="inlineStr"/>
@@ -7840,7 +7872,7 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/14</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="D268" t="inlineStr"/>
@@ -7863,7 +7895,7 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/14</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/14</t>
         </is>
       </c>
       <c r="D269" t="inlineStr"/>
@@ -7886,7 +7918,7 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/14</t>
+          <t>EIA Distillate Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="D270" t="inlineStr"/>
@@ -7909,7 +7941,7 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateFEB/20</t>
+          <t>EIA Gasoline Production ChangeFEB/14</t>
         </is>
       </c>
       <c r="D271" t="inlineStr"/>
@@ -7978,7 +8010,7 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/14</t>
+          <t>EIA Crude Oil Imports ChangeFEB/14</t>
         </is>
       </c>
       <c r="D274" t="inlineStr"/>
@@ -8212,18 +8244,18 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>S&amp;P Global Australia Composite PMI FlashFEB</t>
+          <t>S&amp;P Global Australia Services PMI FlashFEB</t>
         </is>
       </c>
       <c r="D284" t="inlineStr"/>
       <c r="E284" t="inlineStr"/>
       <c r="F284" t="inlineStr">
         <is>
-          <t>50.6</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="G284" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="285">
@@ -8234,21 +8266,17 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>US</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>S&amp;P Global Australia Manufacturing PMI FlashFEB</t>
+          <t>Fed Kugler Speech</t>
         </is>
       </c>
       <c r="D285" t="inlineStr"/>
       <c r="E285" t="inlineStr"/>
-      <c r="F285" t="inlineStr">
-        <is>
-          <t>49.9</t>
-        </is>
-      </c>
+      <c r="F285" t="inlineStr"/>
       <c r="G285" t="n">
         <v>2</v>
       </c>
@@ -8266,14 +8294,14 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>S&amp;P Global Australia Services PMI FlashFEB</t>
+          <t>S&amp;P Global Australia Manufacturing PMI FlashFEB</t>
         </is>
       </c>
       <c r="D286" t="inlineStr"/>
       <c r="E286" t="inlineStr"/>
       <c r="F286" t="inlineStr">
         <is>
-          <t>51.3</t>
+          <t>49.9</t>
         </is>
       </c>
       <c r="G286" t="n">
@@ -8288,19 +8316,23 @@
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>Fed Kugler Speech</t>
+          <t>S&amp;P Global Australia Composite PMI FlashFEB</t>
         </is>
       </c>
       <c r="D287" t="inlineStr"/>
       <c r="E287" t="inlineStr"/>
-      <c r="F287" t="inlineStr"/>
+      <c r="F287" t="inlineStr">
+        <is>
+          <t>50.6</t>
+        </is>
+      </c>
       <c r="G287" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="288">
@@ -8486,22 +8518,18 @@
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>Jibun Bank Manufacturing PMI FlashFEB</t>
+          <t>Jibun Bank Composite PMI FlashFEB</t>
         </is>
       </c>
       <c r="D294" t="inlineStr"/>
-      <c r="E294" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
+      <c r="E294" t="inlineStr"/>
       <c r="F294" t="inlineStr">
         <is>
-          <t>49.6</t>
+          <t>51.5</t>
         </is>
       </c>
       <c r="G294" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="295">
@@ -8517,18 +8545,22 @@
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>Jibun Bank Composite PMI FlashFEB</t>
+          <t>Jibun Bank Manufacturing PMI FlashFEB</t>
         </is>
       </c>
       <c r="D295" t="inlineStr"/>
-      <c r="E295" t="inlineStr"/>
+      <c r="E295" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>51.5</t>
+          <t>49.6</t>
         </is>
       </c>
       <c r="G295" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="296">
@@ -8690,14 +8722,14 @@
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>HSBC Composite PMI FlashFEB</t>
+          <t>HSBC Services PMI FlashFEB</t>
         </is>
       </c>
       <c r="D302" t="inlineStr"/>
       <c r="E302" t="inlineStr"/>
       <c r="F302" t="inlineStr">
         <is>
-          <t>58.2</t>
+          <t>57.5</t>
         </is>
       </c>
       <c r="G302" t="n">
@@ -8717,14 +8749,14 @@
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>HSBC Services PMI FlashFEB</t>
+          <t>HSBC Manufacturing PMI FlashFEB</t>
         </is>
       </c>
       <c r="D303" t="inlineStr"/>
       <c r="E303" t="inlineStr"/>
       <c r="F303" t="inlineStr">
         <is>
-          <t>57.5</t>
+          <t>57.9</t>
         </is>
       </c>
       <c r="G303" t="n">
@@ -8744,14 +8776,14 @@
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>HSBC Manufacturing PMI FlashFEB</t>
+          <t>HSBC Composite PMI FlashFEB</t>
         </is>
       </c>
       <c r="D304" t="inlineStr"/>
       <c r="E304" t="inlineStr"/>
       <c r="F304" t="inlineStr">
         <is>
-          <t>57.9</t>
+          <t>58.2</t>
         </is>
       </c>
       <c r="G304" t="n">
@@ -8771,18 +8803,22 @@
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>Retail Sales YoYJAN</t>
+          <t>Retail Sales MoMJAN</t>
         </is>
       </c>
       <c r="D305" t="inlineStr"/>
-      <c r="E305" t="inlineStr"/>
+      <c r="E305" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>4.0%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G305" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="306">
@@ -8798,22 +8834,18 @@
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>Public Sector Net Borrowing Ex BanksJAN</t>
+          <t>Retail Sales YoYJAN</t>
         </is>
       </c>
       <c r="D306" t="inlineStr"/>
-      <c r="E306" t="inlineStr">
-        <is>
-          <t>£20.5B</t>
-        </is>
-      </c>
+      <c r="E306" t="inlineStr"/>
       <c r="F306" t="inlineStr">
         <is>
-          <t>£19.0B</t>
+          <t>4.0%</t>
         </is>
       </c>
       <c r="G306" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="307">
@@ -8829,14 +8861,18 @@
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>Retail Sales ex Fuel MoMJAN</t>
+          <t>Public Sector Net Borrowing Ex BanksJAN</t>
         </is>
       </c>
       <c r="D307" t="inlineStr"/>
-      <c r="E307" t="inlineStr"/>
+      <c r="E307" t="inlineStr">
+        <is>
+          <t>£20.5B</t>
+        </is>
+      </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>£19.0B</t>
         </is>
       </c>
       <c r="G307" t="n">
@@ -8856,22 +8892,18 @@
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>Retail Sales MoMJAN</t>
+          <t>Retail Sales ex Fuel MoMJAN</t>
         </is>
       </c>
       <c r="D308" t="inlineStr"/>
-      <c r="E308" t="inlineStr">
+      <c r="E308" t="inlineStr"/>
+      <c r="F308" t="inlineStr">
         <is>
           <t>0.3%</t>
         </is>
       </c>
-      <c r="F308" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
       <c r="G308" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="309">
@@ -8914,18 +8946,18 @@
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>Business ConfidenceFEB</t>
+          <t>Business Climate IndicatorFEB</t>
         </is>
       </c>
       <c r="D310" t="inlineStr"/>
       <c r="E310" t="inlineStr"/>
       <c r="F310" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>92</t>
         </is>
       </c>
       <c r="G310" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="311">
@@ -8941,18 +8973,18 @@
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>Business Climate IndicatorFEB</t>
+          <t>Business ConfidenceFEB</t>
         </is>
       </c>
       <c r="D311" t="inlineStr"/>
       <c r="E311" t="inlineStr"/>
       <c r="F311" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>94</t>
         </is>
       </c>
       <c r="G311" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="312">
@@ -8991,18 +9023,14 @@
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>HCOB Manufacturing PMI FlashFEB</t>
+          <t>HCOB Composite PMI FlashFEB</t>
         </is>
       </c>
       <c r="D313" t="inlineStr"/>
-      <c r="E313" t="inlineStr">
-        <is>
-          <t>45.3</t>
-        </is>
-      </c>
+      <c r="E313" t="inlineStr"/>
       <c r="F313" t="inlineStr">
         <is>
-          <t>45.4</t>
+          <t>47.2</t>
         </is>
       </c>
       <c r="G313" t="n">
@@ -9053,14 +9081,18 @@
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>HCOB Composite PMI FlashFEB</t>
+          <t>HCOB Manufacturing PMI FlashFEB</t>
         </is>
       </c>
       <c r="D315" t="inlineStr"/>
-      <c r="E315" t="inlineStr"/>
+      <c r="E315" t="inlineStr">
+        <is>
+          <t>45.3</t>
+        </is>
+      </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t>47.2</t>
+          <t>45.4</t>
         </is>
       </c>
       <c r="G315" t="n">
@@ -9169,18 +9201,14 @@
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>HCOB Manufacturing PMI FlashFEB</t>
+          <t>HCOB Composite PMI FlashFEB</t>
         </is>
       </c>
       <c r="D319" t="inlineStr"/>
-      <c r="E319" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
+      <c r="E319" t="inlineStr"/>
       <c r="F319" t="inlineStr">
         <is>
-          <t>46.8</t>
+          <t>50</t>
         </is>
       </c>
       <c r="G319" t="n">
@@ -9200,14 +9228,18 @@
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>HCOB Composite PMI FlashFEB</t>
+          <t>HCOB Manufacturing PMI FlashFEB</t>
         </is>
       </c>
       <c r="D320" t="inlineStr"/>
-      <c r="E320" t="inlineStr"/>
+      <c r="E320" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
       <c r="F320" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>46.8</t>
         </is>
       </c>
       <c r="G320" t="n">
@@ -9227,18 +9259,18 @@
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>Harmonised Inflation Rate YoY FinalJAN</t>
+          <t>Harmonised Inflation Rate MoM FinalJAN</t>
         </is>
       </c>
       <c r="D321" t="inlineStr"/>
       <c r="E321" t="inlineStr">
         <is>
-          <t>1.7%</t>
+          <t>-0.7%</t>
         </is>
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t>1.7%</t>
+          <t>-0.7%</t>
         </is>
       </c>
       <c r="G321" t="n">
@@ -9289,18 +9321,18 @@
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>Harmonised Inflation Rate MoM FinalJAN</t>
+          <t>Harmonised Inflation Rate YoY FinalJAN</t>
         </is>
       </c>
       <c r="D323" t="inlineStr"/>
       <c r="E323" t="inlineStr">
         <is>
-          <t>-0.7%</t>
+          <t>1.7%</t>
         </is>
       </c>
       <c r="F323" t="inlineStr">
         <is>
-          <t>-0.7%</t>
+          <t>1.7%</t>
         </is>
       </c>
       <c r="G323" t="n">
@@ -9315,23 +9347,23 @@
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>EA</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>HCOB Services PMI FlashFEB</t>
+          <t>Inflation Rate MoM FinalJAN</t>
         </is>
       </c>
       <c r="D324" t="inlineStr"/>
       <c r="E324" t="inlineStr">
         <is>
-          <t>51.5</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="F324" t="inlineStr">
         <is>
-          <t>51.2</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="G324" t="n">
@@ -9346,23 +9378,23 @@
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>EA</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>Inflation Rate MoM FinalJAN</t>
+          <t>HCOB Services PMI FlashFEB</t>
         </is>
       </c>
       <c r="D325" t="inlineStr"/>
       <c r="E325" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>51.5</t>
         </is>
       </c>
       <c r="F325" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>51.2</t>
         </is>
       </c>
       <c r="G325" t="n">
@@ -9471,14 +9503,14 @@
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>Monetary Policy Meeting Minutes</t>
+          <t>Foreign Exchange ReservesFEB/14</t>
         </is>
       </c>
       <c r="D329" t="inlineStr"/>
       <c r="E329" t="inlineStr"/>
       <c r="F329" t="inlineStr"/>
       <c r="G329" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="330">
@@ -9494,14 +9526,14 @@
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>Foreign Exchange ReservesFEB/14</t>
+          <t>Monetary Policy Meeting Minutes</t>
         </is>
       </c>
       <c r="D330" t="inlineStr"/>
       <c r="E330" t="inlineStr"/>
       <c r="F330" t="inlineStr"/>
       <c r="G330" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="331">
@@ -9517,14 +9549,14 @@
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>Economic Activity YoYDEC</t>
+          <t>Economic Activity MoMDEC</t>
         </is>
       </c>
       <c r="D331" t="inlineStr"/>
       <c r="E331" t="inlineStr"/>
       <c r="F331" t="inlineStr">
         <is>
-          <t>2%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="G331" t="n">
@@ -9606,14 +9638,14 @@
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>Economic Activity MoMDEC</t>
+          <t>Economic Activity YoYDEC</t>
         </is>
       </c>
       <c r="D334" t="inlineStr"/>
       <c r="E334" t="inlineStr"/>
       <c r="F334" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>2%</t>
         </is>
       </c>
       <c r="G334" t="n">
@@ -9687,18 +9719,18 @@
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Autos MoMDEC</t>
+          <t>Retail Sales MoM FinalDEC</t>
         </is>
       </c>
       <c r="D337" t="inlineStr"/>
       <c r="E337" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>1.6%</t>
         </is>
       </c>
       <c r="F337" t="inlineStr">
         <is>
-          <t>1%</t>
+          <t>1.6%</t>
         </is>
       </c>
       <c r="G337" t="n">
@@ -9718,18 +9750,18 @@
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>Retail Sales MoM FinalDEC</t>
+          <t>Retail Sales Ex Autos MoMDEC</t>
         </is>
       </c>
       <c r="D338" t="inlineStr"/>
       <c r="E338" t="inlineStr">
         <is>
-          <t>1.6%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F338" t="inlineStr">
         <is>
-          <t>1.6%</t>
+          <t>1%</t>
         </is>
       </c>
       <c r="G338" t="n">
@@ -9776,7 +9808,11 @@
         </is>
       </c>
       <c r="D340" t="inlineStr"/>
-      <c r="E340" t="inlineStr"/>
+      <c r="E340" t="inlineStr">
+        <is>
+          <t>53.2</t>
+        </is>
+      </c>
       <c r="F340" t="inlineStr">
         <is>
           <t>52.7</t>
@@ -9853,22 +9889,22 @@
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>Existing Home SalesJAN</t>
+          <t>Michigan 5 Year Inflation Expectations FinalFEB</t>
         </is>
       </c>
       <c r="D343" t="inlineStr"/>
       <c r="E343" t="inlineStr">
         <is>
-          <t>4.17M</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F343" t="inlineStr">
         <is>
-          <t>4.16M</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="G343" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="344">
@@ -9884,22 +9920,18 @@
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>Michigan Current Conditions FinalFEB</t>
+          <t>Existing Home Sales MoMJAN</t>
         </is>
       </c>
       <c r="D344" t="inlineStr"/>
-      <c r="E344" t="inlineStr">
-        <is>
-          <t>68.7</t>
-        </is>
-      </c>
+      <c r="E344" t="inlineStr"/>
       <c r="F344" t="inlineStr">
         <is>
-          <t>68.7</t>
+          <t>-1.7%</t>
         </is>
       </c>
       <c r="G344" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="345">
@@ -9915,18 +9947,18 @@
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>Michigan 5 Year Inflation Expectations FinalFEB</t>
+          <t>Michigan Inflation Expectations FinalFEB</t>
         </is>
       </c>
       <c r="D345" t="inlineStr"/>
       <c r="E345" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="F345" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="G345" t="n">
@@ -9946,18 +9978,18 @@
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>Michigan Inflation Expectations FinalFEB</t>
+          <t>Michigan Current Conditions FinalFEB</t>
         </is>
       </c>
       <c r="D346" t="inlineStr"/>
       <c r="E346" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>68.7</t>
         </is>
       </c>
       <c r="F346" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>68.7</t>
         </is>
       </c>
       <c r="G346" t="n">
@@ -9977,18 +10009,22 @@
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>Existing Home Sales MoMJAN</t>
+          <t>Michigan Consumer Expectations FinalFEB</t>
         </is>
       </c>
       <c r="D347" t="inlineStr"/>
-      <c r="E347" t="inlineStr"/>
+      <c r="E347" t="inlineStr">
+        <is>
+          <t>67.3</t>
+        </is>
+      </c>
       <c r="F347" t="inlineStr">
         <is>
-          <t>-1.7%</t>
+          <t>67.3</t>
         </is>
       </c>
       <c r="G347" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="348">
@@ -10004,22 +10040,22 @@
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>Michigan Consumer Expectations FinalFEB</t>
+          <t>Michigan Consumer Sentiment FinalFEB</t>
         </is>
       </c>
       <c r="D348" t="inlineStr"/>
       <c r="E348" t="inlineStr">
         <is>
-          <t>67.3</t>
+          <t>67.8</t>
         </is>
       </c>
       <c r="F348" t="inlineStr">
         <is>
-          <t>67.3</t>
+          <t>67.8</t>
         </is>
       </c>
       <c r="G348" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="349">
@@ -10035,22 +10071,22 @@
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>Michigan Consumer Sentiment FinalFEB</t>
+          <t>Existing Home SalesJAN</t>
         </is>
       </c>
       <c r="D349" t="inlineStr"/>
       <c r="E349" t="inlineStr">
         <is>
-          <t>67.8</t>
+          <t>4.17M</t>
         </is>
       </c>
       <c r="F349" t="inlineStr">
         <is>
-          <t>67.8</t>
+          <t>4.16M</t>
         </is>
       </c>
       <c r="G349" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="350">
@@ -10112,7 +10148,7 @@
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>Baker Hughes Oil Rig CountFEB/21</t>
+          <t>Baker Hughes Total Rigs CountFEB/21</t>
         </is>
       </c>
       <c r="D352" t="inlineStr"/>
@@ -10185,7 +10221,7 @@
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>Baker Hughes Total Rigs CountFEB/21</t>
+          <t>Baker Hughes Oil Rig CountFEB/21</t>
         </is>
       </c>
       <c r="D355" t="inlineStr"/>
@@ -10229,14 +10265,14 @@
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>Inflation Rate MoMJAN</t>
+          <t>Core Inflation Rate YoYJAN</t>
         </is>
       </c>
       <c r="D357" t="inlineStr"/>
       <c r="E357" t="inlineStr"/>
       <c r="F357" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>2.0%</t>
         </is>
       </c>
       <c r="G357" t="n">
@@ -10306,14 +10342,14 @@
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>Core Inflation Rate YoYJAN</t>
+          <t>Inflation Rate MoMJAN</t>
         </is>
       </c>
       <c r="D360" t="inlineStr"/>
       <c r="E360" t="inlineStr"/>
       <c r="F360" t="inlineStr">
         <is>
-          <t>2.0%</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="G360" t="n">
@@ -10379,18 +10415,18 @@
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>Ifo Current ConditionsFEB</t>
+          <t>Ifo Business ClimateFEB</t>
         </is>
       </c>
       <c r="D363" t="inlineStr"/>
       <c r="E363" t="inlineStr"/>
       <c r="F363" t="inlineStr">
         <is>
-          <t>85.1</t>
+          <t>84</t>
         </is>
       </c>
       <c r="G363" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="364">
@@ -10406,18 +10442,18 @@
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>Ifo Business ClimateFEB</t>
+          <t>Ifo Current ConditionsFEB</t>
         </is>
       </c>
       <c r="D364" t="inlineStr"/>
       <c r="E364" t="inlineStr"/>
       <c r="F364" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>85.1</t>
         </is>
       </c>
       <c r="G364" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="365">
@@ -10814,7 +10850,7 @@
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>12-Month BTF Auction</t>
+          <t>3-Month BTF Auction</t>
         </is>
       </c>
       <c r="D380" t="inlineStr"/>
@@ -10837,7 +10873,7 @@
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>3-Month BTF Auction</t>
+          <t>6-Month BTF Auction</t>
         </is>
       </c>
       <c r="D381" t="inlineStr"/>
@@ -10860,7 +10896,7 @@
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>6-Month BTF Auction</t>
+          <t>12-Month BTF Auction</t>
         </is>
       </c>
       <c r="D382" t="inlineStr"/>
@@ -10997,12 +11033,12 @@
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>20-Year KTB Auction</t>
+          <t>MAS 4-Week Bill Auction</t>
         </is>
       </c>
       <c r="D388" t="inlineStr"/>
@@ -11043,12 +11079,12 @@
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>MAS 4-Week Bill Auction</t>
+          <t>20-Year KTB Auction</t>
         </is>
       </c>
       <c r="D390" t="inlineStr"/>
@@ -11071,14 +11107,14 @@
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>Balance of TradeDEC</t>
+          <t>ImportsDEC</t>
         </is>
       </c>
       <c r="D391" t="inlineStr"/>
       <c r="E391" t="inlineStr"/>
       <c r="F391" t="inlineStr">
         <is>
-          <t>SAR 34B</t>
+          <t>SAR 60.5B</t>
         </is>
       </c>
       <c r="G391" t="n">
@@ -11098,14 +11134,14 @@
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>ExportsDEC</t>
+          <t>Balance of TradeDEC</t>
         </is>
       </c>
       <c r="D392" t="inlineStr"/>
       <c r="E392" t="inlineStr"/>
       <c r="F392" t="inlineStr">
         <is>
-          <t>SAR 94.5B</t>
+          <t>SAR 34B</t>
         </is>
       </c>
       <c r="G392" t="n">
@@ -11125,14 +11161,14 @@
       </c>
       <c r="C393" t="inlineStr">
         <is>
-          <t>ImportsDEC</t>
+          <t>ExportsDEC</t>
         </is>
       </c>
       <c r="D393" t="inlineStr"/>
       <c r="E393" t="inlineStr"/>
       <c r="F393" t="inlineStr">
         <is>
-          <t>SAR 60.5B</t>
+          <t>SAR 94.5B</t>
         </is>
       </c>
       <c r="G393" t="n">
@@ -11147,19 +11183,23 @@
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>EU</t>
+          <t>ZA</t>
         </is>
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>New Car Registrations YoYJAN</t>
+          <t>Leading Business Cycle Indicator MoMDEC</t>
         </is>
       </c>
       <c r="D394" t="inlineStr"/>
       <c r="E394" t="inlineStr"/>
-      <c r="F394" t="inlineStr"/>
+      <c r="F394" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="G394" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="395">
@@ -11175,7 +11215,7 @@
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>GDP Growth Rate YoY FinalQ4</t>
+          <t>GDP Growth Rate QoQ FinalQ4</t>
         </is>
       </c>
       <c r="D395" t="inlineStr"/>
@@ -11201,23 +11241,27 @@
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>ZA</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>Leading Business Cycle Indicator MoMDEC</t>
+          <t>GDP Growth Rate YoY FinalQ4</t>
         </is>
       </c>
       <c r="D396" t="inlineStr"/>
-      <c r="E396" t="inlineStr"/>
+      <c r="E396" t="inlineStr">
+        <is>
+          <t>-0.2%</t>
+        </is>
+      </c>
       <c r="F396" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>-0.2%</t>
         </is>
       </c>
       <c r="G396" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="397">
@@ -11228,25 +11272,17 @@
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>EU</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>GDP Growth Rate QoQ FinalQ4</t>
+          <t>New Car Registrations YoYJAN</t>
         </is>
       </c>
       <c r="D397" t="inlineStr"/>
-      <c r="E397" t="inlineStr">
-        <is>
-          <t>-0.2%</t>
-        </is>
-      </c>
-      <c r="F397" t="inlineStr">
-        <is>
-          <t>-0.2%</t>
-        </is>
-      </c>
+      <c r="E397" t="inlineStr"/>
+      <c r="F397" t="inlineStr"/>
       <c r="G397" t="n">
         <v>2</v>
       </c>
@@ -11441,7 +11477,7 @@
       </c>
       <c r="C405" t="inlineStr">
         <is>
-          <t>IPCA mid-month CPI YoYFEB</t>
+          <t>IPCA mid-month CPI MoMFEB</t>
         </is>
       </c>
       <c r="D405" t="inlineStr"/>
@@ -11464,7 +11500,7 @@
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>IPCA mid-month CPI MoMFEB</t>
+          <t>IPCA mid-month CPI YoYFEB</t>
         </is>
       </c>
       <c r="D406" t="inlineStr"/>
@@ -11533,18 +11569,14 @@
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price YoYDEC</t>
+          <t>House Price Index MoMDEC</t>
         </is>
       </c>
       <c r="D409" t="inlineStr"/>
       <c r="E409" t="inlineStr"/>
-      <c r="F409" t="inlineStr">
-        <is>
-          <t>4.2%</t>
-        </is>
-      </c>
+      <c r="F409" t="inlineStr"/>
       <c r="G409" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="410">
@@ -11560,7 +11592,7 @@
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>House Price Index MoMDEC</t>
+          <t>S&amp;P/Case-Shiller Home Price MoMDEC</t>
         </is>
       </c>
       <c r="D410" t="inlineStr"/>
@@ -11578,17 +11610,21 @@
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>EA</t>
         </is>
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>House Price IndexDEC</t>
+          <t>Negotiated Wage GrowthQ4</t>
         </is>
       </c>
       <c r="D411" t="inlineStr"/>
       <c r="E411" t="inlineStr"/>
-      <c r="F411" t="inlineStr"/>
+      <c r="F411" t="inlineStr">
+        <is>
+          <t>5.1%</t>
+        </is>
+      </c>
       <c r="G411" t="n">
         <v>3</v>
       </c>
@@ -11601,21 +11637,17 @@
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>EA</t>
+          <t>US</t>
         </is>
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>Negotiated Wage GrowthQ4</t>
+          <t>House Price Index YoYDEC</t>
         </is>
       </c>
       <c r="D412" t="inlineStr"/>
       <c r="E412" t="inlineStr"/>
-      <c r="F412" t="inlineStr">
-        <is>
-          <t>5.1%</t>
-        </is>
-      </c>
+      <c r="F412" t="inlineStr"/>
       <c r="G412" t="n">
         <v>3</v>
       </c>
@@ -11633,7 +11665,7 @@
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>House Price Index YoYDEC</t>
+          <t>House Price IndexDEC</t>
         </is>
       </c>
       <c r="D413" t="inlineStr"/>
@@ -11656,14 +11688,18 @@
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price MoMDEC</t>
+          <t>S&amp;P/Case-Shiller Home Price YoYDEC</t>
         </is>
       </c>
       <c r="D414" t="inlineStr"/>
       <c r="E414" t="inlineStr"/>
-      <c r="F414" t="inlineStr"/>
+      <c r="F414" t="inlineStr">
+        <is>
+          <t>4.2%</t>
+        </is>
+      </c>
       <c r="G414" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="415">
@@ -11674,19 +11710,23 @@
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>EA</t>
         </is>
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>CB Consumer ConfidenceFEB</t>
+          <t>Negotiated Wage GrowthQ4</t>
         </is>
       </c>
       <c r="D415" t="inlineStr"/>
       <c r="E415" t="inlineStr"/>
-      <c r="F415" t="inlineStr"/>
+      <c r="F415" t="inlineStr">
+        <is>
+          <t>5.1%</t>
+        </is>
+      </c>
       <c r="G415" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="416">
@@ -11702,7 +11742,7 @@
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>Richmond Fed Manufacturing IndexFEB</t>
+          <t>Richmond Fed Manufacturing Shipments IndexFEB</t>
         </is>
       </c>
       <c r="D416" t="inlineStr"/>
@@ -11770,21 +11810,17 @@
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>EA</t>
+          <t>US</t>
         </is>
       </c>
       <c r="C419" t="inlineStr">
         <is>
-          <t>Negotiated Wage GrowthQ4</t>
+          <t>Richmond Fed Manufacturing IndexFEB</t>
         </is>
       </c>
       <c r="D419" t="inlineStr"/>
       <c r="E419" t="inlineStr"/>
-      <c r="F419" t="inlineStr">
-        <is>
-          <t>5.1%</t>
-        </is>
-      </c>
+      <c r="F419" t="inlineStr"/>
       <c r="G419" t="n">
         <v>3</v>
       </c>
@@ -11802,14 +11838,14 @@
       </c>
       <c r="C420" t="inlineStr">
         <is>
-          <t>Richmond Fed Manufacturing Shipments IndexFEB</t>
+          <t>CB Consumer ConfidenceFEB</t>
         </is>
       </c>
       <c r="D420" t="inlineStr"/>
       <c r="E420" t="inlineStr"/>
       <c r="F420" t="inlineStr"/>
       <c r="G420" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="421">
@@ -11825,7 +11861,7 @@
       </c>
       <c r="C421" t="inlineStr">
         <is>
-          <t>Dallas Fed Services IndexFEB</t>
+          <t>Dallas Fed Services Revenues IndexFEB</t>
         </is>
       </c>
       <c r="D421" t="inlineStr"/>
@@ -11843,17 +11879,21 @@
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>EA</t>
         </is>
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>Dallas Fed Services Revenues IndexFEB</t>
+          <t>Negotiated Wage GrowthQ4</t>
         </is>
       </c>
       <c r="D422" t="inlineStr"/>
       <c r="E422" t="inlineStr"/>
-      <c r="F422" t="inlineStr"/>
+      <c r="F422" t="inlineStr">
+        <is>
+          <t>5.1%</t>
+        </is>
+      </c>
       <c r="G422" t="n">
         <v>3</v>
       </c>
@@ -11866,21 +11906,17 @@
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>EA</t>
+          <t>US</t>
         </is>
       </c>
       <c r="C423" t="inlineStr">
         <is>
-          <t>Negotiated Wage GrowthQ4</t>
+          <t>Dallas Fed Services IndexFEB</t>
         </is>
       </c>
       <c r="D423" t="inlineStr"/>
       <c r="E423" t="inlineStr"/>
-      <c r="F423" t="inlineStr">
-        <is>
-          <t>5.1%</t>
-        </is>
-      </c>
+      <c r="F423" t="inlineStr"/>
       <c r="G423" t="n">
         <v>3</v>
       </c>
@@ -11898,7 +11934,7 @@
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>Money SupplyJAN</t>
+          <t>5-Year Note Auction</t>
         </is>
       </c>
       <c r="D424" t="inlineStr"/>
@@ -11921,7 +11957,7 @@
       </c>
       <c r="C425" t="inlineStr">
         <is>
-          <t>5-Year Note Auction</t>
+          <t>Money SupplyJAN</t>
         </is>
       </c>
       <c r="D425" t="inlineStr"/>
@@ -11958,6 +11994,60 @@
         <v>3</v>
       </c>
     </row>
+    <row r="427">
+      <c r="A427" t="inlineStr">
+        <is>
+          <t>2025-02-25 14:00:00-05:00</t>
+        </is>
+      </c>
+      <c r="B427" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C427" t="inlineStr">
+        <is>
+          <t>Economic Activity YoYDEC</t>
+        </is>
+      </c>
+      <c r="D427" t="inlineStr"/>
+      <c r="E427" t="inlineStr"/>
+      <c r="F427" t="inlineStr">
+        <is>
+          <t>-1.0%</t>
+        </is>
+      </c>
+      <c r="G427" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="inlineStr">
+        <is>
+          <t>2025-02-25 14:00:00-05:00</t>
+        </is>
+      </c>
+      <c r="B428" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="C428" t="inlineStr">
+        <is>
+          <t>Negotiated Wage GrowthQ4</t>
+        </is>
+      </c>
+      <c r="D428" t="inlineStr"/>
+      <c r="E428" t="inlineStr"/>
+      <c r="F428" t="inlineStr">
+        <is>
+          <t>5.1%</t>
+        </is>
+      </c>
+      <c r="G428" t="n">
+        <v>3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Input_data/EST_All Countries_trad_eco_cal_2025-02-14_to_2025-02-25.xlsx
+++ b/Input_data/EST_All Countries_trad_eco_cal_2025-02-14_to_2025-02-25.xlsx
@@ -699,22 +699,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Inflation Rate MoM FinalJAN</t>
+          <t>Core Inflation Rate YoY FinalJAN</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>2.4%</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>2.4%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>2.4%</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -734,7 +734,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Harmonised Inflation Rate YoY FinalJAN</t>
+          <t>Inflation Rate YoY FinalJAN</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -744,12 +744,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>3%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>3.0%</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -769,22 +769,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Inflation Rate YoY FinalJAN</t>
+          <t>Harmonised Inflation Rate MoM FinalJAN</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>3%</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>3.0%</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -804,22 +804,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Core Inflation Rate YoY FinalJAN</t>
+          <t>Inflation Rate MoM FinalJAN</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2.4%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2.4%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2.4%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -839,22 +839,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Harmonised Inflation Rate MoM FinalJAN</t>
+          <t>Harmonised Inflation Rate YoY FinalJAN</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1220,12 +1220,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Deposit Growth YoYJAN/31</t>
+          <t>Foreign Exchange ReservesFEB/07</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>10.3%</t>
+          <t>$638.26B</t>
         </is>
       </c>
       <c r="E24" t="inlineStr"/>
@@ -1274,12 +1274,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Foreign Exchange ReservesFEB/07</t>
+          <t>Deposit Growth YoYJAN/31</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>$638.26B</t>
+          <t>10.3%</t>
         </is>
       </c>
       <c r="E26" t="inlineStr"/>
@@ -1324,22 +1324,26 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Import Prices YoYJAN</t>
+          <t>Retail Sales MoMJAN</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1.9%</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr"/>
+          <t>-0.9%</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>-0.1%</t>
+        </is>
+      </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -1350,31 +1354,27 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Autos MoMJAN</t>
+          <t>New Motor Vehicle SalesDEC</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>-0.4%</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>135.5K</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>153K</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="30">
@@ -1385,23 +1385,27 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Retail Sales YoYJAN</t>
+          <t>Wholesale Sales MoM FinalDEC</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>4.2%</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr"/>
+          <t>-0.2%</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>3.7%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -1421,22 +1425,26 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Export Prices YoYJAN</t>
+          <t>Import Prices MoMJAN</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2.7%</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr"/>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="32">
@@ -1452,12 +1460,12 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Retail Sales Control Group MoMJAN</t>
+          <t>Export Prices MoMJAN</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>-0.8%</t>
+          <t>1.3%</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1467,7 +1475,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -1482,23 +1490,27 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Gas/Autos MoMJAN</t>
+          <t>Manufacturing Sales MoM FinalDEC</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>-0.5%</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr"/>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>0.7%</t>
+        </is>
+      </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -1518,12 +1530,12 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Export Prices MoMJAN</t>
+          <t>Retail Sales Control Group MoMJAN</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>1.3%</t>
+          <t>-0.8%</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1533,7 +1545,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -1553,26 +1565,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Import Prices MoMJAN</t>
+          <t>Export Prices YoYJAN</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
+          <t>2.7%</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="G35" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="36">
@@ -1583,27 +1591,23 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>US</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Wholesale Sales MoM FinalDEC</t>
+          <t>Retail Sales YoYJAN</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>-0.2%</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
+          <t>4.2%</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>3.7%</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -1618,31 +1622,31 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>US</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Manufacturing Sales MoM FinalDEC</t>
+          <t>Retail Sales Ex Autos MoMJAN</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
+          <t>-0.4%</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
           <t>0.3%</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>0.7%</t>
-        </is>
-      </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G37" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="38">
@@ -1653,23 +1657,23 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>US</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>New Motor Vehicle SalesDEC</t>
+          <t>Import Prices YoYJAN</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>135.5K</t>
+          <t>1.9%</t>
         </is>
       </c>
       <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr">
         <is>
-          <t>153K</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -1689,26 +1693,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Retail Sales MoMJAN</t>
+          <t>Retail Sales Ex Gas/Autos MoMJAN</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>-0.9%</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>-0.1%</t>
-        </is>
-      </c>
+          <t>-0.5%</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G39" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="40">
@@ -2054,12 +2054,12 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Baker Hughes Total Rigs CountFEB/14</t>
+          <t>Baker Hughes Oil Rig CountFEB/14</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>588</t>
+          <t>481</t>
         </is>
       </c>
       <c r="E50" t="inlineStr"/>
@@ -2081,12 +2081,12 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Baker Hughes Oil Rig CountFEB/14</t>
+          <t>Baker Hughes Total Rigs CountFEB/14</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>481</t>
+          <t>588</t>
         </is>
       </c>
       <c r="E51" t="inlineStr"/>

--- a/Input_data/EST_All Countries_trad_eco_cal_2025-02-14_to_2025-02-25.xlsx
+++ b/Input_data/EST_All Countries_trad_eco_cal_2025-02-14_to_2025-02-25.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G428"/>
+  <dimension ref="A1:G430"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -699,22 +699,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Core Inflation Rate YoY FinalJAN</t>
+          <t>Inflation Rate MoM FinalJAN</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2.4%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2.4%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2.4%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -734,22 +734,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Inflation Rate YoY FinalJAN</t>
+          <t>Harmonised Inflation Rate MoM FinalJAN</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>3%</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>3.0%</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -769,22 +769,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Harmonised Inflation Rate MoM FinalJAN</t>
+          <t>Harmonised Inflation Rate YoY FinalJAN</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -804,22 +804,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Inflation Rate MoM FinalJAN</t>
+          <t>Core Inflation Rate YoY FinalJAN</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>2.4%</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>2.4%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>2.4%</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -839,7 +839,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Harmonised Inflation Rate YoY FinalJAN</t>
+          <t>Inflation Rate YoY FinalJAN</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -849,12 +849,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>3%</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>3.0%</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1220,12 +1220,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Foreign Exchange ReservesFEB/07</t>
+          <t>Deposit Growth YoYJAN/31</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>$638.26B</t>
+          <t>10.3%</t>
         </is>
       </c>
       <c r="E24" t="inlineStr"/>
@@ -1274,12 +1274,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Deposit Growth YoYJAN/31</t>
+          <t>Foreign Exchange ReservesFEB/07</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>10.3%</t>
+          <t>$638.26B</t>
         </is>
       </c>
       <c r="E26" t="inlineStr"/>
@@ -1324,26 +1324,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Retail Sales MoMJAN</t>
+          <t>Retail Sales Ex Gas/Autos MoMJAN</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>-0.9%</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>-0.1%</t>
-        </is>
-      </c>
+          <t>-0.5%</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="29">
@@ -1354,23 +1350,23 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>US</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>New Motor Vehicle SalesDEC</t>
+          <t>Import Prices YoYJAN</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>135.5K</t>
+          <t>1.9%</t>
         </is>
       </c>
       <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr">
         <is>
-          <t>153K</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -1385,27 +1381,23 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>US</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Wholesale Sales MoM FinalDEC</t>
+          <t>Retail Sales YoYJAN</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>-0.2%</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
+          <t>4.2%</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>3.7%</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -1425,26 +1417,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Import Prices MoMJAN</t>
+          <t>Export Prices YoYJAN</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
+          <t>2.7%</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="32">
@@ -1460,12 +1448,12 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Export Prices MoMJAN</t>
+          <t>Retail Sales Control Group MoMJAN</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1.3%</t>
+          <t>-0.8%</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1475,7 +1463,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -1490,31 +1478,31 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>US</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Manufacturing Sales MoM FinalDEC</t>
+          <t>Retail Sales Ex Autos MoMJAN</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
+          <t>-0.4%</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
           <t>0.3%</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>0.7%</t>
-        </is>
-      </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G33" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="34">
@@ -1530,12 +1518,12 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Retail Sales Control Group MoMJAN</t>
+          <t>Export Prices MoMJAN</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>-0.8%</t>
+          <t>1.3%</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1545,7 +1533,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -1565,22 +1553,26 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Export Prices YoYJAN</t>
+          <t>Import Prices MoMJAN</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2.7%</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr"/>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G35" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="36">
@@ -1591,23 +1583,27 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Retail Sales YoYJAN</t>
+          <t>Wholesale Sales MoM FinalDEC</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>4.2%</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr"/>
+          <t>-0.2%</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>3.7%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -1622,31 +1618,27 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Autos MoMJAN</t>
+          <t>New Motor Vehicle SalesDEC</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>-0.4%</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>135.5K</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>153K</t>
         </is>
       </c>
       <c r="G37" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="38">
@@ -1662,22 +1654,26 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Import Prices YoYJAN</t>
+          <t>Retail Sales MoMJAN</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>1.9%</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr"/>
+          <t>-0.9%</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>-0.1%</t>
+        </is>
+      </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G38" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="39">
@@ -1688,23 +1684,27 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Gas/Autos MoMJAN</t>
+          <t>Manufacturing Sales MoM FinalDEC</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>-0.5%</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr"/>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>0.7%</t>
+        </is>
+      </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -2054,12 +2054,12 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Baker Hughes Oil Rig CountFEB/14</t>
+          <t>Baker Hughes Total Rigs CountFEB/14</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>481</t>
+          <t>588</t>
         </is>
       </c>
       <c r="E50" t="inlineStr"/>
@@ -2081,12 +2081,12 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Baker Hughes Total Rigs CountFEB/14</t>
+          <t>Baker Hughes Oil Rig CountFEB/14</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>588</t>
+          <t>481</t>
         </is>
       </c>
       <c r="E51" t="inlineStr"/>
@@ -2131,22 +2131,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>GDP Growth Annualized PrelQ4</t>
+          <t>GDP Growth Rate QoQ PrelQ4</t>
         </is>
       </c>
       <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr">
         <is>
-          <t>1%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2.1%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="G53" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="54">
@@ -2224,22 +2224,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>GDP Growth Rate QoQ PrelQ4</t>
+          <t>GDP External Demand QoQ PrelQ4</t>
         </is>
       </c>
       <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr">
         <is>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
           <t>0.3%</t>
         </is>
       </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>0.5%</t>
-        </is>
-      </c>
       <c r="G56" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="57">
@@ -2255,18 +2255,18 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>GDP External Demand QoQ PrelQ4</t>
+          <t>GDP Capital Expenditure QoQ PrelQ4</t>
         </is>
       </c>
       <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr">
         <is>
+          <t>1%</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
           <t>0.4%</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>0.3%</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -2286,7 +2286,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>GDP Capital Expenditure QoQ PrelQ4</t>
+          <t>GDP Growth Annualized PrelQ4</t>
         </is>
       </c>
       <c r="D58" t="inlineStr"/>
@@ -2297,11 +2297,11 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>2.1%</t>
         </is>
       </c>
       <c r="G58" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="59">
@@ -2491,14 +2491,18 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Industrial Production YoY FinalDEC</t>
+          <t>Industrial Production MoM FinalDEC</t>
         </is>
       </c>
       <c r="D65" t="inlineStr"/>
-      <c r="E65" t="inlineStr"/>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>-1.6%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -2513,19 +2517,19 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Vehicle Sales YoYJAN</t>
+          <t>Industrial Production YoY FinalDEC</t>
         </is>
       </c>
       <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr"/>
       <c r="F66" t="inlineStr">
         <is>
-          <t>12.0%</t>
+          <t>-1.6%</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -2540,23 +2544,19 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>SA</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Inflation Rate MoMJAN</t>
+          <t>Vehicle Sales YoYJAN</t>
         </is>
       </c>
       <c r="D67" t="inlineStr"/>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
+      <c r="E67" t="inlineStr"/>
       <c r="F67" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>12.0%</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -2576,18 +2576,18 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Inflation Rate YoYJAN</t>
+          <t>Inflation Rate MoMJAN</t>
         </is>
       </c>
       <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr">
         <is>
-          <t>1.9%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2.0%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -2607,14 +2607,18 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Wholesale Prices YoYJAN</t>
+          <t>Inflation Rate YoYJAN</t>
         </is>
       </c>
       <c r="D69" t="inlineStr"/>
-      <c r="E69" t="inlineStr"/>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>1.9%</t>
+        </is>
+      </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>1.3%</t>
+          <t>2.0%</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -2629,17 +2633,21 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>EA</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Eurogroup Meeting</t>
+          <t>Wholesale Prices YoYJAN</t>
         </is>
       </c>
       <c r="D70" t="inlineStr"/>
       <c r="E70" t="inlineStr"/>
-      <c r="F70" t="inlineStr"/>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>1.3%</t>
+        </is>
+      </c>
       <c r="G70" t="n">
         <v>3</v>
       </c>
@@ -2652,25 +2660,17 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>EA</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Industrial Production MoM FinalDEC</t>
+          <t>Eurogroup Meeting</t>
         </is>
       </c>
       <c r="D71" t="inlineStr"/>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+      <c r="E71" t="inlineStr"/>
+      <c r="F71" t="inlineStr"/>
       <c r="G71" t="n">
         <v>3</v>
       </c>
@@ -2688,18 +2688,14 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Tertiary Industry Index MoMDEC</t>
+          <t>Capacity Utilization MoMDEC</t>
         </is>
       </c>
       <c r="D72" t="inlineStr"/>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
+      <c r="E72" t="inlineStr"/>
       <c r="F72" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -2719,14 +2715,18 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Capacity Utilization MoMDEC</t>
+          <t>Tertiary Industry Index MoMDEC</t>
         </is>
       </c>
       <c r="D73" t="inlineStr"/>
-      <c r="E73" t="inlineStr"/>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -3227,14 +3227,14 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Auto Sales YoYJAN</t>
+          <t>Auto Production YoYJAN</t>
         </is>
       </c>
       <c r="D93" t="inlineStr"/>
       <c r="E93" t="inlineStr"/>
       <c r="F93" t="inlineStr">
         <is>
-          <t>6.0%</t>
+          <t>4.0%</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -3254,14 +3254,14 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Budget BalanceJAN</t>
+          <t>Auto Sales YoYJAN</t>
         </is>
       </c>
       <c r="D94" t="inlineStr"/>
       <c r="E94" t="inlineStr"/>
       <c r="F94" t="inlineStr">
         <is>
-          <t>TRY-150.0B</t>
+          <t>6.0%</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -3276,19 +3276,19 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>TR</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Balance of TradeJAN</t>
+          <t>Budget BalanceJAN</t>
         </is>
       </c>
       <c r="D95" t="inlineStr"/>
       <c r="E95" t="inlineStr"/>
       <c r="F95" t="inlineStr">
         <is>
-          <t>$-24.0B</t>
+          <t>TRY-150.0B</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -3308,7 +3308,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>ImportsJAN</t>
+          <t>ExportsJAN</t>
         </is>
       </c>
       <c r="D96" t="inlineStr"/>
@@ -3326,12 +3326,12 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>EU</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>European Commission Winter Forecasts</t>
+          <t>ImportsJAN</t>
         </is>
       </c>
       <c r="D97" t="inlineStr"/>
@@ -3349,12 +3349,12 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>EU</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>BCB Focus Market Readout</t>
+          <t>European Commission Winter Forecasts</t>
         </is>
       </c>
       <c r="D98" t="inlineStr"/>
@@ -3372,12 +3372,12 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>EA</t>
+          <t>BR</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>ECOFIN Meeting</t>
+          <t>BCB Focus Market Readout</t>
         </is>
       </c>
       <c r="D99" t="inlineStr"/>
@@ -3395,21 +3395,17 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>TR</t>
+          <t>EA</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Auto Production YoYJAN</t>
+          <t>ECOFIN Meeting</t>
         </is>
       </c>
       <c r="D100" t="inlineStr"/>
       <c r="E100" t="inlineStr"/>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>4.0%</t>
-        </is>
-      </c>
+      <c r="F100" t="inlineStr"/>
       <c r="G100" t="n">
         <v>2</v>
       </c>
@@ -3422,12 +3418,12 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>ExportsJAN</t>
+          <t>RBA Press Conference</t>
         </is>
       </c>
       <c r="D101" t="inlineStr"/>
@@ -3445,17 +3441,21 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>RBA Press Conference</t>
+          <t>Balance of TradeJAN</t>
         </is>
       </c>
       <c r="D102" t="inlineStr"/>
       <c r="E102" t="inlineStr"/>
-      <c r="F102" t="inlineStr"/>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>$-24.0B</t>
+        </is>
+      </c>
       <c r="G102" t="n">
         <v>2</v>
       </c>
@@ -3519,18 +3519,14 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Average Earnings excl. Bonus (3Mo/Yr)DEC</t>
+          <t>HMRC Payrolls ChangeJAN</t>
         </is>
       </c>
       <c r="D105" t="inlineStr"/>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>5.9%</t>
-        </is>
-      </c>
+      <c r="E105" t="inlineStr"/>
       <c r="F105" t="inlineStr">
         <is>
-          <t>5.9%</t>
+          <t>-55.0K</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -3670,14 +3666,18 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>HMRC Payrolls ChangeJAN</t>
+          <t>Average Earnings excl. Bonus (3Mo/Yr)DEC</t>
         </is>
       </c>
       <c r="D110" t="inlineStr"/>
-      <c r="E110" t="inlineStr"/>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>5.9%</t>
+        </is>
+      </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>-55.0K</t>
+          <t>5.9%</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -3728,18 +3728,18 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Harmonised Inflation Rate MoM FinalJAN</t>
+          <t>Harmonised Inflation Rate YoY FinalJAN</t>
         </is>
       </c>
       <c r="D112" t="inlineStr"/>
       <c r="E112" t="inlineStr">
         <is>
-          <t>-0.2%</t>
+          <t>1.8%</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>-0.2%</t>
+          <t>1.8%</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -3759,18 +3759,18 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Harmonised Inflation Rate YoY FinalJAN</t>
+          <t>Harmonised Inflation Rate MoM FinalJAN</t>
         </is>
       </c>
       <c r="D113" t="inlineStr"/>
       <c r="E113" t="inlineStr">
         <is>
-          <t>1.8%</t>
+          <t>-0.2%</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>1.8%</t>
+          <t>-0.2%</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>EA</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -3962,16 +3962,16 @@
       <c r="D120" t="inlineStr"/>
       <c r="E120" t="inlineStr">
         <is>
+          <t>24.3</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="F120" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
       <c r="G120" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="121">
@@ -4036,7 +4036,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>EA</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -4047,16 +4047,16 @@
       <c r="D123" t="inlineStr"/>
       <c r="E123" t="inlineStr">
         <is>
-          <t>24.3</t>
+          <t>15</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>12</t>
         </is>
       </c>
       <c r="G123" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="124">
@@ -4095,18 +4095,22 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Core Inflation Rate MoMJAN</t>
+          <t>Inflation Rate MoMJAN</t>
         </is>
       </c>
       <c r="D125" t="inlineStr"/>
-      <c r="E125" t="inlineStr"/>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>0.1%</t>
+        </is>
+      </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G125" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="126">
@@ -4122,18 +4126,14 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Inflation Rate MoMJAN</t>
+          <t>Core Inflation Rate YoYJAN</t>
         </is>
       </c>
       <c r="D126" t="inlineStr"/>
-      <c r="E126" t="inlineStr">
-        <is>
-          <t>0.1%</t>
-        </is>
-      </c>
+      <c r="E126" t="inlineStr"/>
       <c r="F126" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>1.7%</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -4148,27 +4148,23 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>NY Empire State Manufacturing IndexFEB</t>
+          <t>Inflation Rate YoYJAN</t>
         </is>
       </c>
       <c r="D127" t="inlineStr"/>
-      <c r="E127" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
+      <c r="E127" t="inlineStr"/>
       <c r="F127" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1.8%</t>
         </is>
       </c>
       <c r="G127" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="128">
@@ -4184,18 +4180,22 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Inflation Rate YoYJAN</t>
+          <t>CPI Trimmed-Mean YoYJAN</t>
         </is>
       </c>
       <c r="D128" t="inlineStr"/>
-      <c r="E128" t="inlineStr"/>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>2.6%</t>
+        </is>
+      </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>1.8%</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="G128" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="129">
@@ -4211,18 +4211,18 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Core Inflation Rate YoYJAN</t>
+          <t>Core Inflation Rate MoMJAN</t>
         </is>
       </c>
       <c r="D129" t="inlineStr"/>
       <c r="E129" t="inlineStr"/>
       <c r="F129" t="inlineStr">
         <is>
-          <t>1.7%</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="G129" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="130">
@@ -4233,27 +4233,27 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>US</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>CPI Median YoYJAN</t>
+          <t>NY Empire State Manufacturing IndexFEB</t>
         </is>
       </c>
       <c r="D130" t="inlineStr"/>
       <c r="E130" t="inlineStr">
         <is>
-          <t>2.4%</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>2.4%</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G130" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="131">
@@ -4269,18 +4269,18 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>CPI Trimmed-Mean YoYJAN</t>
+          <t>CPI Median YoYJAN</t>
         </is>
       </c>
       <c r="D131" t="inlineStr"/>
       <c r="E131" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>2.4%</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>2.4%</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -4349,19 +4349,19 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>US</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Bundesbank Balz Speech</t>
+          <t>Fed Daly Speech</t>
         </is>
       </c>
       <c r="D134" t="inlineStr"/>
       <c r="E134" t="inlineStr"/>
       <c r="F134" t="inlineStr"/>
       <c r="G134" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="135">
@@ -4372,19 +4372,19 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Fed Daly Speech</t>
+          <t>Bundesbank Balz Speech</t>
         </is>
       </c>
       <c r="D135" t="inlineStr"/>
       <c r="E135" t="inlineStr"/>
       <c r="F135" t="inlineStr"/>
       <c r="G135" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="136">
@@ -4469,14 +4469,14 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>52-Week Bill Auction</t>
+          <t>Fed Barr Speech</t>
         </is>
       </c>
       <c r="D139" t="inlineStr"/>
       <c r="E139" t="inlineStr"/>
       <c r="F139" t="inlineStr"/>
       <c r="G139" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="140">
@@ -4492,14 +4492,14 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Fed Barr Speech</t>
+          <t>52-Week Bill Auction</t>
         </is>
       </c>
       <c r="D140" t="inlineStr"/>
       <c r="E140" t="inlineStr"/>
       <c r="F140" t="inlineStr"/>
       <c r="G140" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="141">
@@ -4542,14 +4542,18 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Overall Net Capital FlowsDEC</t>
+          <t>Net Long-term TIC FlowsDEC</t>
         </is>
       </c>
       <c r="D142" t="inlineStr"/>
-      <c r="E142" t="inlineStr"/>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>$149.1B</t>
+        </is>
+      </c>
       <c r="F142" t="inlineStr"/>
       <c r="G142" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="143">
@@ -4588,18 +4592,14 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Net Long-term TIC FlowsDEC</t>
+          <t>Overall Net Capital FlowsDEC</t>
         </is>
       </c>
       <c r="D144" t="inlineStr"/>
-      <c r="E144" t="inlineStr">
-        <is>
-          <t>$149.1B</t>
-        </is>
-      </c>
+      <c r="E144" t="inlineStr"/>
       <c r="F144" t="inlineStr"/>
       <c r="G144" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="145">
@@ -4615,22 +4615,22 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Imports YoYJAN</t>
+          <t>Balance of TradeJAN</t>
         </is>
       </c>
       <c r="D145" t="inlineStr"/>
       <c r="E145" t="inlineStr">
         <is>
-          <t>9.7%</t>
+          <t>¥-2104B</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>2.0%</t>
+          <t>¥-1400.0B</t>
         </is>
       </c>
       <c r="G145" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="146">
@@ -4646,18 +4646,18 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Machinery Orders YoYDEC</t>
+          <t>Machinery Orders MoMDEC</t>
         </is>
       </c>
       <c r="D146" t="inlineStr"/>
       <c r="E146" t="inlineStr">
         <is>
-          <t>6.9%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>7.6%</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -4677,18 +4677,18 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Exports YoYJAN</t>
+          <t>Machinery Orders YoYDEC</t>
         </is>
       </c>
       <c r="D147" t="inlineStr"/>
       <c r="E147" t="inlineStr">
         <is>
-          <t>7.9%</t>
+          <t>6.9%</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>3.0%</t>
+          <t>7.6%</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -4708,22 +4708,22 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Balance of TradeJAN</t>
+          <t>Imports YoYJAN</t>
         </is>
       </c>
       <c r="D148" t="inlineStr"/>
       <c r="E148" t="inlineStr">
         <is>
-          <t>¥-2104B</t>
+          <t>9.7%</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>¥-1400.0B</t>
+          <t>2.0%</t>
         </is>
       </c>
       <c r="G148" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="149">
@@ -4739,18 +4739,18 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Machinery Orders MoMDEC</t>
+          <t>Exports YoYJAN</t>
         </is>
       </c>
       <c r="D149" t="inlineStr"/>
       <c r="E149" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>7.9%</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>3.0%</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -4828,12 +4828,20 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>RBA Chart Pack</t>
+          <t>Wage Price Index QoQQ4</t>
         </is>
       </c>
       <c r="D152" t="inlineStr"/>
-      <c r="E152" t="inlineStr"/>
-      <c r="F152" t="inlineStr"/>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>0.8%</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
       <c r="G152" t="n">
         <v>3</v>
       </c>
@@ -4851,20 +4859,12 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Wage Price Index QoQQ4</t>
+          <t>RBA Chart Pack</t>
         </is>
       </c>
       <c r="D153" t="inlineStr"/>
-      <c r="E153" t="inlineStr">
-        <is>
-          <t>0.8%</t>
-        </is>
-      </c>
-      <c r="F153" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
+      <c r="E153" t="inlineStr"/>
+      <c r="F153" t="inlineStr"/>
       <c r="G153" t="n">
         <v>3</v>
       </c>
@@ -4955,14 +4955,14 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>PPI Core Output MoMJAN</t>
+          <t>PPI Input YoYJAN</t>
         </is>
       </c>
       <c r="D157" t="inlineStr"/>
       <c r="E157" t="inlineStr"/>
       <c r="F157" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>-0.8%</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -4982,14 +4982,14 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Core Inflation Rate MoMJAN</t>
+          <t>PPI Core Output MoMJAN</t>
         </is>
       </c>
       <c r="D158" t="inlineStr"/>
       <c r="E158" t="inlineStr"/>
       <c r="F158" t="inlineStr">
         <is>
-          <t>-0.7%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -5009,18 +5009,18 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Inflation Rate MoMJAN</t>
+          <t>PPI Core Output YoYJAN</t>
         </is>
       </c>
       <c r="D159" t="inlineStr"/>
       <c r="E159" t="inlineStr"/>
       <c r="F159" t="inlineStr">
         <is>
-          <t>-0.3%</t>
+          <t>1.3%</t>
         </is>
       </c>
       <c r="G159" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="160">
@@ -5036,22 +5036,22 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Core Inflation Rate YoYJAN</t>
+          <t>PPI Input MoMJAN</t>
         </is>
       </c>
       <c r="D160" t="inlineStr"/>
       <c r="E160" t="inlineStr">
         <is>
-          <t>3.7%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="G160" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="161">
@@ -5067,22 +5067,22 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Inflation Rate YoYJAN</t>
+          <t>PPI Output MoMJAN</t>
         </is>
       </c>
       <c r="D161" t="inlineStr"/>
       <c r="E161" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>2.7%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G161" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="162">
@@ -5098,14 +5098,14 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>PPI Input YoYJAN</t>
+          <t>PPI Output YoYJAN</t>
         </is>
       </c>
       <c r="D162" t="inlineStr"/>
       <c r="E162" t="inlineStr"/>
       <c r="F162" t="inlineStr">
         <is>
-          <t>-0.8%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -5125,18 +5125,14 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>PPI Output MoMJAN</t>
+          <t>Retail Price Index MoMJAN</t>
         </is>
       </c>
       <c r="D163" t="inlineStr"/>
-      <c r="E163" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
+      <c r="E163" t="inlineStr"/>
       <c r="F163" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="G163" t="n">
@@ -5156,14 +5152,18 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>PPI Output YoYJAN</t>
+          <t>Retail Price Index YoYJAN</t>
         </is>
       </c>
       <c r="D164" t="inlineStr"/>
-      <c r="E164" t="inlineStr"/>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>3.7%</t>
+        </is>
+      </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>3.6%</t>
         </is>
       </c>
       <c r="G164" t="n">
@@ -5183,14 +5183,14 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Retail Price Index MoMJAN</t>
+          <t>Core Inflation Rate MoMJAN</t>
         </is>
       </c>
       <c r="D165" t="inlineStr"/>
       <c r="E165" t="inlineStr"/>
       <c r="F165" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>-0.7%</t>
         </is>
       </c>
       <c r="G165" t="n">
@@ -5210,7 +5210,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Retail Price Index YoYJAN</t>
+          <t>Core Inflation Rate YoYJAN</t>
         </is>
       </c>
       <c r="D166" t="inlineStr"/>
@@ -5221,11 +5221,11 @@
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>3.6%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="G166" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="167">
@@ -5241,18 +5241,18 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>PPI Core Output YoYJAN</t>
+          <t>Inflation Rate MoMJAN</t>
         </is>
       </c>
       <c r="D167" t="inlineStr"/>
       <c r="E167" t="inlineStr"/>
       <c r="F167" t="inlineStr">
         <is>
-          <t>1.3%</t>
+          <t>-0.3%</t>
         </is>
       </c>
       <c r="G167" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="168">
@@ -5268,22 +5268,22 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>PPI Input MoMJAN</t>
+          <t>Inflation Rate YoYJAN</t>
         </is>
       </c>
       <c r="D168" t="inlineStr"/>
       <c r="E168" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>2.7%</t>
         </is>
       </c>
       <c r="G168" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="169">
@@ -5326,18 +5326,18 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Deposit Facility RateFEB</t>
+          <t>Lending Facility RateFEB</t>
         </is>
       </c>
       <c r="D170" t="inlineStr"/>
       <c r="E170" t="inlineStr">
         <is>
-          <t>5%</t>
+          <t>6.5%</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>5%</t>
+          <t>6.5%</t>
         </is>
       </c>
       <c r="G170" t="n">
@@ -5357,18 +5357,18 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Lending Facility RateFEB</t>
+          <t>Deposit Facility RateFEB</t>
         </is>
       </c>
       <c r="D171" t="inlineStr"/>
       <c r="E171" t="inlineStr">
         <is>
-          <t>6.5%</t>
+          <t>5%</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>6.5%</t>
+          <t>5%</t>
         </is>
       </c>
       <c r="G171" t="n">
@@ -5441,17 +5441,21 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>EA</t>
+          <t>ZA</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>ECB Non-Monetary Policy Meeting</t>
+          <t>Core Inflation Rate MoMJAN</t>
         </is>
       </c>
       <c r="D174" t="inlineStr"/>
       <c r="E174" t="inlineStr"/>
-      <c r="F174" t="inlineStr"/>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>0.1%</t>
+        </is>
+      </c>
       <c r="G174" t="n">
         <v>3</v>
       </c>
@@ -5469,14 +5473,14 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Inflation Rate MoMJAN</t>
+          <t>Inflation Rate YoYJAN</t>
         </is>
       </c>
       <c r="D175" t="inlineStr"/>
       <c r="E175" t="inlineStr"/>
       <c r="F175" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="G175" t="n">
@@ -5496,14 +5500,14 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Inflation Rate YoYJAN</t>
+          <t>Inflation Rate MoMJAN</t>
         </is>
       </c>
       <c r="D176" t="inlineStr"/>
       <c r="E176" t="inlineStr"/>
       <c r="F176" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="G176" t="n">
@@ -5518,21 +5522,17 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>ZA</t>
+          <t>EA</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Core Inflation Rate MoMJAN</t>
+          <t>ECB Non-Monetary Policy Meeting</t>
         </is>
       </c>
       <c r="D177" t="inlineStr"/>
       <c r="E177" t="inlineStr"/>
-      <c r="F177" t="inlineStr">
-        <is>
-          <t>0.1%</t>
-        </is>
-      </c>
+      <c r="F177" t="inlineStr"/>
       <c r="G177" t="n">
         <v>3</v>
       </c>
@@ -5735,7 +5735,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>6-Month Bill Auction</t>
+          <t>3-Month Bill Auction</t>
         </is>
       </c>
       <c r="D185" t="inlineStr"/>
@@ -5758,7 +5758,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>3-Month Bill Auction</t>
+          <t>6-Month Bill Auction</t>
         </is>
       </c>
       <c r="D186" t="inlineStr"/>
@@ -5827,7 +5827,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsFEB/14</t>
+          <t>MBA Purchase IndexFEB/14</t>
         </is>
       </c>
       <c r="D189" t="inlineStr"/>
@@ -5850,7 +5850,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexFEB/14</t>
+          <t>MBA Mortgage Refinance IndexFEB/14</t>
         </is>
       </c>
       <c r="D190" t="inlineStr"/>
@@ -5873,7 +5873,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexFEB/14</t>
+          <t>MBA Mortgage Market IndexFEB/14</t>
         </is>
       </c>
       <c r="D191" t="inlineStr"/>
@@ -5896,7 +5896,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexFEB/14</t>
+          <t>MBA Mortgage ApplicationsFEB/14</t>
         </is>
       </c>
       <c r="D192" t="inlineStr"/>
@@ -6085,14 +6085,14 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>PPI YoYJAN</t>
+          <t>PPI MoMJAN</t>
         </is>
       </c>
       <c r="D199" t="inlineStr"/>
       <c r="E199" t="inlineStr"/>
       <c r="F199" t="inlineStr">
         <is>
-          <t>8.2%</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="G199" t="n">
@@ -6112,14 +6112,14 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>PPI MoMJAN</t>
+          <t>PPI YoYJAN</t>
         </is>
       </c>
       <c r="D200" t="inlineStr"/>
       <c r="E200" t="inlineStr"/>
       <c r="F200" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>8.2%</t>
         </is>
       </c>
       <c r="G200" t="n">
@@ -6235,18 +6235,18 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Consumer ConfidenceFEB</t>
+          <t>PPI YoYJAN</t>
         </is>
       </c>
       <c r="D205" t="inlineStr"/>
       <c r="E205" t="inlineStr"/>
       <c r="F205" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>1.8%</t>
         </is>
       </c>
       <c r="G205" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="206">
@@ -6289,18 +6289,18 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>PPI YoYJAN</t>
+          <t>Consumer ConfidenceFEB</t>
         </is>
       </c>
       <c r="D207" t="inlineStr"/>
       <c r="E207" t="inlineStr"/>
       <c r="F207" t="inlineStr">
         <is>
-          <t>1.8%</t>
+          <t>93</t>
         </is>
       </c>
       <c r="G207" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="208">
@@ -6362,7 +6362,7 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Foreign Bond InvestmentFEB/15</t>
+          <t>Stock Investment by ForeignersFEB/15</t>
         </is>
       </c>
       <c r="D210" t="inlineStr"/>
@@ -6385,7 +6385,7 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Stock Investment by ForeignersFEB/15</t>
+          <t>Foreign Bond InvestmentFEB/15</t>
         </is>
       </c>
       <c r="D211" t="inlineStr"/>
@@ -6408,22 +6408,22 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Unemployment RateJAN</t>
+          <t>Employment ChangeJAN</t>
         </is>
       </c>
       <c r="D212" t="inlineStr"/>
       <c r="E212" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>20K</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>4.0%</t>
+          <t>23.0K</t>
         </is>
       </c>
       <c r="G212" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="213">
@@ -6439,22 +6439,22 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Employment ChangeJAN</t>
+          <t>Participation RateJAN</t>
         </is>
       </c>
       <c r="D213" t="inlineStr"/>
       <c r="E213" t="inlineStr">
         <is>
-          <t>20K</t>
+          <t>67.1%</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>23.0K</t>
+          <t>67.0%</t>
         </is>
       </c>
       <c r="G213" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="214">
@@ -6470,18 +6470,18 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Full Time Employment ChgJAN</t>
+          <t>Part Time Employment ChgJAN</t>
         </is>
       </c>
       <c r="D214" t="inlineStr"/>
       <c r="E214" t="inlineStr"/>
       <c r="F214" t="inlineStr">
         <is>
-          <t>33.0K</t>
+          <t>-10.0K</t>
         </is>
       </c>
       <c r="G214" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="215">
@@ -6497,18 +6497,18 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Part Time Employment ChgJAN</t>
+          <t>Full Time Employment ChgJAN</t>
         </is>
       </c>
       <c r="D215" t="inlineStr"/>
       <c r="E215" t="inlineStr"/>
       <c r="F215" t="inlineStr">
         <is>
-          <t>-10.0K</t>
+          <t>33.0K</t>
         </is>
       </c>
       <c r="G215" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="216">
@@ -6524,22 +6524,22 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Participation RateJAN</t>
+          <t>Unemployment RateJAN</t>
         </is>
       </c>
       <c r="D216" t="inlineStr"/>
       <c r="E216" t="inlineStr">
         <is>
-          <t>67.1%</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>67.0%</t>
+          <t>4.0%</t>
         </is>
       </c>
       <c r="G216" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="217">
@@ -6555,18 +6555,18 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Loan Prime Rate 5YFEB</t>
+          <t>Loan Prime Rate 1Y</t>
         </is>
       </c>
       <c r="D217" t="inlineStr"/>
       <c r="E217" t="inlineStr">
         <is>
-          <t>3.6%</t>
+          <t>3.1%</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>3.6%</t>
+          <t>3.1%</t>
         </is>
       </c>
       <c r="G217" t="n">
@@ -6586,18 +6586,18 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Loan Prime Rate 1Y</t>
+          <t>Loan Prime Rate 5YFEB</t>
         </is>
       </c>
       <c r="D218" t="inlineStr"/>
       <c r="E218" t="inlineStr">
         <is>
-          <t>3.1%</t>
+          <t>3.6%</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>3.1%</t>
+          <t>3.6%</t>
         </is>
       </c>
       <c r="G218" t="n">
@@ -6639,21 +6639,17 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>ID</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Leading Indicator MoMJAN</t>
+          <t>M2 Money Supply YoYJAN</t>
         </is>
       </c>
       <c r="D220" t="inlineStr"/>
       <c r="E220" t="inlineStr"/>
-      <c r="F220" t="inlineStr">
-        <is>
-          <t>1.5%</t>
-        </is>
-      </c>
+      <c r="F220" t="inlineStr"/>
       <c r="G220" t="n">
         <v>3</v>
       </c>
@@ -6693,17 +6689,21 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>ID</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>M2 Money Supply YoYJAN</t>
+          <t>Leading Indicator MoMJAN</t>
         </is>
       </c>
       <c r="D222" t="inlineStr"/>
       <c r="E222" t="inlineStr"/>
-      <c r="F222" t="inlineStr"/>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>1.5%</t>
+        </is>
+      </c>
       <c r="G222" t="n">
         <v>3</v>
       </c>
@@ -6716,19 +6716,19 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>TR</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Consumer ConfidenceFEB</t>
+          <t>PPI YoYJAN</t>
         </is>
       </c>
       <c r="D223" t="inlineStr"/>
       <c r="E223" t="inlineStr"/>
       <c r="F223" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>1.1%</t>
         </is>
       </c>
       <c r="G223" t="n">
@@ -6743,27 +6743,23 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>TR</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>PPI MoMJAN</t>
+          <t>Consumer ConfidenceFEB</t>
         </is>
       </c>
       <c r="D224" t="inlineStr"/>
-      <c r="E224" t="inlineStr">
-        <is>
-          <t>0.6%</t>
-        </is>
-      </c>
+      <c r="E224" t="inlineStr"/>
       <c r="F224" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>80</t>
         </is>
       </c>
       <c r="G224" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="225">
@@ -6779,18 +6775,22 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>PPI YoYJAN</t>
+          <t>PPI MoMJAN</t>
         </is>
       </c>
       <c r="D225" t="inlineStr"/>
-      <c r="E225" t="inlineStr"/>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>0.6%</t>
+        </is>
+      </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>1.1%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="G225" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="226">
@@ -6833,7 +6833,7 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>8-Year Obligacion Auction</t>
+          <t>3-Year Bonos Auction</t>
         </is>
       </c>
       <c r="D227" t="inlineStr"/>
@@ -6879,7 +6879,7 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>3-Year Bonos Auction</t>
+          <t>8-Year Obligacion Auction</t>
         </is>
       </c>
       <c r="D229" t="inlineStr"/>
@@ -6897,17 +6897,21 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>EA</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>5-Year OAT Auction</t>
+          <t>Construction Output YoYDEC</t>
         </is>
       </c>
       <c r="D230" t="inlineStr"/>
       <c r="E230" t="inlineStr"/>
-      <c r="F230" t="inlineStr"/>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>-0.5%</t>
+        </is>
+      </c>
       <c r="G230" t="n">
         <v>3</v>
       </c>
@@ -6925,7 +6929,7 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>4-Year OAT Auction</t>
+          <t>3-Year OAT Auction</t>
         </is>
       </c>
       <c r="D231" t="inlineStr"/>
@@ -6948,7 +6952,7 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>3-Year OAT Auction</t>
+          <t>4-Year OAT Auction</t>
         </is>
       </c>
       <c r="D232" t="inlineStr"/>
@@ -6966,21 +6970,17 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>EA</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Construction Output YoYDEC</t>
+          <t>5-Year OAT Auction</t>
         </is>
       </c>
       <c r="D233" t="inlineStr"/>
       <c r="E233" t="inlineStr"/>
-      <c r="F233" t="inlineStr">
-        <is>
-          <t>-0.5%</t>
-        </is>
-      </c>
+      <c r="F233" t="inlineStr"/>
       <c r="G233" t="n">
         <v>3</v>
       </c>
@@ -7062,27 +7062,23 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>ZA</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>CBI Industrial Trends OrdersFEB</t>
+          <t>Building Permits YoYDEC</t>
         </is>
       </c>
       <c r="D237" t="inlineStr"/>
-      <c r="E237" t="inlineStr">
-        <is>
-          <t>-30</t>
-        </is>
-      </c>
+      <c r="E237" t="inlineStr"/>
       <c r="F237" t="inlineStr">
         <is>
-          <t>-25</t>
+          <t>18.0%</t>
         </is>
       </c>
       <c r="G237" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="238">
@@ -7093,23 +7089,27 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>ZA</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Building Permits YoYDEC</t>
+          <t>CBI Industrial Trends OrdersFEB</t>
         </is>
       </c>
       <c r="D238" t="inlineStr"/>
-      <c r="E238" t="inlineStr"/>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t>-30</t>
+        </is>
+      </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>18.0%</t>
+          <t>-25</t>
         </is>
       </c>
       <c r="G238" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="239">
@@ -7171,14 +7171,14 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Retail Sales YoYDEC</t>
+          <t>Retail Sales MoMDEC</t>
         </is>
       </c>
       <c r="D241" t="inlineStr"/>
       <c r="E241" t="inlineStr"/>
       <c r="F241" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>-0.4%</t>
         </is>
       </c>
       <c r="G241" t="n">
@@ -7198,14 +7198,14 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Retail Sales MoMDEC</t>
+          <t>Retail Sales YoYDEC</t>
         </is>
       </c>
       <c r="D242" t="inlineStr"/>
       <c r="E242" t="inlineStr"/>
       <c r="F242" t="inlineStr">
         <is>
-          <t>-0.4%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="G242" t="n">
@@ -7225,22 +7225,18 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/15</t>
+          <t>Continuing Jobless ClaimsFEB/08</t>
         </is>
       </c>
       <c r="D243" t="inlineStr"/>
-      <c r="E243" t="inlineStr">
-        <is>
-          <t>216K</t>
-        </is>
-      </c>
+      <c r="E243" t="inlineStr"/>
       <c r="F243" t="inlineStr">
         <is>
-          <t>220.0K</t>
+          <t>1879.0K</t>
         </is>
       </c>
       <c r="G243" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="244">
@@ -7256,18 +7252,22 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/15</t>
+          <t>Initial Jobless ClaimsFEB/15</t>
         </is>
       </c>
       <c r="D244" t="inlineStr"/>
-      <c r="E244" t="inlineStr"/>
+      <c r="E244" t="inlineStr">
+        <is>
+          <t>216K</t>
+        </is>
+      </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>219.0K</t>
+          <t>220.0K</t>
         </is>
       </c>
       <c r="G244" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="245">
@@ -7314,14 +7314,14 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/08</t>
+          <t>Jobless Claims 4-week AverageFEB/15</t>
         </is>
       </c>
       <c r="D246" t="inlineStr"/>
       <c r="E246" t="inlineStr"/>
       <c r="F246" t="inlineStr">
         <is>
-          <t>1879.0K</t>
+          <t>219.0K</t>
         </is>
       </c>
       <c r="G246" t="n">
@@ -7456,14 +7456,14 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Raw Materials Prices MoMJAN</t>
+          <t>Raw Materials Prices YoYJAN</t>
         </is>
       </c>
       <c r="D252" t="inlineStr"/>
       <c r="E252" t="inlineStr"/>
       <c r="F252" t="inlineStr">
         <is>
-          <t>-0.2%</t>
+          <t>10.0%</t>
         </is>
       </c>
       <c r="G252" t="n">
@@ -7483,14 +7483,14 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>PPI YoYJAN</t>
+          <t>Raw Materials Prices MoMJAN</t>
         </is>
       </c>
       <c r="D253" t="inlineStr"/>
       <c r="E253" t="inlineStr"/>
       <c r="F253" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>-0.2%</t>
         </is>
       </c>
       <c r="G253" t="n">
@@ -7510,14 +7510,14 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Raw Materials Prices YoYJAN</t>
+          <t>PPI YoYJAN</t>
         </is>
       </c>
       <c r="D254" t="inlineStr"/>
       <c r="E254" t="inlineStr"/>
       <c r="F254" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="G254" t="n">
@@ -7849,7 +7849,7 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateFEB/20</t>
+          <t>30-Year Mortgage RateFEB/20</t>
         </is>
       </c>
       <c r="D267" t="inlineStr"/>
@@ -7872,7 +7872,7 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/14</t>
+          <t>EIA Crude Oil Imports ChangeFEB/14</t>
         </is>
       </c>
       <c r="D268" t="inlineStr"/>
@@ -7895,7 +7895,7 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/14</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="D269" t="inlineStr"/>
@@ -7918,7 +7918,7 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/14</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/14</t>
         </is>
       </c>
       <c r="D270" t="inlineStr"/>
@@ -7941,7 +7941,7 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/14</t>
+          <t>EIA Distillate Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="D271" t="inlineStr"/>
@@ -7964,7 +7964,7 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/14</t>
+          <t>EIA Gasoline Production ChangeFEB/14</t>
         </is>
       </c>
       <c r="D272" t="inlineStr"/>
@@ -7987,7 +7987,7 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/14</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="D273" t="inlineStr"/>
@@ -8010,7 +8010,7 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/14</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/14</t>
         </is>
       </c>
       <c r="D274" t="inlineStr"/>
@@ -8033,14 +8033,14 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/14</t>
+          <t>15-Year Mortgage RateFEB/20</t>
         </is>
       </c>
       <c r="D275" t="inlineStr"/>
       <c r="E275" t="inlineStr"/>
       <c r="F275" t="inlineStr"/>
       <c r="G275" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="276">
@@ -8056,14 +8056,14 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateFEB/20</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="D276" t="inlineStr"/>
       <c r="E276" t="inlineStr"/>
       <c r="F276" t="inlineStr"/>
       <c r="G276" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="277">
@@ -8074,19 +8074,19 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>US</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>2-Year Bond Auction</t>
+          <t>EIA Gasoline Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="D277" t="inlineStr"/>
       <c r="E277" t="inlineStr"/>
       <c r="F277" t="inlineStr"/>
       <c r="G277" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="278">
@@ -8097,19 +8097,19 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/14</t>
+          <t>2-Year Bond Auction</t>
         </is>
       </c>
       <c r="D278" t="inlineStr"/>
       <c r="E278" t="inlineStr"/>
       <c r="F278" t="inlineStr"/>
       <c r="G278" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="279">
@@ -8244,14 +8244,14 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>S&amp;P Global Australia Services PMI FlashFEB</t>
+          <t>S&amp;P Global Australia Manufacturing PMI FlashFEB</t>
         </is>
       </c>
       <c r="D284" t="inlineStr"/>
       <c r="E284" t="inlineStr"/>
       <c r="F284" t="inlineStr">
         <is>
-          <t>51.3</t>
+          <t>49.9</t>
         </is>
       </c>
       <c r="G284" t="n">
@@ -8266,17 +8266,21 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>Fed Kugler Speech</t>
+          <t>S&amp;P Global Australia Services PMI FlashFEB</t>
         </is>
       </c>
       <c r="D285" t="inlineStr"/>
       <c r="E285" t="inlineStr"/>
-      <c r="F285" t="inlineStr"/>
+      <c r="F285" t="inlineStr">
+        <is>
+          <t>51.3</t>
+        </is>
+      </c>
       <c r="G285" t="n">
         <v>2</v>
       </c>
@@ -8294,18 +8298,18 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>S&amp;P Global Australia Manufacturing PMI FlashFEB</t>
+          <t>S&amp;P Global Australia Composite PMI FlashFEB</t>
         </is>
       </c>
       <c r="D286" t="inlineStr"/>
       <c r="E286" t="inlineStr"/>
       <c r="F286" t="inlineStr">
         <is>
-          <t>49.9</t>
+          <t>50.6</t>
         </is>
       </c>
       <c r="G286" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="287">
@@ -8316,23 +8320,19 @@
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>US</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>S&amp;P Global Australia Composite PMI FlashFEB</t>
+          <t>Fed Kugler Speech</t>
         </is>
       </c>
       <c r="D287" t="inlineStr"/>
       <c r="E287" t="inlineStr"/>
-      <c r="F287" t="inlineStr">
-        <is>
-          <t>50.6</t>
-        </is>
-      </c>
+      <c r="F287" t="inlineStr"/>
       <c r="G287" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="288">
@@ -8375,18 +8375,18 @@
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>Inflation Rate MoMJAN</t>
+          <t>Inflation Rate YoYJAN</t>
         </is>
       </c>
       <c r="D289" t="inlineStr"/>
       <c r="E289" t="inlineStr"/>
       <c r="F289" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>3.7%</t>
         </is>
       </c>
       <c r="G289" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="290">
@@ -8402,18 +8402,22 @@
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>Inflation Rate Ex-Food and Energy YoYJAN</t>
+          <t>Core Inflation Rate YoYJAN</t>
         </is>
       </c>
       <c r="D290" t="inlineStr"/>
-      <c r="E290" t="inlineStr"/>
+      <c r="E290" t="inlineStr">
+        <is>
+          <t>3.1%</t>
+        </is>
+      </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="G290" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="291">
@@ -8429,22 +8433,18 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>Core Inflation Rate YoYJAN</t>
+          <t>Inflation Rate Ex-Food and Energy YoYJAN</t>
         </is>
       </c>
       <c r="D291" t="inlineStr"/>
-      <c r="E291" t="inlineStr">
-        <is>
-          <t>3.1%</t>
-        </is>
-      </c>
+      <c r="E291" t="inlineStr"/>
       <c r="F291" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>2.6%</t>
         </is>
       </c>
       <c r="G291" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="292">
@@ -8460,18 +8460,18 @@
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>Inflation Rate YoYJAN</t>
+          <t>Inflation Rate MoMJAN</t>
         </is>
       </c>
       <c r="D292" t="inlineStr"/>
       <c r="E292" t="inlineStr"/>
       <c r="F292" t="inlineStr">
         <is>
-          <t>3.7%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G292" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="293">
@@ -8603,7 +8603,7 @@
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>6-Month LTN Auction</t>
+          <t>2-Year LTN Auction</t>
         </is>
       </c>
       <c r="D297" t="inlineStr"/>
@@ -8626,7 +8626,7 @@
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>2-Year LTN Auction</t>
+          <t>10-Year NTN-F Auction</t>
         </is>
       </c>
       <c r="D298" t="inlineStr"/>
@@ -8644,17 +8644,21 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>TR</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>10-Year NTN-F Auction</t>
+          <t>Central Government DebtJAN</t>
         </is>
       </c>
       <c r="D299" t="inlineStr"/>
       <c r="E299" t="inlineStr"/>
-      <c r="F299" t="inlineStr"/>
+      <c r="F299" t="inlineStr">
+        <is>
+          <t>TRY 9.4T</t>
+        </is>
+      </c>
       <c r="G299" t="n">
         <v>3</v>
       </c>
@@ -8690,21 +8694,17 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>TR</t>
+          <t>BR</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>Central Government DebtJAN</t>
+          <t>6-Month LTN Auction</t>
         </is>
       </c>
       <c r="D301" t="inlineStr"/>
       <c r="E301" t="inlineStr"/>
-      <c r="F301" t="inlineStr">
-        <is>
-          <t>TRY 9.4T</t>
-        </is>
-      </c>
+      <c r="F301" t="inlineStr"/>
       <c r="G301" t="n">
         <v>3</v>
       </c>
@@ -8722,14 +8722,14 @@
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>HSBC Services PMI FlashFEB</t>
+          <t>HSBC Composite PMI FlashFEB</t>
         </is>
       </c>
       <c r="D302" t="inlineStr"/>
       <c r="E302" t="inlineStr"/>
       <c r="F302" t="inlineStr">
         <is>
-          <t>57.5</t>
+          <t>58.2</t>
         </is>
       </c>
       <c r="G302" t="n">
@@ -8749,14 +8749,14 @@
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>HSBC Manufacturing PMI FlashFEB</t>
+          <t>HSBC Services PMI FlashFEB</t>
         </is>
       </c>
       <c r="D303" t="inlineStr"/>
       <c r="E303" t="inlineStr"/>
       <c r="F303" t="inlineStr">
         <is>
-          <t>57.9</t>
+          <t>57.5</t>
         </is>
       </c>
       <c r="G303" t="n">
@@ -8776,14 +8776,14 @@
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>HSBC Composite PMI FlashFEB</t>
+          <t>HSBC Manufacturing PMI FlashFEB</t>
         </is>
       </c>
       <c r="D304" t="inlineStr"/>
       <c r="E304" t="inlineStr"/>
       <c r="F304" t="inlineStr">
         <is>
-          <t>58.2</t>
+          <t>57.9</t>
         </is>
       </c>
       <c r="G304" t="n">
@@ -9050,18 +9050,18 @@
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>HCOB Services PMI FlashFEB</t>
+          <t>HCOB Manufacturing PMI FlashFEB</t>
         </is>
       </c>
       <c r="D314" t="inlineStr"/>
       <c r="E314" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>45.3</t>
         </is>
       </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>45.4</t>
         </is>
       </c>
       <c r="G314" t="n">
@@ -9081,18 +9081,18 @@
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>HCOB Manufacturing PMI FlashFEB</t>
+          <t>HCOB Services PMI FlashFEB</t>
         </is>
       </c>
       <c r="D315" t="inlineStr"/>
       <c r="E315" t="inlineStr">
         <is>
-          <t>45.3</t>
+          <t>49</t>
         </is>
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t>45.4</t>
+          <t>48</t>
         </is>
       </c>
       <c r="G315" t="n">
@@ -9112,22 +9112,22 @@
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>HCOB Services PMI FlashFEB</t>
+          <t>HCOB Manufacturing PMI FlashFEB</t>
         </is>
       </c>
       <c r="D316" t="inlineStr"/>
       <c r="E316" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>45.5</t>
         </is>
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t>51.9</t>
+          <t>45.1</t>
         </is>
       </c>
       <c r="G316" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="317">
@@ -9170,22 +9170,22 @@
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>HCOB Manufacturing PMI FlashFEB</t>
+          <t>HCOB Services PMI FlashFEB</t>
         </is>
       </c>
       <c r="D318" t="inlineStr"/>
       <c r="E318" t="inlineStr">
         <is>
-          <t>45.5</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="F318" t="inlineStr">
         <is>
-          <t>45.1</t>
+          <t>51.9</t>
         </is>
       </c>
       <c r="G318" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="319">
@@ -9196,19 +9196,23 @@
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>EA</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>HCOB Composite PMI FlashFEB</t>
+          <t>Inflation Rate YoY FinalJAN</t>
         </is>
       </c>
       <c r="D319" t="inlineStr"/>
-      <c r="E319" t="inlineStr"/>
+      <c r="E319" t="inlineStr">
+        <is>
+          <t>1.5%</t>
+        </is>
+      </c>
       <c r="F319" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>1.5%</t>
         </is>
       </c>
       <c r="G319" t="n">
@@ -9223,27 +9227,27 @@
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>EA</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>HCOB Manufacturing PMI FlashFEB</t>
+          <t>Harmonised Inflation Rate YoY FinalJAN</t>
         </is>
       </c>
       <c r="D320" t="inlineStr"/>
       <c r="E320" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>1.7%</t>
         </is>
       </c>
       <c r="F320" t="inlineStr">
         <is>
-          <t>46.8</t>
+          <t>1.7%</t>
         </is>
       </c>
       <c r="G320" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="321">
@@ -9290,18 +9294,18 @@
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>Inflation Rate YoY FinalJAN</t>
+          <t>Inflation Rate MoM FinalJAN</t>
         </is>
       </c>
       <c r="D322" t="inlineStr"/>
       <c r="E322" t="inlineStr">
         <is>
-          <t>1.5%</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t>1.5%</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="G322" t="n">
@@ -9316,27 +9320,27 @@
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>EA</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>Harmonised Inflation Rate YoY FinalJAN</t>
+          <t>HCOB Services PMI FlashFEB</t>
         </is>
       </c>
       <c r="D323" t="inlineStr"/>
       <c r="E323" t="inlineStr">
         <is>
-          <t>1.7%</t>
+          <t>51.5</t>
         </is>
       </c>
       <c r="F323" t="inlineStr">
         <is>
-          <t>1.7%</t>
+          <t>51.2</t>
         </is>
       </c>
       <c r="G323" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="324">
@@ -9347,23 +9351,23 @@
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>EA</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>Inflation Rate MoM FinalJAN</t>
+          <t>HCOB Manufacturing PMI FlashFEB</t>
         </is>
       </c>
       <c r="D324" t="inlineStr"/>
       <c r="E324" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>47</t>
         </is>
       </c>
       <c r="F324" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>46.8</t>
         </is>
       </c>
       <c r="G324" t="n">
@@ -9383,18 +9387,14 @@
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>HCOB Services PMI FlashFEB</t>
+          <t>HCOB Composite PMI FlashFEB</t>
         </is>
       </c>
       <c r="D325" t="inlineStr"/>
-      <c r="E325" t="inlineStr">
-        <is>
-          <t>51.5</t>
-        </is>
-      </c>
+      <c r="E325" t="inlineStr"/>
       <c r="F325" t="inlineStr">
         <is>
-          <t>51.2</t>
+          <t>50</t>
         </is>
       </c>
       <c r="G325" t="n">
@@ -9414,18 +9414,18 @@
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>S&amp;P Global Manufacturing PMI FlashFEB</t>
+          <t>S&amp;P Global Services PMI FlashFEB</t>
         </is>
       </c>
       <c r="D326" t="inlineStr"/>
       <c r="E326" t="inlineStr">
         <is>
-          <t>48.5</t>
+          <t>51</t>
         </is>
       </c>
       <c r="F326" t="inlineStr">
         <is>
-          <t>48.5</t>
+          <t>51</t>
         </is>
       </c>
       <c r="G326" t="n">
@@ -9445,18 +9445,18 @@
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>S&amp;P Global Services PMI FlashFEB</t>
+          <t>S&amp;P Global Manufacturing PMI FlashFEB</t>
         </is>
       </c>
       <c r="D327" t="inlineStr"/>
       <c r="E327" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>48.5</t>
         </is>
       </c>
       <c r="F327" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>48.5</t>
         </is>
       </c>
       <c r="G327" t="n">
@@ -9503,14 +9503,14 @@
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>Foreign Exchange ReservesFEB/14</t>
+          <t>Monetary Policy Meeting Minutes</t>
         </is>
       </c>
       <c r="D329" t="inlineStr"/>
       <c r="E329" t="inlineStr"/>
       <c r="F329" t="inlineStr"/>
       <c r="G329" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="330">
@@ -9526,14 +9526,14 @@
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>Monetary Policy Meeting Minutes</t>
+          <t>Foreign Exchange ReservesFEB/14</t>
         </is>
       </c>
       <c r="D330" t="inlineStr"/>
       <c r="E330" t="inlineStr"/>
       <c r="F330" t="inlineStr"/>
       <c r="G330" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="331">
@@ -9549,18 +9549,22 @@
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>Economic Activity MoMDEC</t>
+          <t>GDP Growth Rate QoQ FinalQ4</t>
         </is>
       </c>
       <c r="D331" t="inlineStr"/>
-      <c r="E331" t="inlineStr"/>
+      <c r="E331" t="inlineStr">
+        <is>
+          <t>-0.6%</t>
+        </is>
+      </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>-0.6%</t>
         </is>
       </c>
       <c r="G331" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="332">
@@ -9576,22 +9580,18 @@
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>GDP Growth Rate QoQ FinalQ4</t>
+          <t>Economic Activity YoYDEC</t>
         </is>
       </c>
       <c r="D332" t="inlineStr"/>
-      <c r="E332" t="inlineStr">
-        <is>
-          <t>-0.6%</t>
-        </is>
-      </c>
+      <c r="E332" t="inlineStr"/>
       <c r="F332" t="inlineStr">
         <is>
-          <t>-0.6%</t>
+          <t>2%</t>
         </is>
       </c>
       <c r="G332" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="333">
@@ -9607,22 +9607,18 @@
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>GDP Growth Rate YoY FinalQ4</t>
+          <t>Economic Activity MoMDEC</t>
         </is>
       </c>
       <c r="D333" t="inlineStr"/>
-      <c r="E333" t="inlineStr">
-        <is>
-          <t>0.6%</t>
-        </is>
-      </c>
+      <c r="E333" t="inlineStr"/>
       <c r="F333" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="G333" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="334">
@@ -9638,18 +9634,22 @@
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>Economic Activity YoYDEC</t>
+          <t>GDP Growth Rate YoY FinalQ4</t>
         </is>
       </c>
       <c r="D334" t="inlineStr"/>
-      <c r="E334" t="inlineStr"/>
+      <c r="E334" t="inlineStr">
+        <is>
+          <t>0.6%</t>
+        </is>
+      </c>
       <c r="F334" t="inlineStr">
         <is>
-          <t>2%</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="G334" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="335">
@@ -9804,15 +9804,11 @@
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>S&amp;P Global Services PMI FlashFEB</t>
+          <t>S&amp;P Global Composite PMI FlashFEB</t>
         </is>
       </c>
       <c r="D340" t="inlineStr"/>
-      <c r="E340" t="inlineStr">
-        <is>
-          <t>53.2</t>
-        </is>
-      </c>
+      <c r="E340" t="inlineStr"/>
       <c r="F340" t="inlineStr">
         <is>
           <t>52.7</t>
@@ -9835,14 +9831,18 @@
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>S&amp;P Global Manufacturing PMI FlashFEB</t>
+          <t>S&amp;P Global Services PMI FlashFEB</t>
         </is>
       </c>
       <c r="D341" t="inlineStr"/>
-      <c r="E341" t="inlineStr"/>
+      <c r="E341" t="inlineStr">
+        <is>
+          <t>53.2</t>
+        </is>
+      </c>
       <c r="F341" t="inlineStr">
         <is>
-          <t>51.3</t>
+          <t>52.7</t>
         </is>
       </c>
       <c r="G341" t="n">
@@ -9862,14 +9862,14 @@
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>S&amp;P Global Composite PMI FlashFEB</t>
+          <t>S&amp;P Global Manufacturing PMI FlashFEB</t>
         </is>
       </c>
       <c r="D342" t="inlineStr"/>
       <c r="E342" t="inlineStr"/>
       <c r="F342" t="inlineStr">
         <is>
-          <t>52.7</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="G342" t="n">
@@ -9889,18 +9889,18 @@
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>Michigan 5 Year Inflation Expectations FinalFEB</t>
+          <t>Michigan Inflation Expectations FinalFEB</t>
         </is>
       </c>
       <c r="D343" t="inlineStr"/>
       <c r="E343" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="F343" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="G343" t="n">
@@ -9920,18 +9920,22 @@
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>Existing Home Sales MoMJAN</t>
+          <t>Michigan Current Conditions FinalFEB</t>
         </is>
       </c>
       <c r="D344" t="inlineStr"/>
-      <c r="E344" t="inlineStr"/>
+      <c r="E344" t="inlineStr">
+        <is>
+          <t>68.7</t>
+        </is>
+      </c>
       <c r="F344" t="inlineStr">
         <is>
-          <t>-1.7%</t>
+          <t>68.7</t>
         </is>
       </c>
       <c r="G344" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="345">
@@ -9947,18 +9951,18 @@
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>Michigan Inflation Expectations FinalFEB</t>
+          <t>Michigan Consumer Expectations FinalFEB</t>
         </is>
       </c>
       <c r="D345" t="inlineStr"/>
       <c r="E345" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>67.3</t>
         </is>
       </c>
       <c r="F345" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>67.3</t>
         </is>
       </c>
       <c r="G345" t="n">
@@ -9978,18 +9982,18 @@
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>Michigan Current Conditions FinalFEB</t>
+          <t>Michigan 5 Year Inflation Expectations FinalFEB</t>
         </is>
       </c>
       <c r="D346" t="inlineStr"/>
       <c r="E346" t="inlineStr">
         <is>
-          <t>68.7</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F346" t="inlineStr">
         <is>
-          <t>68.7</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="G346" t="n">
@@ -10009,22 +10013,22 @@
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>Michigan Consumer Expectations FinalFEB</t>
+          <t>Michigan Consumer Sentiment FinalFEB</t>
         </is>
       </c>
       <c r="D347" t="inlineStr"/>
       <c r="E347" t="inlineStr">
         <is>
-          <t>67.3</t>
+          <t>67.8</t>
         </is>
       </c>
       <c r="F347" t="inlineStr">
         <is>
-          <t>67.3</t>
+          <t>67.8</t>
         </is>
       </c>
       <c r="G347" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="348">
@@ -10040,22 +10044,22 @@
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>Michigan Consumer Sentiment FinalFEB</t>
+          <t>Existing Home SalesJAN</t>
         </is>
       </c>
       <c r="D348" t="inlineStr"/>
       <c r="E348" t="inlineStr">
         <is>
-          <t>67.8</t>
+          <t>4.17M</t>
         </is>
       </c>
       <c r="F348" t="inlineStr">
         <is>
-          <t>67.8</t>
+          <t>4.16M</t>
         </is>
       </c>
       <c r="G348" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="349">
@@ -10071,22 +10075,18 @@
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>Existing Home SalesJAN</t>
+          <t>Existing Home Sales MoMJAN</t>
         </is>
       </c>
       <c r="D349" t="inlineStr"/>
-      <c r="E349" t="inlineStr">
-        <is>
-          <t>4.17M</t>
-        </is>
-      </c>
+      <c r="E349" t="inlineStr"/>
       <c r="F349" t="inlineStr">
         <is>
-          <t>4.16M</t>
+          <t>-1.7%</t>
         </is>
       </c>
       <c r="G349" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="350">
@@ -10148,7 +10148,7 @@
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>Baker Hughes Total Rigs CountFEB/21</t>
+          <t>Baker Hughes Oil Rig CountFEB/21</t>
         </is>
       </c>
       <c r="D352" t="inlineStr"/>
@@ -10221,7 +10221,7 @@
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>Baker Hughes Oil Rig CountFEB/21</t>
+          <t>Baker Hughes Total Rigs CountFEB/21</t>
         </is>
       </c>
       <c r="D355" t="inlineStr"/>
@@ -10369,14 +10369,14 @@
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>Business ConfidenceFEB</t>
+          <t>Capacity UtilizationFEB</t>
         </is>
       </c>
       <c r="D361" t="inlineStr"/>
       <c r="E361" t="inlineStr"/>
       <c r="F361" t="inlineStr"/>
       <c r="G361" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="362">
@@ -10392,14 +10392,14 @@
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>Capacity UtilizationFEB</t>
+          <t>Business ConfidenceFEB</t>
         </is>
       </c>
       <c r="D362" t="inlineStr"/>
       <c r="E362" t="inlineStr"/>
       <c r="F362" t="inlineStr"/>
       <c r="G362" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="363">
@@ -10415,18 +10415,18 @@
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>Ifo Business ClimateFEB</t>
+          <t>Ifo ExpectationsFEB</t>
         </is>
       </c>
       <c r="D363" t="inlineStr"/>
       <c r="E363" t="inlineStr"/>
       <c r="F363" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>83</t>
         </is>
       </c>
       <c r="G363" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="364">
@@ -10469,18 +10469,18 @@
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>Ifo ExpectationsFEB</t>
+          <t>Ifo Business ClimateFEB</t>
         </is>
       </c>
       <c r="D365" t="inlineStr"/>
       <c r="E365" t="inlineStr"/>
       <c r="F365" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>84</t>
         </is>
       </c>
       <c r="G365" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="366">
@@ -10712,7 +10712,7 @@
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>Mid-month Core Inflation Rate MoMFEB</t>
+          <t>Mid-month Core Inflation Rate YoYFEB</t>
         </is>
       </c>
       <c r="D374" t="inlineStr"/>
@@ -10781,7 +10781,7 @@
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>Mid-month Core Inflation Rate YoYFEB</t>
+          <t>Mid-month Core Inflation Rate MoMFEB</t>
         </is>
       </c>
       <c r="D377" t="inlineStr"/>
@@ -10942,7 +10942,7 @@
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>6-Month Bill Auction</t>
+          <t>3-Month Bill Auction</t>
         </is>
       </c>
       <c r="D384" t="inlineStr"/>
@@ -10965,7 +10965,7 @@
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>3-Month Bill Auction</t>
+          <t>6-Month Bill Auction</t>
         </is>
       </c>
       <c r="D385" t="inlineStr"/>
@@ -11107,14 +11107,14 @@
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>ImportsDEC</t>
+          <t>ExportsDEC</t>
         </is>
       </c>
       <c r="D391" t="inlineStr"/>
       <c r="E391" t="inlineStr"/>
       <c r="F391" t="inlineStr">
         <is>
-          <t>SAR 60.5B</t>
+          <t>SAR 94.5B</t>
         </is>
       </c>
       <c r="G391" t="n">
@@ -11161,14 +11161,14 @@
       </c>
       <c r="C393" t="inlineStr">
         <is>
-          <t>ExportsDEC</t>
+          <t>ImportsDEC</t>
         </is>
       </c>
       <c r="D393" t="inlineStr"/>
       <c r="E393" t="inlineStr"/>
       <c r="F393" t="inlineStr">
         <is>
-          <t>SAR 94.5B</t>
+          <t>SAR 60.5B</t>
         </is>
       </c>
       <c r="G393" t="n">
@@ -11183,23 +11183,27 @@
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>ZA</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>Leading Business Cycle Indicator MoMDEC</t>
+          <t>GDP Growth Rate QoQ FinalQ4</t>
         </is>
       </c>
       <c r="D394" t="inlineStr"/>
-      <c r="E394" t="inlineStr"/>
+      <c r="E394" t="inlineStr">
+        <is>
+          <t>-0.2%</t>
+        </is>
+      </c>
       <c r="F394" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>-0.2%</t>
         </is>
       </c>
       <c r="G394" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="395">
@@ -11210,27 +11214,23 @@
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>ZA</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>GDP Growth Rate QoQ FinalQ4</t>
+          <t>Leading Business Cycle Indicator MoMDEC</t>
         </is>
       </c>
       <c r="D395" t="inlineStr"/>
-      <c r="E395" t="inlineStr">
-        <is>
-          <t>-0.2%</t>
-        </is>
-      </c>
+      <c r="E395" t="inlineStr"/>
       <c r="F395" t="inlineStr">
         <is>
-          <t>-0.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G395" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="396">
@@ -11241,25 +11241,17 @@
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>EU</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>GDP Growth Rate YoY FinalQ4</t>
+          <t>New Car Registrations YoYJAN</t>
         </is>
       </c>
       <c r="D396" t="inlineStr"/>
-      <c r="E396" t="inlineStr">
-        <is>
-          <t>-0.2%</t>
-        </is>
-      </c>
-      <c r="F396" t="inlineStr">
-        <is>
-          <t>-0.2%</t>
-        </is>
-      </c>
+      <c r="E396" t="inlineStr"/>
+      <c r="F396" t="inlineStr"/>
       <c r="G396" t="n">
         <v>2</v>
       </c>
@@ -11272,17 +11264,25 @@
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>EU</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>New Car Registrations YoYJAN</t>
+          <t>GDP Growth Rate YoY FinalQ4</t>
         </is>
       </c>
       <c r="D397" t="inlineStr"/>
-      <c r="E397" t="inlineStr"/>
-      <c r="F397" t="inlineStr"/>
+      <c r="E397" t="inlineStr">
+        <is>
+          <t>-0.2%</t>
+        </is>
+      </c>
+      <c r="F397" t="inlineStr">
+        <is>
+          <t>-0.2%</t>
+        </is>
+      </c>
       <c r="G397" t="n">
         <v>2</v>
       </c>
@@ -11569,7 +11569,7 @@
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>House Price Index MoMDEC</t>
+          <t>House Price Index YoYDEC</t>
         </is>
       </c>
       <c r="D409" t="inlineStr"/>
@@ -11592,14 +11592,18 @@
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price MoMDEC</t>
+          <t>S&amp;P/Case-Shiller Home Price YoYDEC</t>
         </is>
       </c>
       <c r="D410" t="inlineStr"/>
       <c r="E410" t="inlineStr"/>
-      <c r="F410" t="inlineStr"/>
+      <c r="F410" t="inlineStr">
+        <is>
+          <t>4.2%</t>
+        </is>
+      </c>
       <c r="G410" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="411">
@@ -11642,7 +11646,7 @@
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>House Price Index YoYDEC</t>
+          <t>S&amp;P/Case-Shiller Home Price MoMDEC</t>
         </is>
       </c>
       <c r="D412" t="inlineStr"/>
@@ -11665,7 +11669,7 @@
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>House Price IndexDEC</t>
+          <t>House Price Index MoMDEC</t>
         </is>
       </c>
       <c r="D413" t="inlineStr"/>
@@ -11688,18 +11692,14 @@
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price YoYDEC</t>
+          <t>House Price IndexDEC</t>
         </is>
       </c>
       <c r="D414" t="inlineStr"/>
       <c r="E414" t="inlineStr"/>
-      <c r="F414" t="inlineStr">
-        <is>
-          <t>4.2%</t>
-        </is>
-      </c>
+      <c r="F414" t="inlineStr"/>
       <c r="G414" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="415">
@@ -11710,23 +11710,19 @@
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>EA</t>
+          <t>US</t>
         </is>
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>Negotiated Wage GrowthQ4</t>
+          <t>CB Consumer ConfidenceFEB</t>
         </is>
       </c>
       <c r="D415" t="inlineStr"/>
       <c r="E415" t="inlineStr"/>
-      <c r="F415" t="inlineStr">
-        <is>
-          <t>5.1%</t>
-        </is>
-      </c>
+      <c r="F415" t="inlineStr"/>
       <c r="G415" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="416">
@@ -11737,17 +11733,21 @@
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>MX</t>
         </is>
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>Richmond Fed Manufacturing Shipments IndexFEB</t>
+          <t>Current AccountQ4</t>
         </is>
       </c>
       <c r="D416" t="inlineStr"/>
       <c r="E416" t="inlineStr"/>
-      <c r="F416" t="inlineStr"/>
+      <c r="F416" t="inlineStr">
+        <is>
+          <t>$ 7500M</t>
+        </is>
+      </c>
       <c r="G416" t="n">
         <v>3</v>
       </c>
@@ -11760,21 +11760,17 @@
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>MX</t>
+          <t>US</t>
         </is>
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>Current AccountQ4</t>
+          <t>Richmond Fed Manufacturing Shipments IndexFEB</t>
         </is>
       </c>
       <c r="D417" t="inlineStr"/>
       <c r="E417" t="inlineStr"/>
-      <c r="F417" t="inlineStr">
-        <is>
-          <t>$ 7500M</t>
-        </is>
-      </c>
+      <c r="F417" t="inlineStr"/>
       <c r="G417" t="n">
         <v>3</v>
       </c>
@@ -11792,7 +11788,7 @@
       </c>
       <c r="C418" t="inlineStr">
         <is>
-          <t>Richmond Fed Services Revenues IndexFEB</t>
+          <t>Richmond Fed Manufacturing IndexFEB</t>
         </is>
       </c>
       <c r="D418" t="inlineStr"/>
@@ -11810,17 +11806,21 @@
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>EA</t>
         </is>
       </c>
       <c r="C419" t="inlineStr">
         <is>
-          <t>Richmond Fed Manufacturing IndexFEB</t>
+          <t>Negotiated Wage GrowthQ4</t>
         </is>
       </c>
       <c r="D419" t="inlineStr"/>
       <c r="E419" t="inlineStr"/>
-      <c r="F419" t="inlineStr"/>
+      <c r="F419" t="inlineStr">
+        <is>
+          <t>5.1%</t>
+        </is>
+      </c>
       <c r="G419" t="n">
         <v>3</v>
       </c>
@@ -11838,14 +11838,14 @@
       </c>
       <c r="C420" t="inlineStr">
         <is>
-          <t>CB Consumer ConfidenceFEB</t>
+          <t>Richmond Fed Services Revenues IndexFEB</t>
         </is>
       </c>
       <c r="D420" t="inlineStr"/>
       <c r="E420" t="inlineStr"/>
       <c r="F420" t="inlineStr"/>
       <c r="G420" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="421">
@@ -11861,7 +11861,7 @@
       </c>
       <c r="C421" t="inlineStr">
         <is>
-          <t>Dallas Fed Services Revenues IndexFEB</t>
+          <t>Dallas Fed Services IndexFEB</t>
         </is>
       </c>
       <c r="D421" t="inlineStr"/>
@@ -11879,21 +11879,17 @@
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>EA</t>
+          <t>US</t>
         </is>
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>Negotiated Wage GrowthQ4</t>
+          <t>Dallas Fed Services Revenues IndexFEB</t>
         </is>
       </c>
       <c r="D422" t="inlineStr"/>
       <c r="E422" t="inlineStr"/>
-      <c r="F422" t="inlineStr">
-        <is>
-          <t>5.1%</t>
-        </is>
-      </c>
+      <c r="F422" t="inlineStr"/>
       <c r="G422" t="n">
         <v>3</v>
       </c>
@@ -11906,17 +11902,21 @@
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>EA</t>
         </is>
       </c>
       <c r="C423" t="inlineStr">
         <is>
-          <t>Dallas Fed Services IndexFEB</t>
+          <t>Negotiated Wage GrowthQ4</t>
         </is>
       </c>
       <c r="D423" t="inlineStr"/>
       <c r="E423" t="inlineStr"/>
-      <c r="F423" t="inlineStr"/>
+      <c r="F423" t="inlineStr">
+        <is>
+          <t>5.1%</t>
+        </is>
+      </c>
       <c r="G423" t="n">
         <v>3</v>
       </c>
@@ -11952,17 +11952,21 @@
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>EA</t>
         </is>
       </c>
       <c r="C425" t="inlineStr">
         <is>
-          <t>Money SupplyJAN</t>
+          <t>Negotiated Wage GrowthQ4</t>
         </is>
       </c>
       <c r="D425" t="inlineStr"/>
       <c r="E425" t="inlineStr"/>
-      <c r="F425" t="inlineStr"/>
+      <c r="F425" t="inlineStr">
+        <is>
+          <t>5.1%</t>
+        </is>
+      </c>
       <c r="G425" t="n">
         <v>3</v>
       </c>
@@ -11975,21 +11979,17 @@
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>EA</t>
+          <t>US</t>
         </is>
       </c>
       <c r="C426" t="inlineStr">
         <is>
-          <t>Negotiated Wage GrowthQ4</t>
+          <t>Money SupplyJAN</t>
         </is>
       </c>
       <c r="D426" t="inlineStr"/>
       <c r="E426" t="inlineStr"/>
-      <c r="F426" t="inlineStr">
-        <is>
-          <t>5.1%</t>
-        </is>
-      </c>
+      <c r="F426" t="inlineStr"/>
       <c r="G426" t="n">
         <v>3</v>
       </c>
@@ -12046,6 +12046,56 @@
       </c>
       <c r="G428" t="n">
         <v>3</v>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="inlineStr">
+        <is>
+          <t>2025-02-25 16:30:00-05:00</t>
+        </is>
+      </c>
+      <c r="B429" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="C429" t="inlineStr">
+        <is>
+          <t>API Crude Oil Stock ChangeFEB/21</t>
+        </is>
+      </c>
+      <c r="D429" t="inlineStr"/>
+      <c r="E429" t="inlineStr"/>
+      <c r="F429" t="inlineStr"/>
+      <c r="G429" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="inlineStr">
+        <is>
+          <t>2025-02-25 16:30:00-05:00</t>
+        </is>
+      </c>
+      <c r="B430" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="C430" t="inlineStr">
+        <is>
+          <t>Negotiated Wage GrowthQ4</t>
+        </is>
+      </c>
+      <c r="D430" t="inlineStr"/>
+      <c r="E430" t="inlineStr"/>
+      <c r="F430" t="inlineStr">
+        <is>
+          <t>5.1%</t>
+        </is>
+      </c>
+      <c r="G430" t="n">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
